--- a/templates/SALES_REPORT_TEMPLATE.xlsx
+++ b/templates/SALES_REPORT_TEMPLATE.xlsx
@@ -15,9 +15,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="100">
-  <si>
-    <t>nw</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="99">
+  <si>
+    <t>Date</t>
   </si>
   <si>
     <t>Order Number</t>
@@ -95,9 +95,6 @@
     <t>Prime</t>
   </si>
   <si>
-    <t>Date</t>
-  </si>
-  <si>
     <t>Order No</t>
   </si>
   <si>
@@ -236,7 +233,7 @@
     <t>What the importer does with it</t>
   </si>
   <si>
-    <t>Date / DATE / nw</t>
+    <t>Date / DATE</t>
   </si>
   <si>
     <t>Yes</t>
@@ -245,7 +242,7 @@
     <t>yyyy-mm-dd (or any Excel date cell)</t>
   </si>
   <si>
-    <t>Sale date. Drives every period figure — Sold Today, This Month, and the date-range reports. A row with no readable date is rejected.</t>
+    <t>Sale date. Drives every period figure — Sold Today, This Month, and the date-range reports. A row with no readable date is rejected. Older Amazon files head this column "nw"; that is still accepted, but new files should say Date.</t>
   </si>
   <si>
     <t>Free text, e.g. AMZ-5001</t>
@@ -917,10 +914,10 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -941,7 +938,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>8</v>
@@ -950,7 +947,7 @@
         <v>9</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>10</v>
@@ -973,16 +970,16 @@
         <v>15</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="F2" s="2">
         <v>1</v>
@@ -994,7 +991,7 @@
         <v>329</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>20</v>
@@ -1047,22 +1044,22 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
@@ -1074,51 +1071,51 @@
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>12</v>
       </c>
       <c r="R1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="F2" s="2">
         <v>1</v>
@@ -1187,7 +1184,7 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -1211,22 +1208,22 @@
         <v>8</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>57</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>14</v>
@@ -1234,19 +1231,19 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="F2" s="2">
         <v>275</v>
@@ -1302,60 +1299,60 @@
   <sheetData>
     <row r="1" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="C9" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="D9" s="6" t="s">
         <v>71</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="C10" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="D10" s="8" t="s">
         <v>75</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1363,13 +1360,13 @@
         <v>1</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C11" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D11" s="8" t="s">
         <v>77</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1377,13 +1374,13 @@
         <v>2</v>
       </c>
       <c r="B12" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="D12" s="8" t="s">
         <v>80</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1391,13 +1388,13 @@
         <v>3</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C13" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="D13" s="8" t="s">
         <v>82</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1405,27 +1402,27 @@
         <v>4</v>
       </c>
       <c r="B14" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="C14" s="8" t="s">
-        <v>80</v>
-      </c>
       <c r="D14" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="B15" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="C15" s="8" t="s">
+      <c r="D15" s="8" t="s">
         <v>86</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1433,13 +1430,13 @@
         <v>6</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C16" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="D16" s="8" t="s">
         <v>88</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1447,41 +1444,41 @@
         <v>7</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C18" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D18" s="8" t="s">
         <v>91</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>92</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C19" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="B19" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="C19" s="8" t="s">
+      <c r="D19" s="8" t="s">
         <v>94</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1489,27 +1486,27 @@
         <v>14</v>
       </c>
       <c r="B20" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C20" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="C20" s="8" t="s">
-        <v>80</v>
-      </c>
       <c r="D20" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>96</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C21" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="B21" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="C21" s="8" t="s">
+      <c r="D21" s="8" t="s">
         <v>98</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/templates/SALES_REPORT_TEMPLATE.xlsx
+++ b/templates/SALES_REPORT_TEMPLATE.xlsx
@@ -8,14 +8,15 @@
     <sheet sheetId="2" name="BM" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="EBAY" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="ONBUY" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="README" state="visible" r:id="rId8"/>
+    <sheet sheetId="5" name="TEMU" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="README" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="104">
   <si>
     <t>Date</t>
   </si>
@@ -201,6 +202,21 @@
   </si>
   <si>
     <t>NORTHSIDE STOCK</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>PO-210-07053322437751959</t>
+  </si>
+  <si>
+    <t>SG-A17-128GB-OB</t>
+  </si>
+  <si>
+    <t>350901801557294</t>
+  </si>
+  <si>
+    <t>MHL</t>
   </si>
   <si>
     <t>SALES REPORT — upload template</t>
@@ -1285,6 +1301,122 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:O2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="4" width="12" customWidth="1"/>
+    <col min="5" max="6" width="16" customWidth="1"/>
+    <col min="7" max="9" width="12" customWidth="1"/>
+    <col min="10" max="12" width="16" customWidth="1"/>
+    <col min="13" max="14" width="12" customWidth="1"/>
+    <col min="15" max="15" width="28" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F2" s="2">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2">
+        <v>100</v>
+      </c>
+      <c r="H2" s="2">
+        <v>119.33</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="2">
+        <v>6.3</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:O1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF10B981"/>
   </sheetPr>
@@ -1299,60 +1431,60 @@
   <sheetData>
     <row r="1" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1360,13 +1492,13 @@
         <v>1</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1374,13 +1506,13 @@
         <v>2</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1388,13 +1520,13 @@
         <v>3</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1402,27 +1534,27 @@
         <v>4</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1430,13 +1562,13 @@
         <v>6</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1444,13 +1576,13 @@
         <v>7</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1458,27 +1590,27 @@
         <v>27</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1486,27 +1618,27 @@
         <v>14</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/templates/SALES_REPORT_TEMPLATE.xlsx
+++ b/templates/SALES_REPORT_TEMPLATE.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="109">
   <si>
     <t>Date</t>
   </si>
@@ -204,7 +204,22 @@
     <t>NORTHSIDE STOCK</t>
   </si>
   <si>
-    <t>2026-07-24</t>
+    <t>Commission VAT</t>
+  </si>
+  <si>
+    <t>P. VAT</t>
+  </si>
+  <si>
+    <t>Acc</t>
+  </si>
+  <si>
+    <t>Total VAT</t>
+  </si>
+  <si>
+    <t>Total VAT NTP</t>
+  </si>
+  <si>
+    <t>2026-06-18</t>
   </si>
   <si>
     <t>PO-210-07053322437751959</t>
@@ -1301,7 +1316,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:S2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1309,12 +1324,14 @@
     <col min="3" max="4" width="12" customWidth="1"/>
     <col min="5" max="6" width="16" customWidth="1"/>
     <col min="7" max="9" width="12" customWidth="1"/>
-    <col min="10" max="12" width="16" customWidth="1"/>
-    <col min="13" max="14" width="12" customWidth="1"/>
-    <col min="15" max="15" width="28" customWidth="1"/>
+    <col min="10" max="14" width="16" customWidth="1"/>
+    <col min="15" max="15" width="12" customWidth="1"/>
+    <col min="16" max="16" width="16" customWidth="1"/>
+    <col min="17" max="18" width="12" customWidth="1"/>
+    <col min="19" max="19" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" ht="22" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1349,42 +1366,54 @@
         <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="S1" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F2" s="2">
         <v>1</v>
       </c>
       <c r="G2" s="2">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="H2" s="2">
-        <v>119.33</v>
+        <v>83.99</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>20</v>
@@ -1392,24 +1421,36 @@
       <c r="J2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>20</v>
+      <c r="K2" s="2">
+        <v>3.87</v>
       </c>
       <c r="L2" s="2">
+        <v>4.07</v>
+      </c>
+      <c r="M2" s="2">
         <v>6.3</v>
       </c>
-      <c r="M2" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="N2" s="2" t="s">
         <v>20</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>20</v>
       </c>
+      <c r="P2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O1"/>
+  <autoFilter ref="A1:S1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -1431,60 +1472,60 @@
   <sheetData>
     <row r="1" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1492,13 +1533,13 @@
         <v>1</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1506,13 +1547,13 @@
         <v>2</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1520,13 +1561,13 @@
         <v>3</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1534,27 +1575,27 @@
         <v>4</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1562,13 +1603,13 @@
         <v>6</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1576,13 +1617,13 @@
         <v>7</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1590,27 +1631,27 @@
         <v>27</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1618,27 +1659,27 @@
         <v>14</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/templates/SALES_REPORT_TEMPLATE.xlsx
+++ b/templates/SALES_REPORT_TEMPLATE.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="83">
   <si>
     <t>Date</t>
   </si>
@@ -111,22 +111,22 @@
     <t>Colour</t>
   </si>
   <si>
-    <t>AMAZON-EXAMPLE</t>
+    <t>AMZ-5001</t>
   </si>
   <si>
-    <t>SG-A24-128-DS-BK-EX</t>
+    <t>IP13-128-MID</t>
   </si>
   <si>
-    <t>350100000000001</t>
+    <t>350100000000000</t>
   </si>
   <si>
-    <t>EXAMPLE SUPPLIER</t>
+    <t>MOBILE WHOLESALE LTD</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>Samsung Galaxy A24 128GB</t>
+    <t>Apple iPhone 13 128GB</t>
   </si>
   <si>
     <t>TOTAL</t>
@@ -135,13 +135,16 @@
     <t>Customer Care Fees</t>
   </si>
   <si>
-    <t>BM-EXAMPLE</t>
+    <t>BM-7781</t>
   </si>
   <si>
-    <t>SG-A23-128-BK-EX</t>
+    <t>S22-128-GRN</t>
   </si>
   <si>
-    <t>Samsung Galaxy A23 128GB</t>
+    <t>350100000015838</t>
+  </si>
+  <si>
+    <t>PHONEBOX DIRECT</t>
   </si>
   <si>
     <t>Units</t>
@@ -165,34 +168,49 @@
     <t>M. VAT</t>
   </si>
   <si>
-    <t>EBAY-EXAMPLE</t>
+    <t>EB-3310</t>
   </si>
   <si>
-    <t>SG-XC5-64-BK</t>
+    <t>IP13P-256-GRA</t>
   </si>
   <si>
-    <t>Samsung Galaxy XC5 64GB</t>
+    <t>350100000023757</t>
+  </si>
+  <si>
+    <t>CELLHUB TRADING</t>
+  </si>
+  <si>
+    <t>Apple iPhone 13P 256GB</t>
   </si>
   <si>
     <t>VAT 20%</t>
   </si>
   <si>
-    <t>ONBUY-EXAMPLE</t>
+    <t>OB-9002</t>
   </si>
   <si>
-    <t>ASI-SG-S20-128-CG</t>
+    <t>PIX7-128-BLK</t>
   </si>
   <si>
-    <t>Samsung Galaxy S20 128GB</t>
+    <t>350100000031676</t>
+  </si>
+  <si>
+    <t>NORTHSIDE STOCK</t>
   </si>
   <si>
     <t>Commission VAT</t>
   </si>
   <si>
-    <t>TEMU-EXAMPLE</t>
+    <t>PO-210-07053322437751959</t>
   </si>
   <si>
     <t>SG-A17-128GB-OB</t>
+  </si>
+  <si>
+    <t>350901801557294</t>
+  </si>
+  <si>
+    <t>MHL</t>
   </si>
   <si>
     <t>Samsung Galaxy A17 128GB</t>
@@ -659,7 +677,7 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B1" t="s">
         <v>35</v>
@@ -667,66 +685,66 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -855,10 +873,10 @@
         <v>1</v>
       </c>
       <c r="G2" s="3">
-        <v>100</v>
+        <v>320</v>
       </c>
       <c r="H2" s="3">
-        <v>139.99</v>
+        <v>425</v>
       </c>
       <c r="I2" s="3">
         <f>IF($H2="","",H2-G2)</f>
@@ -879,7 +897,7 @@
         <f>IF($H2="","",M2*20%)</f>
       </c>
       <c r="O2" s="3">
-        <v>6.3</v>
+        <v>8</v>
       </c>
       <c r="P2" s="3">
         <f>IF($H2="","",O2*20%)</f>
@@ -10294,19 +10312,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2" s="3">
-        <v>73</v>
+        <v>240</v>
       </c>
       <c r="H2" s="3">
-        <v>129</v>
+        <v>329</v>
       </c>
       <c r="I2" s="3">
         <f>IF($H2="","",H2-G2)</f>
@@ -10321,7 +10339,7 @@
         <v>8.99</v>
       </c>
       <c r="M2" s="3">
-        <v>6.3</v>
+        <v>8</v>
       </c>
       <c r="N2" s="3">
         <f>IF($H2="","",M2*20%)</f>
@@ -10342,7 +10360,7 @@
         <v>35</v>
       </c>
       <c r="T2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Z2" s="3">
         <f>IF($H2="","",P2-Y2)</f>
@@ -17844,7 +17862,7 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G1" t="s">
         <v>6</v>
@@ -17862,16 +17880,16 @@
         <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P1" t="s">
         <v>14</v>
@@ -17880,10 +17898,10 @@
         <v>15</v>
       </c>
       <c r="R1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="S1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="T1" t="s">
         <v>16</v>
@@ -17936,25 +17954,25 @@
         <v>46235.5</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="E2" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2" s="3">
-        <v>30</v>
+        <v>520</v>
       </c>
       <c r="H2" s="3">
-        <v>55.99</v>
+        <v>679</v>
       </c>
       <c r="I2" s="3">
         <f>IF($H2="","",H2-G2)</f>
@@ -17978,7 +17996,7 @@
         <f>IF($H2="","",K2+L2+M2+N2)</f>
       </c>
       <c r="P2" s="3">
-        <v>4.65</v>
+        <v>8</v>
       </c>
       <c r="Q2" s="3">
         <v>0</v>
@@ -18008,7 +18026,7 @@
         <v>35</v>
       </c>
       <c r="Z2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="AF2" s="3">
         <f>IF($H2="","",V2-AE2)</f>
@@ -28343,7 +28361,7 @@
         <v>10</v>
       </c>
       <c r="K1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="L1" t="s">
         <v>14</v>
@@ -28402,22 +28420,22 @@
         <v>46235.5</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="E2" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="F2" s="3">
-        <v>110</v>
+        <v>275</v>
       </c>
       <c r="G2" s="3">
-        <v>159.99</v>
+        <v>359</v>
       </c>
       <c r="H2" s="3">
         <f>IF($G2="","",G2-F2)</f>
@@ -28432,7 +28450,7 @@
         <f>IF($G2="","",J2*20%)</f>
       </c>
       <c r="L2" s="3">
-        <v>6.3</v>
+        <v>8</v>
       </c>
       <c r="M2" s="3">
         <f>IF($G2="","",L2*20%)</f>
@@ -28456,7 +28474,7 @@
         <v>35</v>
       </c>
       <c r="T2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Z2" s="3">
         <f>IF($G2="","",P2-Y2)</f>
@@ -36576,7 +36594,7 @@
         <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="M1" t="s">
         <v>14</v>
@@ -36635,16 +36653,16 @@
         <v>46235.5</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="E2" t="s">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -36692,7 +36710,7 @@
         <v>35</v>
       </c>
       <c r="U2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="AA2" s="3">
         <f>IF($H2="","",Q2-Z2)</f>

--- a/templates/SALES_REPORT_TEMPLATE.xlsx
+++ b/templates/SALES_REPORT_TEMPLATE.xlsx
@@ -879,43 +879,43 @@
         <v>425</v>
       </c>
       <c r="I2" s="3">
-        <f>IF($H2="","",H2-G2)</f>
+        <f>H2-G2</f>
       </c>
       <c r="J2" s="3">
-        <f>IF($H2="","",I2*16.67%)</f>
+        <f>I2*16.67%</f>
       </c>
       <c r="K2" s="3">
-        <f>IF($H2="","",H2/100*7)</f>
+        <f>H2/100*7</f>
       </c>
       <c r="L2" s="3">
-        <f>IF($H2="","",K2*20%)</f>
+        <f>K2*20%</f>
       </c>
       <c r="M2" s="3">
-        <f>IF($H2="","",K2*2%)</f>
+        <f>K2*2%</f>
       </c>
       <c r="N2" s="3">
-        <f>IF($H2="","",M2*20%)</f>
+        <f>M2*20%</f>
       </c>
       <c r="O2" s="3">
         <v>8</v>
       </c>
       <c r="P2" s="3">
-        <f>IF($H2="","",O2*20%)</f>
+        <f>O2*20%</f>
       </c>
       <c r="Q2" s="3">
         <v>1</v>
       </c>
       <c r="R2" s="3">
-        <f>IF($H2="","",L2+N2+P2)</f>
+        <f>L2+N2+P2</f>
       </c>
       <c r="S2" s="3">
-        <f>IF($H2="","",I2-J2-K2-L2-M2-N2-O2-P2-Q2)</f>
+        <f>I2-J2-K2-L2-M2-N2-O2-P2-Q2</f>
       </c>
       <c r="T2" s="3">
-        <f>IF($H2="","",(S2-AB2)/G2*100)</f>
+        <f>(S2-AB2)/G2*100</f>
       </c>
       <c r="U2" s="3">
-        <f>IF($H2="","",J2-R2)</f>
+        <f>J2-R2</f>
       </c>
       <c r="V2" t="s">
         <v>35</v>
@@ -924,7 +924,7 @@
         <v>36</v>
       </c>
       <c r="AC2" s="3">
-        <f>IF($H2="","",S2-AB2)</f>
+        <f>S2-AB2</f>
       </c>
       <c r="AD2" t="s">
         <v>35</v>
@@ -933,7 +933,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="D3" s="2"/>
       <c r="G3" s="3"/>
@@ -979,7 +979,7 @@
         <f>IF($H3="","",S3-AB3)</f>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="D4" s="2"/>
       <c r="G4" s="3"/>
@@ -1025,7 +1025,7 @@
         <f>IF($H4="","",S4-AB4)</f>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="D5" s="2"/>
       <c r="G5" s="3"/>
@@ -1071,7 +1071,7 @@
         <f>IF($H5="","",S5-AB5)</f>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="D6" s="2"/>
       <c r="G6" s="3"/>
@@ -1117,7 +1117,7 @@
         <f>IF($H6="","",S6-AB6)</f>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="D7" s="2"/>
       <c r="G7" s="3"/>
@@ -1163,7 +1163,7 @@
         <f>IF($H7="","",S7-AB7)</f>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="D8" s="2"/>
       <c r="G8" s="3"/>
@@ -1209,7 +1209,7 @@
         <f>IF($H8="","",S8-AB8)</f>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="D9" s="2"/>
       <c r="G9" s="3"/>
@@ -1255,7 +1255,7 @@
         <f>IF($H9="","",S9-AB9)</f>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="D10" s="2"/>
       <c r="G10" s="3"/>
@@ -1301,7 +1301,7 @@
         <f>IF($H10="","",S10-AB10)</f>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="D11" s="2"/>
       <c r="G11" s="3"/>
@@ -1347,7 +1347,7 @@
         <f>IF($H11="","",S11-AB11)</f>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="D12" s="2"/>
       <c r="G12" s="3"/>
@@ -1393,7 +1393,7 @@
         <f>IF($H12="","",S12-AB12)</f>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="D13" s="2"/>
       <c r="G13" s="3"/>
@@ -1439,7 +1439,7 @@
         <f>IF($H13="","",S13-AB13)</f>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="D14" s="2"/>
       <c r="G14" s="3"/>
@@ -1485,7 +1485,7 @@
         <f>IF($H14="","",S14-AB14)</f>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="D15" s="2"/>
       <c r="G15" s="3"/>
@@ -1531,7 +1531,7 @@
         <f>IF($H15="","",S15-AB15)</f>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="D16" s="2"/>
       <c r="G16" s="3"/>
@@ -1577,7 +1577,7 @@
         <f>IF($H16="","",S16-AB16)</f>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="D17" s="2"/>
       <c r="G17" s="3"/>
@@ -1623,7 +1623,7 @@
         <f>IF($H17="","",S17-AB17)</f>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="D18" s="2"/>
       <c r="G18" s="3"/>
@@ -1669,7 +1669,7 @@
         <f>IF($H18="","",S18-AB18)</f>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="D19" s="2"/>
       <c r="G19" s="3"/>
@@ -1715,7 +1715,7 @@
         <f>IF($H19="","",S19-AB19)</f>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="D20" s="2"/>
       <c r="G20" s="3"/>
@@ -1761,7 +1761,7 @@
         <f>IF($H20="","",S20-AB20)</f>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="D21" s="2"/>
       <c r="G21" s="3"/>
@@ -1807,7 +1807,7 @@
         <f>IF($H21="","",S21-AB21)</f>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="D22" s="2"/>
       <c r="G22" s="3"/>
@@ -1853,7 +1853,7 @@
         <f>IF($H22="","",S22-AB22)</f>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="D23" s="2"/>
       <c r="G23" s="3"/>
@@ -1899,7 +1899,7 @@
         <f>IF($H23="","",S23-AB23)</f>
       </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="D24" s="2"/>
       <c r="G24" s="3"/>
@@ -1945,7 +1945,7 @@
         <f>IF($H24="","",S24-AB24)</f>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="D25" s="2"/>
       <c r="G25" s="3"/>
@@ -1991,7 +1991,7 @@
         <f>IF($H25="","",S25-AB25)</f>
       </c>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="D26" s="2"/>
       <c r="G26" s="3"/>
@@ -2037,7 +2037,7 @@
         <f>IF($H26="","",S26-AB26)</f>
       </c>
     </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="D27" s="2"/>
       <c r="G27" s="3"/>
@@ -2083,7 +2083,7 @@
         <f>IF($H27="","",S27-AB27)</f>
       </c>
     </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="D28" s="2"/>
       <c r="G28" s="3"/>
@@ -2129,7 +2129,7 @@
         <f>IF($H28="","",S28-AB28)</f>
       </c>
     </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="D29" s="2"/>
       <c r="G29" s="3"/>
@@ -2175,7 +2175,7 @@
         <f>IF($H29="","",S29-AB29)</f>
       </c>
     </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="D30" s="2"/>
       <c r="G30" s="3"/>
@@ -2221,7 +2221,7 @@
         <f>IF($H30="","",S30-AB30)</f>
       </c>
     </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="D31" s="2"/>
       <c r="G31" s="3"/>
@@ -2267,7 +2267,7 @@
         <f>IF($H31="","",S31-AB31)</f>
       </c>
     </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="D32" s="2"/>
       <c r="G32" s="3"/>
@@ -2313,7 +2313,7 @@
         <f>IF($H32="","",S32-AB32)</f>
       </c>
     </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="D33" s="2"/>
       <c r="G33" s="3"/>
@@ -2359,7 +2359,7 @@
         <f>IF($H33="","",S33-AB33)</f>
       </c>
     </row>
-    <row r="34" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="D34" s="2"/>
       <c r="G34" s="3"/>
@@ -2405,7 +2405,7 @@
         <f>IF($H34="","",S34-AB34)</f>
       </c>
     </row>
-    <row r="35" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="D35" s="2"/>
       <c r="G35" s="3"/>
@@ -2451,7 +2451,7 @@
         <f>IF($H35="","",S35-AB35)</f>
       </c>
     </row>
-    <row r="36" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="D36" s="2"/>
       <c r="G36" s="3"/>
@@ -2497,7 +2497,7 @@
         <f>IF($H36="","",S36-AB36)</f>
       </c>
     </row>
-    <row r="37" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="D37" s="2"/>
       <c r="G37" s="3"/>
@@ -2543,7 +2543,7 @@
         <f>IF($H37="","",S37-AB37)</f>
       </c>
     </row>
-    <row r="38" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="D38" s="2"/>
       <c r="G38" s="3"/>
@@ -2589,7 +2589,7 @@
         <f>IF($H38="","",S38-AB38)</f>
       </c>
     </row>
-    <row r="39" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="D39" s="2"/>
       <c r="G39" s="3"/>
@@ -2635,7 +2635,7 @@
         <f>IF($H39="","",S39-AB39)</f>
       </c>
     </row>
-    <row r="40" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="D40" s="2"/>
       <c r="G40" s="3"/>
@@ -2681,7 +2681,7 @@
         <f>IF($H40="","",S40-AB40)</f>
       </c>
     </row>
-    <row r="41" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="D41" s="2"/>
       <c r="G41" s="3"/>
@@ -2727,7 +2727,7 @@
         <f>IF($H41="","",S41-AB41)</f>
       </c>
     </row>
-    <row r="42" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="D42" s="2"/>
       <c r="G42" s="3"/>
@@ -2773,7 +2773,7 @@
         <f>IF($H42="","",S42-AB42)</f>
       </c>
     </row>
-    <row r="43" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="D43" s="2"/>
       <c r="G43" s="3"/>
@@ -2819,7 +2819,7 @@
         <f>IF($H43="","",S43-AB43)</f>
       </c>
     </row>
-    <row r="44" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="D44" s="2"/>
       <c r="G44" s="3"/>
@@ -2865,7 +2865,7 @@
         <f>IF($H44="","",S44-AB44)</f>
       </c>
     </row>
-    <row r="45" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="D45" s="2"/>
       <c r="G45" s="3"/>
@@ -2911,7 +2911,7 @@
         <f>IF($H45="","",S45-AB45)</f>
       </c>
     </row>
-    <row r="46" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="D46" s="2"/>
       <c r="G46" s="3"/>
@@ -2957,7 +2957,7 @@
         <f>IF($H46="","",S46-AB46)</f>
       </c>
     </row>
-    <row r="47" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="D47" s="2"/>
       <c r="G47" s="3"/>
@@ -3003,7 +3003,7 @@
         <f>IF($H47="","",S47-AB47)</f>
       </c>
     </row>
-    <row r="48" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="D48" s="2"/>
       <c r="G48" s="3"/>
@@ -3049,7 +3049,7 @@
         <f>IF($H48="","",S48-AB48)</f>
       </c>
     </row>
-    <row r="49" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
       <c r="D49" s="2"/>
       <c r="G49" s="3"/>
@@ -3095,7 +3095,7 @@
         <f>IF($H49="","",S49-AB49)</f>
       </c>
     </row>
-    <row r="50" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
       <c r="D50" s="2"/>
       <c r="G50" s="3"/>
@@ -3141,7 +3141,7 @@
         <f>IF($H50="","",S50-AB50)</f>
       </c>
     </row>
-    <row r="51" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
       <c r="D51" s="2"/>
       <c r="G51" s="3"/>
@@ -3187,7 +3187,7 @@
         <f>IF($H51="","",S51-AB51)</f>
       </c>
     </row>
-    <row r="52" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
       <c r="D52" s="2"/>
       <c r="G52" s="3"/>
@@ -3233,7 +3233,7 @@
         <f>IF($H52="","",S52-AB52)</f>
       </c>
     </row>
-    <row r="53" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
       <c r="D53" s="2"/>
       <c r="G53" s="3"/>
@@ -3279,7 +3279,7 @@
         <f>IF($H53="","",S53-AB53)</f>
       </c>
     </row>
-    <row r="54" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
       <c r="D54" s="2"/>
       <c r="G54" s="3"/>
@@ -3325,7 +3325,7 @@
         <f>IF($H54="","",S54-AB54)</f>
       </c>
     </row>
-    <row r="55" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
       <c r="D55" s="2"/>
       <c r="G55" s="3"/>
@@ -3371,7 +3371,7 @@
         <f>IF($H55="","",S55-AB55)</f>
       </c>
     </row>
-    <row r="56" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
       <c r="D56" s="2"/>
       <c r="G56" s="3"/>
@@ -3417,7 +3417,7 @@
         <f>IF($H56="","",S56-AB56)</f>
       </c>
     </row>
-    <row r="57" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
       <c r="D57" s="2"/>
       <c r="G57" s="3"/>
@@ -3463,7 +3463,7 @@
         <f>IF($H57="","",S57-AB57)</f>
       </c>
     </row>
-    <row r="58" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
       <c r="D58" s="2"/>
       <c r="G58" s="3"/>
@@ -3509,7 +3509,7 @@
         <f>IF($H58="","",S58-AB58)</f>
       </c>
     </row>
-    <row r="59" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
       <c r="D59" s="2"/>
       <c r="G59" s="3"/>
@@ -3555,7 +3555,7 @@
         <f>IF($H59="","",S59-AB59)</f>
       </c>
     </row>
-    <row r="60" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
       <c r="D60" s="2"/>
       <c r="G60" s="3"/>
@@ -3601,7 +3601,7 @@
         <f>IF($H60="","",S60-AB60)</f>
       </c>
     </row>
-    <row r="61" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
       <c r="D61" s="2"/>
       <c r="G61" s="3"/>
@@ -3647,7 +3647,7 @@
         <f>IF($H61="","",S61-AB61)</f>
       </c>
     </row>
-    <row r="62" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
       <c r="D62" s="2"/>
       <c r="G62" s="3"/>
@@ -3693,7 +3693,7 @@
         <f>IF($H62="","",S62-AB62)</f>
       </c>
     </row>
-    <row r="63" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
       <c r="D63" s="2"/>
       <c r="G63" s="3"/>
@@ -3739,7 +3739,7 @@
         <f>IF($H63="","",S63-AB63)</f>
       </c>
     </row>
-    <row r="64" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
       <c r="D64" s="2"/>
       <c r="G64" s="3"/>
@@ -3785,7 +3785,7 @@
         <f>IF($H64="","",S64-AB64)</f>
       </c>
     </row>
-    <row r="65" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
       <c r="D65" s="2"/>
       <c r="G65" s="3"/>
@@ -3831,7 +3831,7 @@
         <f>IF($H65="","",S65-AB65)</f>
       </c>
     </row>
-    <row r="66" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
       <c r="D66" s="2"/>
       <c r="G66" s="3"/>
@@ -3877,7 +3877,7 @@
         <f>IF($H66="","",S66-AB66)</f>
       </c>
     </row>
-    <row r="67" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
       <c r="D67" s="2"/>
       <c r="G67" s="3"/>
@@ -3923,7 +3923,7 @@
         <f>IF($H67="","",S67-AB67)</f>
       </c>
     </row>
-    <row r="68" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
       <c r="D68" s="2"/>
       <c r="G68" s="3"/>
@@ -3969,7 +3969,7 @@
         <f>IF($H68="","",S68-AB68)</f>
       </c>
     </row>
-    <row r="69" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
       <c r="D69" s="2"/>
       <c r="G69" s="3"/>
@@ -4015,7 +4015,7 @@
         <f>IF($H69="","",S69-AB69)</f>
       </c>
     </row>
-    <row r="70" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
       <c r="D70" s="2"/>
       <c r="G70" s="3"/>
@@ -4061,7 +4061,7 @@
         <f>IF($H70="","",S70-AB70)</f>
       </c>
     </row>
-    <row r="71" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
       <c r="D71" s="2"/>
       <c r="G71" s="3"/>
@@ -4107,7 +4107,7 @@
         <f>IF($H71="","",S71-AB71)</f>
       </c>
     </row>
-    <row r="72" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
       <c r="D72" s="2"/>
       <c r="G72" s="3"/>
@@ -4153,7 +4153,7 @@
         <f>IF($H72="","",S72-AB72)</f>
       </c>
     </row>
-    <row r="73" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
       <c r="D73" s="2"/>
       <c r="G73" s="3"/>
@@ -4199,7 +4199,7 @@
         <f>IF($H73="","",S73-AB73)</f>
       </c>
     </row>
-    <row r="74" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
       <c r="D74" s="2"/>
       <c r="G74" s="3"/>
@@ -4245,7 +4245,7 @@
         <f>IF($H74="","",S74-AB74)</f>
       </c>
     </row>
-    <row r="75" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
       <c r="D75" s="2"/>
       <c r="G75" s="3"/>
@@ -4291,7 +4291,7 @@
         <f>IF($H75="","",S75-AB75)</f>
       </c>
     </row>
-    <row r="76" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
       <c r="D76" s="2"/>
       <c r="G76" s="3"/>
@@ -4337,7 +4337,7 @@
         <f>IF($H76="","",S76-AB76)</f>
       </c>
     </row>
-    <row r="77" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
       <c r="D77" s="2"/>
       <c r="G77" s="3"/>
@@ -4383,7 +4383,7 @@
         <f>IF($H77="","",S77-AB77)</f>
       </c>
     </row>
-    <row r="78" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
       <c r="D78" s="2"/>
       <c r="G78" s="3"/>
@@ -4429,7 +4429,7 @@
         <f>IF($H78="","",S78-AB78)</f>
       </c>
     </row>
-    <row r="79" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="D79" s="2"/>
       <c r="G79" s="3"/>
@@ -4475,7 +4475,7 @@
         <f>IF($H79="","",S79-AB79)</f>
       </c>
     </row>
-    <row r="80" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
       <c r="D80" s="2"/>
       <c r="G80" s="3"/>
@@ -4521,7 +4521,7 @@
         <f>IF($H80="","",S80-AB80)</f>
       </c>
     </row>
-    <row r="81" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
       <c r="D81" s="2"/>
       <c r="G81" s="3"/>
@@ -4567,7 +4567,7 @@
         <f>IF($H81="","",S81-AB81)</f>
       </c>
     </row>
-    <row r="82" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
       <c r="D82" s="2"/>
       <c r="G82" s="3"/>
@@ -4613,7 +4613,7 @@
         <f>IF($H82="","",S82-AB82)</f>
       </c>
     </row>
-    <row r="83" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
       <c r="D83" s="2"/>
       <c r="G83" s="3"/>
@@ -4659,7 +4659,7 @@
         <f>IF($H83="","",S83-AB83)</f>
       </c>
     </row>
-    <row r="84" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
       <c r="D84" s="2"/>
       <c r="G84" s="3"/>
@@ -4705,7 +4705,7 @@
         <f>IF($H84="","",S84-AB84)</f>
       </c>
     </row>
-    <row r="85" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="D85" s="2"/>
       <c r="G85" s="3"/>
@@ -4751,7 +4751,7 @@
         <f>IF($H85="","",S85-AB85)</f>
       </c>
     </row>
-    <row r="86" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="D86" s="2"/>
       <c r="G86" s="3"/>
@@ -4797,7 +4797,7 @@
         <f>IF($H86="","",S86-AB86)</f>
       </c>
     </row>
-    <row r="87" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="D87" s="2"/>
       <c r="G87" s="3"/>
@@ -4843,7 +4843,7 @@
         <f>IF($H87="","",S87-AB87)</f>
       </c>
     </row>
-    <row r="88" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="D88" s="2"/>
       <c r="G88" s="3"/>
@@ -4889,7 +4889,7 @@
         <f>IF($H88="","",S88-AB88)</f>
       </c>
     </row>
-    <row r="89" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="D89" s="2"/>
       <c r="G89" s="3"/>
@@ -4935,7 +4935,7 @@
         <f>IF($H89="","",S89-AB89)</f>
       </c>
     </row>
-    <row r="90" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="D90" s="2"/>
       <c r="G90" s="3"/>
@@ -4981,7 +4981,7 @@
         <f>IF($H90="","",S90-AB90)</f>
       </c>
     </row>
-    <row r="91" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="D91" s="2"/>
       <c r="G91" s="3"/>
@@ -5027,7 +5027,7 @@
         <f>IF($H91="","",S91-AB91)</f>
       </c>
     </row>
-    <row r="92" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="D92" s="2"/>
       <c r="G92" s="3"/>
@@ -5073,7 +5073,7 @@
         <f>IF($H92="","",S92-AB92)</f>
       </c>
     </row>
-    <row r="93" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="D93" s="2"/>
       <c r="G93" s="3"/>
@@ -5119,7 +5119,7 @@
         <f>IF($H93="","",S93-AB93)</f>
       </c>
     </row>
-    <row r="94" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="D94" s="2"/>
       <c r="G94" s="3"/>
@@ -5165,7 +5165,7 @@
         <f>IF($H94="","",S94-AB94)</f>
       </c>
     </row>
-    <row r="95" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="D95" s="2"/>
       <c r="G95" s="3"/>
@@ -5211,7 +5211,7 @@
         <f>IF($H95="","",S95-AB95)</f>
       </c>
     </row>
-    <row r="96" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="D96" s="2"/>
       <c r="G96" s="3"/>
@@ -5257,7 +5257,7 @@
         <f>IF($H96="","",S96-AB96)</f>
       </c>
     </row>
-    <row r="97" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="D97" s="2"/>
       <c r="G97" s="3"/>
@@ -5303,7 +5303,7 @@
         <f>IF($H97="","",S97-AB97)</f>
       </c>
     </row>
-    <row r="98" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="D98" s="2"/>
       <c r="G98" s="3"/>
@@ -5349,7 +5349,7 @@
         <f>IF($H98="","",S98-AB98)</f>
       </c>
     </row>
-    <row r="99" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="D99" s="2"/>
       <c r="G99" s="3"/>
@@ -5395,7 +5395,7 @@
         <f>IF($H99="","",S99-AB99)</f>
       </c>
     </row>
-    <row r="100" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
       <c r="D100" s="2"/>
       <c r="G100" s="3"/>
@@ -5441,7 +5441,7 @@
         <f>IF($H100="","",S100-AB100)</f>
       </c>
     </row>
-    <row r="101" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="D101" s="2"/>
       <c r="G101" s="3"/>
@@ -5487,7 +5487,7 @@
         <f>IF($H101="","",S101-AB101)</f>
       </c>
     </row>
-    <row r="102" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="D102" s="2"/>
       <c r="G102" s="3"/>
@@ -5533,7 +5533,7 @@
         <f>IF($H102="","",S102-AB102)</f>
       </c>
     </row>
-    <row r="103" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="D103" s="2"/>
       <c r="G103" s="3"/>
@@ -5579,7 +5579,7 @@
         <f>IF($H103="","",S103-AB103)</f>
       </c>
     </row>
-    <row r="104" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="D104" s="2"/>
       <c r="G104" s="3"/>
@@ -5625,7 +5625,7 @@
         <f>IF($H104="","",S104-AB104)</f>
       </c>
     </row>
-    <row r="105" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="D105" s="2"/>
       <c r="G105" s="3"/>
@@ -5671,7 +5671,7 @@
         <f>IF($H105="","",S105-AB105)</f>
       </c>
     </row>
-    <row r="106" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="D106" s="2"/>
       <c r="G106" s="3"/>
@@ -5717,7 +5717,7 @@
         <f>IF($H106="","",S106-AB106)</f>
       </c>
     </row>
-    <row r="107" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="D107" s="2"/>
       <c r="G107" s="3"/>
@@ -5763,7 +5763,7 @@
         <f>IF($H107="","",S107-AB107)</f>
       </c>
     </row>
-    <row r="108" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="D108" s="2"/>
       <c r="G108" s="3"/>
@@ -5809,7 +5809,7 @@
         <f>IF($H108="","",S108-AB108)</f>
       </c>
     </row>
-    <row r="109" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="D109" s="2"/>
       <c r="G109" s="3"/>
@@ -5855,7 +5855,7 @@
         <f>IF($H109="","",S109-AB109)</f>
       </c>
     </row>
-    <row r="110" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="D110" s="2"/>
       <c r="G110" s="3"/>
@@ -5901,7 +5901,7 @@
         <f>IF($H110="","",S110-AB110)</f>
       </c>
     </row>
-    <row r="111" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
       <c r="D111" s="2"/>
       <c r="G111" s="3"/>
@@ -5947,7 +5947,7 @@
         <f>IF($H111="","",S111-AB111)</f>
       </c>
     </row>
-    <row r="112" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="D112" s="2"/>
       <c r="G112" s="3"/>
@@ -5993,7 +5993,7 @@
         <f>IF($H112="","",S112-AB112)</f>
       </c>
     </row>
-    <row r="113" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="D113" s="2"/>
       <c r="G113" s="3"/>
@@ -6039,7 +6039,7 @@
         <f>IF($H113="","",S113-AB113)</f>
       </c>
     </row>
-    <row r="114" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="D114" s="2"/>
       <c r="G114" s="3"/>
@@ -6085,7 +6085,7 @@
         <f>IF($H114="","",S114-AB114)</f>
       </c>
     </row>
-    <row r="115" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="D115" s="2"/>
       <c r="G115" s="3"/>
@@ -6131,7 +6131,7 @@
         <f>IF($H115="","",S115-AB115)</f>
       </c>
     </row>
-    <row r="116" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="D116" s="2"/>
       <c r="G116" s="3"/>
@@ -6177,7 +6177,7 @@
         <f>IF($H116="","",S116-AB116)</f>
       </c>
     </row>
-    <row r="117" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="D117" s="2"/>
       <c r="G117" s="3"/>
@@ -6223,7 +6223,7 @@
         <f>IF($H117="","",S117-AB117)</f>
       </c>
     </row>
-    <row r="118" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="D118" s="2"/>
       <c r="G118" s="3"/>
@@ -6269,7 +6269,7 @@
         <f>IF($H118="","",S118-AB118)</f>
       </c>
     </row>
-    <row r="119" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="D119" s="2"/>
       <c r="G119" s="3"/>
@@ -6315,7 +6315,7 @@
         <f>IF($H119="","",S119-AB119)</f>
       </c>
     </row>
-    <row r="120" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="D120" s="2"/>
       <c r="G120" s="3"/>
@@ -6361,7 +6361,7 @@
         <f>IF($H120="","",S120-AB120)</f>
       </c>
     </row>
-    <row r="121" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="D121" s="2"/>
       <c r="G121" s="3"/>
@@ -6407,7 +6407,7 @@
         <f>IF($H121="","",S121-AB121)</f>
       </c>
     </row>
-    <row r="122" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="D122" s="2"/>
       <c r="G122" s="3"/>
@@ -6453,7 +6453,7 @@
         <f>IF($H122="","",S122-AB122)</f>
       </c>
     </row>
-    <row r="123" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="D123" s="2"/>
       <c r="G123" s="3"/>
@@ -6499,7 +6499,7 @@
         <f>IF($H123="","",S123-AB123)</f>
       </c>
     </row>
-    <row r="124" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="D124" s="2"/>
       <c r="G124" s="3"/>
@@ -6545,7 +6545,7 @@
         <f>IF($H124="","",S124-AB124)</f>
       </c>
     </row>
-    <row r="125" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="D125" s="2"/>
       <c r="G125" s="3"/>
@@ -6591,7 +6591,7 @@
         <f>IF($H125="","",S125-AB125)</f>
       </c>
     </row>
-    <row r="126" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="D126" s="2"/>
       <c r="G126" s="3"/>
@@ -6637,7 +6637,7 @@
         <f>IF($H126="","",S126-AB126)</f>
       </c>
     </row>
-    <row r="127" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="D127" s="2"/>
       <c r="G127" s="3"/>
@@ -6683,7 +6683,7 @@
         <f>IF($H127="","",S127-AB127)</f>
       </c>
     </row>
-    <row r="128" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A128" s="1"/>
       <c r="D128" s="2"/>
       <c r="G128" s="3"/>
@@ -6729,7 +6729,7 @@
         <f>IF($H128="","",S128-AB128)</f>
       </c>
     </row>
-    <row r="129" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A129" s="1"/>
       <c r="D129" s="2"/>
       <c r="G129" s="3"/>
@@ -6775,7 +6775,7 @@
         <f>IF($H129="","",S129-AB129)</f>
       </c>
     </row>
-    <row r="130" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A130" s="1"/>
       <c r="D130" s="2"/>
       <c r="G130" s="3"/>
@@ -6821,7 +6821,7 @@
         <f>IF($H130="","",S130-AB130)</f>
       </c>
     </row>
-    <row r="131" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A131" s="1"/>
       <c r="D131" s="2"/>
       <c r="G131" s="3"/>
@@ -6867,7 +6867,7 @@
         <f>IF($H131="","",S131-AB131)</f>
       </c>
     </row>
-    <row r="132" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A132" s="1"/>
       <c r="D132" s="2"/>
       <c r="G132" s="3"/>
@@ -6913,7 +6913,7 @@
         <f>IF($H132="","",S132-AB132)</f>
       </c>
     </row>
-    <row r="133" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
       <c r="D133" s="2"/>
       <c r="G133" s="3"/>
@@ -6959,7 +6959,7 @@
         <f>IF($H133="","",S133-AB133)</f>
       </c>
     </row>
-    <row r="134" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
       <c r="D134" s="2"/>
       <c r="G134" s="3"/>
@@ -7005,7 +7005,7 @@
         <f>IF($H134="","",S134-AB134)</f>
       </c>
     </row>
-    <row r="135" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A135" s="1"/>
       <c r="D135" s="2"/>
       <c r="G135" s="3"/>
@@ -7051,7 +7051,7 @@
         <f>IF($H135="","",S135-AB135)</f>
       </c>
     </row>
-    <row r="136" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A136" s="1"/>
       <c r="D136" s="2"/>
       <c r="G136" s="3"/>
@@ -7097,7 +7097,7 @@
         <f>IF($H136="","",S136-AB136)</f>
       </c>
     </row>
-    <row r="137" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A137" s="1"/>
       <c r="D137" s="2"/>
       <c r="G137" s="3"/>
@@ -7143,7 +7143,7 @@
         <f>IF($H137="","",S137-AB137)</f>
       </c>
     </row>
-    <row r="138" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A138" s="1"/>
       <c r="D138" s="2"/>
       <c r="G138" s="3"/>
@@ -7189,7 +7189,7 @@
         <f>IF($H138="","",S138-AB138)</f>
       </c>
     </row>
-    <row r="139" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A139" s="1"/>
       <c r="D139" s="2"/>
       <c r="G139" s="3"/>
@@ -7235,7 +7235,7 @@
         <f>IF($H139="","",S139-AB139)</f>
       </c>
     </row>
-    <row r="140" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A140" s="1"/>
       <c r="D140" s="2"/>
       <c r="G140" s="3"/>
@@ -7281,7 +7281,7 @@
         <f>IF($H140="","",S140-AB140)</f>
       </c>
     </row>
-    <row r="141" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="D141" s="2"/>
       <c r="G141" s="3"/>
@@ -7327,7 +7327,7 @@
         <f>IF($H141="","",S141-AB141)</f>
       </c>
     </row>
-    <row r="142" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A142" s="1"/>
       <c r="D142" s="2"/>
       <c r="G142" s="3"/>
@@ -7373,7 +7373,7 @@
         <f>IF($H142="","",S142-AB142)</f>
       </c>
     </row>
-    <row r="143" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="D143" s="2"/>
       <c r="G143" s="3"/>
@@ -7419,7 +7419,7 @@
         <f>IF($H143="","",S143-AB143)</f>
       </c>
     </row>
-    <row r="144" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="D144" s="2"/>
       <c r="G144" s="3"/>
@@ -7465,7 +7465,7 @@
         <f>IF($H144="","",S144-AB144)</f>
       </c>
     </row>
-    <row r="145" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A145" s="1"/>
       <c r="D145" s="2"/>
       <c r="G145" s="3"/>
@@ -7511,7 +7511,7 @@
         <f>IF($H145="","",S145-AB145)</f>
       </c>
     </row>
-    <row r="146" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
       <c r="D146" s="2"/>
       <c r="G146" s="3"/>
@@ -7557,7 +7557,7 @@
         <f>IF($H146="","",S146-AB146)</f>
       </c>
     </row>
-    <row r="147" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A147" s="1"/>
       <c r="D147" s="2"/>
       <c r="G147" s="3"/>
@@ -7603,7 +7603,7 @@
         <f>IF($H147="","",S147-AB147)</f>
       </c>
     </row>
-    <row r="148" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A148" s="1"/>
       <c r="D148" s="2"/>
       <c r="G148" s="3"/>
@@ -7649,7 +7649,7 @@
         <f>IF($H148="","",S148-AB148)</f>
       </c>
     </row>
-    <row r="149" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
       <c r="D149" s="2"/>
       <c r="G149" s="3"/>
@@ -7695,7 +7695,7 @@
         <f>IF($H149="","",S149-AB149)</f>
       </c>
     </row>
-    <row r="150" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A150" s="1"/>
       <c r="D150" s="2"/>
       <c r="G150" s="3"/>
@@ -7741,7 +7741,7 @@
         <f>IF($H150="","",S150-AB150)</f>
       </c>
     </row>
-    <row r="151" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
       <c r="D151" s="2"/>
       <c r="G151" s="3"/>
@@ -7787,7 +7787,7 @@
         <f>IF($H151="","",S151-AB151)</f>
       </c>
     </row>
-    <row r="152" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A152" s="1"/>
       <c r="D152" s="2"/>
       <c r="G152" s="3"/>
@@ -7833,7 +7833,7 @@
         <f>IF($H152="","",S152-AB152)</f>
       </c>
     </row>
-    <row r="153" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
       <c r="D153" s="2"/>
       <c r="G153" s="3"/>
@@ -7879,7 +7879,7 @@
         <f>IF($H153="","",S153-AB153)</f>
       </c>
     </row>
-    <row r="154" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
       <c r="D154" s="2"/>
       <c r="G154" s="3"/>
@@ -7925,7 +7925,7 @@
         <f>IF($H154="","",S154-AB154)</f>
       </c>
     </row>
-    <row r="155" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A155" s="1"/>
       <c r="D155" s="2"/>
       <c r="G155" s="3"/>
@@ -7971,7 +7971,7 @@
         <f>IF($H155="","",S155-AB155)</f>
       </c>
     </row>
-    <row r="156" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A156" s="1"/>
       <c r="D156" s="2"/>
       <c r="G156" s="3"/>
@@ -8017,7 +8017,7 @@
         <f>IF($H156="","",S156-AB156)</f>
       </c>
     </row>
-    <row r="157" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A157" s="1"/>
       <c r="D157" s="2"/>
       <c r="G157" s="3"/>
@@ -8063,7 +8063,7 @@
         <f>IF($H157="","",S157-AB157)</f>
       </c>
     </row>
-    <row r="158" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A158" s="1"/>
       <c r="D158" s="2"/>
       <c r="G158" s="3"/>
@@ -8109,7 +8109,7 @@
         <f>IF($H158="","",S158-AB158)</f>
       </c>
     </row>
-    <row r="159" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A159" s="1"/>
       <c r="D159" s="2"/>
       <c r="G159" s="3"/>
@@ -8155,7 +8155,7 @@
         <f>IF($H159="","",S159-AB159)</f>
       </c>
     </row>
-    <row r="160" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A160" s="1"/>
       <c r="D160" s="2"/>
       <c r="G160" s="3"/>
@@ -8201,7 +8201,7 @@
         <f>IF($H160="","",S160-AB160)</f>
       </c>
     </row>
-    <row r="161" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A161" s="1"/>
       <c r="D161" s="2"/>
       <c r="G161" s="3"/>
@@ -8247,7 +8247,7 @@
         <f>IF($H161="","",S161-AB161)</f>
       </c>
     </row>
-    <row r="162" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A162" s="1"/>
       <c r="D162" s="2"/>
       <c r="G162" s="3"/>
@@ -8293,7 +8293,7 @@
         <f>IF($H162="","",S162-AB162)</f>
       </c>
     </row>
-    <row r="163" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A163" s="1"/>
       <c r="D163" s="2"/>
       <c r="G163" s="3"/>
@@ -8339,7 +8339,7 @@
         <f>IF($H163="","",S163-AB163)</f>
       </c>
     </row>
-    <row r="164" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A164" s="1"/>
       <c r="D164" s="2"/>
       <c r="G164" s="3"/>
@@ -8385,7 +8385,7 @@
         <f>IF($H164="","",S164-AB164)</f>
       </c>
     </row>
-    <row r="165" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A165" s="1"/>
       <c r="D165" s="2"/>
       <c r="G165" s="3"/>
@@ -8431,7 +8431,7 @@
         <f>IF($H165="","",S165-AB165)</f>
       </c>
     </row>
-    <row r="166" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A166" s="1"/>
       <c r="D166" s="2"/>
       <c r="G166" s="3"/>
@@ -8477,7 +8477,7 @@
         <f>IF($H166="","",S166-AB166)</f>
       </c>
     </row>
-    <row r="167" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A167" s="1"/>
       <c r="D167" s="2"/>
       <c r="G167" s="3"/>
@@ -8523,7 +8523,7 @@
         <f>IF($H167="","",S167-AB167)</f>
       </c>
     </row>
-    <row r="168" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A168" s="1"/>
       <c r="D168" s="2"/>
       <c r="G168" s="3"/>
@@ -8569,7 +8569,7 @@
         <f>IF($H168="","",S168-AB168)</f>
       </c>
     </row>
-    <row r="169" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A169" s="1"/>
       <c r="D169" s="2"/>
       <c r="G169" s="3"/>
@@ -8615,7 +8615,7 @@
         <f>IF($H169="","",S169-AB169)</f>
       </c>
     </row>
-    <row r="170" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A170" s="1"/>
       <c r="D170" s="2"/>
       <c r="G170" s="3"/>
@@ -8661,7 +8661,7 @@
         <f>IF($H170="","",S170-AB170)</f>
       </c>
     </row>
-    <row r="171" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A171" s="1"/>
       <c r="D171" s="2"/>
       <c r="G171" s="3"/>
@@ -8707,7 +8707,7 @@
         <f>IF($H171="","",S171-AB171)</f>
       </c>
     </row>
-    <row r="172" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A172" s="1"/>
       <c r="D172" s="2"/>
       <c r="G172" s="3"/>
@@ -8753,7 +8753,7 @@
         <f>IF($H172="","",S172-AB172)</f>
       </c>
     </row>
-    <row r="173" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A173" s="1"/>
       <c r="D173" s="2"/>
       <c r="G173" s="3"/>
@@ -8799,7 +8799,7 @@
         <f>IF($H173="","",S173-AB173)</f>
       </c>
     </row>
-    <row r="174" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A174" s="1"/>
       <c r="D174" s="2"/>
       <c r="G174" s="3"/>
@@ -8845,7 +8845,7 @@
         <f>IF($H174="","",S174-AB174)</f>
       </c>
     </row>
-    <row r="175" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A175" s="1"/>
       <c r="D175" s="2"/>
       <c r="G175" s="3"/>
@@ -8891,7 +8891,7 @@
         <f>IF($H175="","",S175-AB175)</f>
       </c>
     </row>
-    <row r="176" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A176" s="1"/>
       <c r="D176" s="2"/>
       <c r="G176" s="3"/>
@@ -8937,7 +8937,7 @@
         <f>IF($H176="","",S176-AB176)</f>
       </c>
     </row>
-    <row r="177" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A177" s="1"/>
       <c r="D177" s="2"/>
       <c r="G177" s="3"/>
@@ -8983,7 +8983,7 @@
         <f>IF($H177="","",S177-AB177)</f>
       </c>
     </row>
-    <row r="178" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A178" s="1"/>
       <c r="D178" s="2"/>
       <c r="G178" s="3"/>
@@ -9029,7 +9029,7 @@
         <f>IF($H178="","",S178-AB178)</f>
       </c>
     </row>
-    <row r="179" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A179" s="1"/>
       <c r="D179" s="2"/>
       <c r="G179" s="3"/>
@@ -9075,7 +9075,7 @@
         <f>IF($H179="","",S179-AB179)</f>
       </c>
     </row>
-    <row r="180" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A180" s="1"/>
       <c r="D180" s="2"/>
       <c r="G180" s="3"/>
@@ -9121,7 +9121,7 @@
         <f>IF($H180="","",S180-AB180)</f>
       </c>
     </row>
-    <row r="181" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A181" s="1"/>
       <c r="D181" s="2"/>
       <c r="G181" s="3"/>
@@ -9167,7 +9167,7 @@
         <f>IF($H181="","",S181-AB181)</f>
       </c>
     </row>
-    <row r="182" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A182" s="1"/>
       <c r="D182" s="2"/>
       <c r="G182" s="3"/>
@@ -9213,7 +9213,7 @@
         <f>IF($H182="","",S182-AB182)</f>
       </c>
     </row>
-    <row r="183" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A183" s="1"/>
       <c r="D183" s="2"/>
       <c r="G183" s="3"/>
@@ -9259,7 +9259,7 @@
         <f>IF($H183="","",S183-AB183)</f>
       </c>
     </row>
-    <row r="184" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A184" s="1"/>
       <c r="D184" s="2"/>
       <c r="G184" s="3"/>
@@ -9305,7 +9305,7 @@
         <f>IF($H184="","",S184-AB184)</f>
       </c>
     </row>
-    <row r="185" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A185" s="1"/>
       <c r="D185" s="2"/>
       <c r="G185" s="3"/>
@@ -9351,7 +9351,7 @@
         <f>IF($H185="","",S185-AB185)</f>
       </c>
     </row>
-    <row r="186" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A186" s="1"/>
       <c r="D186" s="2"/>
       <c r="G186" s="3"/>
@@ -9397,7 +9397,7 @@
         <f>IF($H186="","",S186-AB186)</f>
       </c>
     </row>
-    <row r="187" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A187" s="1"/>
       <c r="D187" s="2"/>
       <c r="G187" s="3"/>
@@ -9443,7 +9443,7 @@
         <f>IF($H187="","",S187-AB187)</f>
       </c>
     </row>
-    <row r="188" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A188" s="1"/>
       <c r="D188" s="2"/>
       <c r="G188" s="3"/>
@@ -9489,7 +9489,7 @@
         <f>IF($H188="","",S188-AB188)</f>
       </c>
     </row>
-    <row r="189" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A189" s="1"/>
       <c r="D189" s="2"/>
       <c r="G189" s="3"/>
@@ -9535,7 +9535,7 @@
         <f>IF($H189="","",S189-AB189)</f>
       </c>
     </row>
-    <row r="190" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A190" s="1"/>
       <c r="D190" s="2"/>
       <c r="G190" s="3"/>
@@ -9581,7 +9581,7 @@
         <f>IF($H190="","",S190-AB190)</f>
       </c>
     </row>
-    <row r="191" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A191" s="1"/>
       <c r="D191" s="2"/>
       <c r="G191" s="3"/>
@@ -9627,7 +9627,7 @@
         <f>IF($H191="","",S191-AB191)</f>
       </c>
     </row>
-    <row r="192" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A192" s="1"/>
       <c r="D192" s="2"/>
       <c r="G192" s="3"/>
@@ -9673,7 +9673,7 @@
         <f>IF($H192="","",S192-AB192)</f>
       </c>
     </row>
-    <row r="193" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A193" s="1"/>
       <c r="D193" s="2"/>
       <c r="G193" s="3"/>
@@ -9719,7 +9719,7 @@
         <f>IF($H193="","",S193-AB193)</f>
       </c>
     </row>
-    <row r="194" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A194" s="1"/>
       <c r="D194" s="2"/>
       <c r="G194" s="3"/>
@@ -9765,7 +9765,7 @@
         <f>IF($H194="","",S194-AB194)</f>
       </c>
     </row>
-    <row r="195" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A195" s="1"/>
       <c r="D195" s="2"/>
       <c r="G195" s="3"/>
@@ -9811,7 +9811,7 @@
         <f>IF($H195="","",S195-AB195)</f>
       </c>
     </row>
-    <row r="196" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A196" s="1"/>
       <c r="D196" s="2"/>
       <c r="G196" s="3"/>
@@ -9857,7 +9857,7 @@
         <f>IF($H196="","",S196-AB196)</f>
       </c>
     </row>
-    <row r="197" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A197" s="1"/>
       <c r="D197" s="2"/>
       <c r="G197" s="3"/>
@@ -9903,7 +9903,7 @@
         <f>IF($H197="","",S197-AB197)</f>
       </c>
     </row>
-    <row r="198" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A198" s="1"/>
       <c r="D198" s="2"/>
       <c r="G198" s="3"/>
@@ -9949,7 +9949,7 @@
         <f>IF($H198="","",S198-AB198)</f>
       </c>
     </row>
-    <row r="199" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A199" s="1"/>
       <c r="D199" s="2"/>
       <c r="G199" s="3"/>
@@ -9995,7 +9995,7 @@
         <f>IF($H199="","",S199-AB199)</f>
       </c>
     </row>
-    <row r="200" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A200" s="1"/>
       <c r="D200" s="2"/>
       <c r="G200" s="3"/>
@@ -10041,7 +10041,7 @@
         <f>IF($H200="","",S200-AB200)</f>
       </c>
     </row>
-    <row r="201" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A201" s="1"/>
       <c r="D201" s="2"/>
       <c r="G201" s="3"/>
@@ -10087,7 +10087,7 @@
         <f>IF($H201="","",S201-AB201)</f>
       </c>
     </row>
-    <row r="202" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A202" s="1"/>
       <c r="D202" s="2"/>
       <c r="G202" s="3"/>
@@ -10327,13 +10327,13 @@
         <v>329</v>
       </c>
       <c r="I2" s="3">
-        <f>IF($H2="","",H2-G2)</f>
+        <f>H2-G2</f>
       </c>
       <c r="J2" s="3">
-        <f>IF($H2="","",I2*16.67%)</f>
+        <f>I2*16.67%</f>
       </c>
       <c r="K2" s="3">
-        <f>IF($H2="","",H2/100*11)</f>
+        <f>H2/100*11</f>
       </c>
       <c r="L2" s="3">
         <v>8.99</v>
@@ -10342,19 +10342,19 @@
         <v>8</v>
       </c>
       <c r="N2" s="3">
-        <f>IF($H2="","",M2*20%)</f>
+        <f>M2*20%</f>
       </c>
       <c r="O2" s="3">
         <v>1</v>
       </c>
       <c r="P2" s="3">
-        <f>IF($H2="","",I2-J2-K2-L2-M2-N2-O2)</f>
+        <f>I2-J2-K2-L2-M2-N2-O2</f>
       </c>
       <c r="Q2" s="3">
-        <f>IF($H2="","",(P2-Y2)/G2*100)</f>
+        <f>(P2-Y2)/G2*100</f>
       </c>
       <c r="R2" s="3">
-        <f>IF($H2="","",J2-N2)</f>
+        <f>J2-N2</f>
       </c>
       <c r="S2" t="s">
         <v>35</v>
@@ -10363,7 +10363,7 @@
         <v>40</v>
       </c>
       <c r="Z2" s="3">
-        <f>IF($H2="","",P2-Y2)</f>
+        <f>P2-Y2</f>
       </c>
       <c r="AA2" t="s">
         <v>35</v>
@@ -10372,7 +10372,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="D3" s="2"/>
       <c r="G3" s="3"/>
@@ -10409,7 +10409,7 @@
         <f>IF($H3="","",P3-Y3)</f>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="D4" s="2"/>
       <c r="G4" s="3"/>
@@ -10446,7 +10446,7 @@
         <f>IF($H4="","",P4-Y4)</f>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="D5" s="2"/>
       <c r="G5" s="3"/>
@@ -10483,7 +10483,7 @@
         <f>IF($H5="","",P5-Y5)</f>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="D6" s="2"/>
       <c r="G6" s="3"/>
@@ -10520,7 +10520,7 @@
         <f>IF($H6="","",P6-Y6)</f>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="D7" s="2"/>
       <c r="G7" s="3"/>
@@ -10557,7 +10557,7 @@
         <f>IF($H7="","",P7-Y7)</f>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="D8" s="2"/>
       <c r="G8" s="3"/>
@@ -10594,7 +10594,7 @@
         <f>IF($H8="","",P8-Y8)</f>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="D9" s="2"/>
       <c r="G9" s="3"/>
@@ -10631,7 +10631,7 @@
         <f>IF($H9="","",P9-Y9)</f>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="D10" s="2"/>
       <c r="G10" s="3"/>
@@ -10668,7 +10668,7 @@
         <f>IF($H10="","",P10-Y10)</f>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="D11" s="2"/>
       <c r="G11" s="3"/>
@@ -10705,7 +10705,7 @@
         <f>IF($H11="","",P11-Y11)</f>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="D12" s="2"/>
       <c r="G12" s="3"/>
@@ -10742,7 +10742,7 @@
         <f>IF($H12="","",P12-Y12)</f>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="D13" s="2"/>
       <c r="G13" s="3"/>
@@ -10779,7 +10779,7 @@
         <f>IF($H13="","",P13-Y13)</f>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="D14" s="2"/>
       <c r="G14" s="3"/>
@@ -10816,7 +10816,7 @@
         <f>IF($H14="","",P14-Y14)</f>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="D15" s="2"/>
       <c r="G15" s="3"/>
@@ -10853,7 +10853,7 @@
         <f>IF($H15="","",P15-Y15)</f>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="D16" s="2"/>
       <c r="G16" s="3"/>
@@ -10890,7 +10890,7 @@
         <f>IF($H16="","",P16-Y16)</f>
       </c>
     </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="D17" s="2"/>
       <c r="G17" s="3"/>
@@ -10927,7 +10927,7 @@
         <f>IF($H17="","",P17-Y17)</f>
       </c>
     </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="D18" s="2"/>
       <c r="G18" s="3"/>
@@ -10964,7 +10964,7 @@
         <f>IF($H18="","",P18-Y18)</f>
       </c>
     </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="D19" s="2"/>
       <c r="G19" s="3"/>
@@ -11001,7 +11001,7 @@
         <f>IF($H19="","",P19-Y19)</f>
       </c>
     </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="D20" s="2"/>
       <c r="G20" s="3"/>
@@ -11038,7 +11038,7 @@
         <f>IF($H20="","",P20-Y20)</f>
       </c>
     </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="D21" s="2"/>
       <c r="G21" s="3"/>
@@ -11075,7 +11075,7 @@
         <f>IF($H21="","",P21-Y21)</f>
       </c>
     </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="D22" s="2"/>
       <c r="G22" s="3"/>
@@ -11112,7 +11112,7 @@
         <f>IF($H22="","",P22-Y22)</f>
       </c>
     </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="D23" s="2"/>
       <c r="G23" s="3"/>
@@ -11149,7 +11149,7 @@
         <f>IF($H23="","",P23-Y23)</f>
       </c>
     </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="D24" s="2"/>
       <c r="G24" s="3"/>
@@ -11186,7 +11186,7 @@
         <f>IF($H24="","",P24-Y24)</f>
       </c>
     </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="D25" s="2"/>
       <c r="G25" s="3"/>
@@ -11223,7 +11223,7 @@
         <f>IF($H25="","",P25-Y25)</f>
       </c>
     </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="D26" s="2"/>
       <c r="G26" s="3"/>
@@ -11260,7 +11260,7 @@
         <f>IF($H26="","",P26-Y26)</f>
       </c>
     </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="D27" s="2"/>
       <c r="G27" s="3"/>
@@ -11297,7 +11297,7 @@
         <f>IF($H27="","",P27-Y27)</f>
       </c>
     </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="D28" s="2"/>
       <c r="G28" s="3"/>
@@ -11334,7 +11334,7 @@
         <f>IF($H28="","",P28-Y28)</f>
       </c>
     </row>
-    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="D29" s="2"/>
       <c r="G29" s="3"/>
@@ -11371,7 +11371,7 @@
         <f>IF($H29="","",P29-Y29)</f>
       </c>
     </row>
-    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="D30" s="2"/>
       <c r="G30" s="3"/>
@@ -11408,7 +11408,7 @@
         <f>IF($H30="","",P30-Y30)</f>
       </c>
     </row>
-    <row r="31" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="D31" s="2"/>
       <c r="G31" s="3"/>
@@ -11445,7 +11445,7 @@
         <f>IF($H31="","",P31-Y31)</f>
       </c>
     </row>
-    <row r="32" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="D32" s="2"/>
       <c r="G32" s="3"/>
@@ -11482,7 +11482,7 @@
         <f>IF($H32="","",P32-Y32)</f>
       </c>
     </row>
-    <row r="33" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="D33" s="2"/>
       <c r="G33" s="3"/>
@@ -11519,7 +11519,7 @@
         <f>IF($H33="","",P33-Y33)</f>
       </c>
     </row>
-    <row r="34" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="D34" s="2"/>
       <c r="G34" s="3"/>
@@ -11556,7 +11556,7 @@
         <f>IF($H34="","",P34-Y34)</f>
       </c>
     </row>
-    <row r="35" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="D35" s="2"/>
       <c r="G35" s="3"/>
@@ -11593,7 +11593,7 @@
         <f>IF($H35="","",P35-Y35)</f>
       </c>
     </row>
-    <row r="36" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="D36" s="2"/>
       <c r="G36" s="3"/>
@@ -11630,7 +11630,7 @@
         <f>IF($H36="","",P36-Y36)</f>
       </c>
     </row>
-    <row r="37" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="D37" s="2"/>
       <c r="G37" s="3"/>
@@ -11667,7 +11667,7 @@
         <f>IF($H37="","",P37-Y37)</f>
       </c>
     </row>
-    <row r="38" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="D38" s="2"/>
       <c r="G38" s="3"/>
@@ -11704,7 +11704,7 @@
         <f>IF($H38="","",P38-Y38)</f>
       </c>
     </row>
-    <row r="39" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="D39" s="2"/>
       <c r="G39" s="3"/>
@@ -11741,7 +11741,7 @@
         <f>IF($H39="","",P39-Y39)</f>
       </c>
     </row>
-    <row r="40" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="D40" s="2"/>
       <c r="G40" s="3"/>
@@ -11778,7 +11778,7 @@
         <f>IF($H40="","",P40-Y40)</f>
       </c>
     </row>
-    <row r="41" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="D41" s="2"/>
       <c r="G41" s="3"/>
@@ -11815,7 +11815,7 @@
         <f>IF($H41="","",P41-Y41)</f>
       </c>
     </row>
-    <row r="42" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="D42" s="2"/>
       <c r="G42" s="3"/>
@@ -11852,7 +11852,7 @@
         <f>IF($H42="","",P42-Y42)</f>
       </c>
     </row>
-    <row r="43" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="D43" s="2"/>
       <c r="G43" s="3"/>
@@ -11889,7 +11889,7 @@
         <f>IF($H43="","",P43-Y43)</f>
       </c>
     </row>
-    <row r="44" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="D44" s="2"/>
       <c r="G44" s="3"/>
@@ -11926,7 +11926,7 @@
         <f>IF($H44="","",P44-Y44)</f>
       </c>
     </row>
-    <row r="45" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="D45" s="2"/>
       <c r="G45" s="3"/>
@@ -11963,7 +11963,7 @@
         <f>IF($H45="","",P45-Y45)</f>
       </c>
     </row>
-    <row r="46" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="D46" s="2"/>
       <c r="G46" s="3"/>
@@ -12000,7 +12000,7 @@
         <f>IF($H46="","",P46-Y46)</f>
       </c>
     </row>
-    <row r="47" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="D47" s="2"/>
       <c r="G47" s="3"/>
@@ -12037,7 +12037,7 @@
         <f>IF($H47="","",P47-Y47)</f>
       </c>
     </row>
-    <row r="48" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="D48" s="2"/>
       <c r="G48" s="3"/>
@@ -12074,7 +12074,7 @@
         <f>IF($H48="","",P48-Y48)</f>
       </c>
     </row>
-    <row r="49" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
       <c r="D49" s="2"/>
       <c r="G49" s="3"/>
@@ -12111,7 +12111,7 @@
         <f>IF($H49="","",P49-Y49)</f>
       </c>
     </row>
-    <row r="50" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
       <c r="D50" s="2"/>
       <c r="G50" s="3"/>
@@ -12148,7 +12148,7 @@
         <f>IF($H50="","",P50-Y50)</f>
       </c>
     </row>
-    <row r="51" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
       <c r="D51" s="2"/>
       <c r="G51" s="3"/>
@@ -12185,7 +12185,7 @@
         <f>IF($H51="","",P51-Y51)</f>
       </c>
     </row>
-    <row r="52" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
       <c r="D52" s="2"/>
       <c r="G52" s="3"/>
@@ -12222,7 +12222,7 @@
         <f>IF($H52="","",P52-Y52)</f>
       </c>
     </row>
-    <row r="53" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
       <c r="D53" s="2"/>
       <c r="G53" s="3"/>
@@ -12259,7 +12259,7 @@
         <f>IF($H53="","",P53-Y53)</f>
       </c>
     </row>
-    <row r="54" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
       <c r="D54" s="2"/>
       <c r="G54" s="3"/>
@@ -12296,7 +12296,7 @@
         <f>IF($H54="","",P54-Y54)</f>
       </c>
     </row>
-    <row r="55" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
       <c r="D55" s="2"/>
       <c r="G55" s="3"/>
@@ -12333,7 +12333,7 @@
         <f>IF($H55="","",P55-Y55)</f>
       </c>
     </row>
-    <row r="56" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
       <c r="D56" s="2"/>
       <c r="G56" s="3"/>
@@ -12370,7 +12370,7 @@
         <f>IF($H56="","",P56-Y56)</f>
       </c>
     </row>
-    <row r="57" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
       <c r="D57" s="2"/>
       <c r="G57" s="3"/>
@@ -12407,7 +12407,7 @@
         <f>IF($H57="","",P57-Y57)</f>
       </c>
     </row>
-    <row r="58" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
       <c r="D58" s="2"/>
       <c r="G58" s="3"/>
@@ -12444,7 +12444,7 @@
         <f>IF($H58="","",P58-Y58)</f>
       </c>
     </row>
-    <row r="59" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
       <c r="D59" s="2"/>
       <c r="G59" s="3"/>
@@ -12481,7 +12481,7 @@
         <f>IF($H59="","",P59-Y59)</f>
       </c>
     </row>
-    <row r="60" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
       <c r="D60" s="2"/>
       <c r="G60" s="3"/>
@@ -12518,7 +12518,7 @@
         <f>IF($H60="","",P60-Y60)</f>
       </c>
     </row>
-    <row r="61" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
       <c r="D61" s="2"/>
       <c r="G61" s="3"/>
@@ -12555,7 +12555,7 @@
         <f>IF($H61="","",P61-Y61)</f>
       </c>
     </row>
-    <row r="62" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
       <c r="D62" s="2"/>
       <c r="G62" s="3"/>
@@ -12592,7 +12592,7 @@
         <f>IF($H62="","",P62-Y62)</f>
       </c>
     </row>
-    <row r="63" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
       <c r="D63" s="2"/>
       <c r="G63" s="3"/>
@@ -12629,7 +12629,7 @@
         <f>IF($H63="","",P63-Y63)</f>
       </c>
     </row>
-    <row r="64" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
       <c r="D64" s="2"/>
       <c r="G64" s="3"/>
@@ -12666,7 +12666,7 @@
         <f>IF($H64="","",P64-Y64)</f>
       </c>
     </row>
-    <row r="65" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
       <c r="D65" s="2"/>
       <c r="G65" s="3"/>
@@ -12703,7 +12703,7 @@
         <f>IF($H65="","",P65-Y65)</f>
       </c>
     </row>
-    <row r="66" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
       <c r="D66" s="2"/>
       <c r="G66" s="3"/>
@@ -12740,7 +12740,7 @@
         <f>IF($H66="","",P66-Y66)</f>
       </c>
     </row>
-    <row r="67" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
       <c r="D67" s="2"/>
       <c r="G67" s="3"/>
@@ -12777,7 +12777,7 @@
         <f>IF($H67="","",P67-Y67)</f>
       </c>
     </row>
-    <row r="68" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
       <c r="D68" s="2"/>
       <c r="G68" s="3"/>
@@ -12814,7 +12814,7 @@
         <f>IF($H68="","",P68-Y68)</f>
       </c>
     </row>
-    <row r="69" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
       <c r="D69" s="2"/>
       <c r="G69" s="3"/>
@@ -12851,7 +12851,7 @@
         <f>IF($H69="","",P69-Y69)</f>
       </c>
     </row>
-    <row r="70" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
       <c r="D70" s="2"/>
       <c r="G70" s="3"/>
@@ -12888,7 +12888,7 @@
         <f>IF($H70="","",P70-Y70)</f>
       </c>
     </row>
-    <row r="71" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
       <c r="D71" s="2"/>
       <c r="G71" s="3"/>
@@ -12925,7 +12925,7 @@
         <f>IF($H71="","",P71-Y71)</f>
       </c>
     </row>
-    <row r="72" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
       <c r="D72" s="2"/>
       <c r="G72" s="3"/>
@@ -12962,7 +12962,7 @@
         <f>IF($H72="","",P72-Y72)</f>
       </c>
     </row>
-    <row r="73" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
       <c r="D73" s="2"/>
       <c r="G73" s="3"/>
@@ -12999,7 +12999,7 @@
         <f>IF($H73="","",P73-Y73)</f>
       </c>
     </row>
-    <row r="74" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
       <c r="D74" s="2"/>
       <c r="G74" s="3"/>
@@ -13036,7 +13036,7 @@
         <f>IF($H74="","",P74-Y74)</f>
       </c>
     </row>
-    <row r="75" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
       <c r="D75" s="2"/>
       <c r="G75" s="3"/>
@@ -13073,7 +13073,7 @@
         <f>IF($H75="","",P75-Y75)</f>
       </c>
     </row>
-    <row r="76" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
       <c r="D76" s="2"/>
       <c r="G76" s="3"/>
@@ -13110,7 +13110,7 @@
         <f>IF($H76="","",P76-Y76)</f>
       </c>
     </row>
-    <row r="77" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
       <c r="D77" s="2"/>
       <c r="G77" s="3"/>
@@ -13147,7 +13147,7 @@
         <f>IF($H77="","",P77-Y77)</f>
       </c>
     </row>
-    <row r="78" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
       <c r="D78" s="2"/>
       <c r="G78" s="3"/>
@@ -13184,7 +13184,7 @@
         <f>IF($H78="","",P78-Y78)</f>
       </c>
     </row>
-    <row r="79" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="D79" s="2"/>
       <c r="G79" s="3"/>
@@ -13221,7 +13221,7 @@
         <f>IF($H79="","",P79-Y79)</f>
       </c>
     </row>
-    <row r="80" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
       <c r="D80" s="2"/>
       <c r="G80" s="3"/>
@@ -13258,7 +13258,7 @@
         <f>IF($H80="","",P80-Y80)</f>
       </c>
     </row>
-    <row r="81" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
       <c r="D81" s="2"/>
       <c r="G81" s="3"/>
@@ -13295,7 +13295,7 @@
         <f>IF($H81="","",P81-Y81)</f>
       </c>
     </row>
-    <row r="82" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
       <c r="D82" s="2"/>
       <c r="G82" s="3"/>
@@ -13332,7 +13332,7 @@
         <f>IF($H82="","",P82-Y82)</f>
       </c>
     </row>
-    <row r="83" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
       <c r="D83" s="2"/>
       <c r="G83" s="3"/>
@@ -13369,7 +13369,7 @@
         <f>IF($H83="","",P83-Y83)</f>
       </c>
     </row>
-    <row r="84" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
       <c r="D84" s="2"/>
       <c r="G84" s="3"/>
@@ -13406,7 +13406,7 @@
         <f>IF($H84="","",P84-Y84)</f>
       </c>
     </row>
-    <row r="85" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="D85" s="2"/>
       <c r="G85" s="3"/>
@@ -13443,7 +13443,7 @@
         <f>IF($H85="","",P85-Y85)</f>
       </c>
     </row>
-    <row r="86" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="D86" s="2"/>
       <c r="G86" s="3"/>
@@ -13480,7 +13480,7 @@
         <f>IF($H86="","",P86-Y86)</f>
       </c>
     </row>
-    <row r="87" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="D87" s="2"/>
       <c r="G87" s="3"/>
@@ -13517,7 +13517,7 @@
         <f>IF($H87="","",P87-Y87)</f>
       </c>
     </row>
-    <row r="88" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="D88" s="2"/>
       <c r="G88" s="3"/>
@@ -13554,7 +13554,7 @@
         <f>IF($H88="","",P88-Y88)</f>
       </c>
     </row>
-    <row r="89" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="D89" s="2"/>
       <c r="G89" s="3"/>
@@ -13591,7 +13591,7 @@
         <f>IF($H89="","",P89-Y89)</f>
       </c>
     </row>
-    <row r="90" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="D90" s="2"/>
       <c r="G90" s="3"/>
@@ -13628,7 +13628,7 @@
         <f>IF($H90="","",P90-Y90)</f>
       </c>
     </row>
-    <row r="91" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="D91" s="2"/>
       <c r="G91" s="3"/>
@@ -13665,7 +13665,7 @@
         <f>IF($H91="","",P91-Y91)</f>
       </c>
     </row>
-    <row r="92" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="D92" s="2"/>
       <c r="G92" s="3"/>
@@ -13702,7 +13702,7 @@
         <f>IF($H92="","",P92-Y92)</f>
       </c>
     </row>
-    <row r="93" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="D93" s="2"/>
       <c r="G93" s="3"/>
@@ -13739,7 +13739,7 @@
         <f>IF($H93="","",P93-Y93)</f>
       </c>
     </row>
-    <row r="94" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="D94" s="2"/>
       <c r="G94" s="3"/>
@@ -13776,7 +13776,7 @@
         <f>IF($H94="","",P94-Y94)</f>
       </c>
     </row>
-    <row r="95" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="D95" s="2"/>
       <c r="G95" s="3"/>
@@ -13813,7 +13813,7 @@
         <f>IF($H95="","",P95-Y95)</f>
       </c>
     </row>
-    <row r="96" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="D96" s="2"/>
       <c r="G96" s="3"/>
@@ -13850,7 +13850,7 @@
         <f>IF($H96="","",P96-Y96)</f>
       </c>
     </row>
-    <row r="97" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="D97" s="2"/>
       <c r="G97" s="3"/>
@@ -13887,7 +13887,7 @@
         <f>IF($H97="","",P97-Y97)</f>
       </c>
     </row>
-    <row r="98" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="D98" s="2"/>
       <c r="G98" s="3"/>
@@ -13924,7 +13924,7 @@
         <f>IF($H98="","",P98-Y98)</f>
       </c>
     </row>
-    <row r="99" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="D99" s="2"/>
       <c r="G99" s="3"/>
@@ -13961,7 +13961,7 @@
         <f>IF($H99="","",P99-Y99)</f>
       </c>
     </row>
-    <row r="100" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
       <c r="D100" s="2"/>
       <c r="G100" s="3"/>
@@ -13998,7 +13998,7 @@
         <f>IF($H100="","",P100-Y100)</f>
       </c>
     </row>
-    <row r="101" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="D101" s="2"/>
       <c r="G101" s="3"/>
@@ -14035,7 +14035,7 @@
         <f>IF($H101="","",P101-Y101)</f>
       </c>
     </row>
-    <row r="102" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="D102" s="2"/>
       <c r="G102" s="3"/>
@@ -14072,7 +14072,7 @@
         <f>IF($H102="","",P102-Y102)</f>
       </c>
     </row>
-    <row r="103" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="D103" s="2"/>
       <c r="G103" s="3"/>
@@ -14109,7 +14109,7 @@
         <f>IF($H103="","",P103-Y103)</f>
       </c>
     </row>
-    <row r="104" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="D104" s="2"/>
       <c r="G104" s="3"/>
@@ -14146,7 +14146,7 @@
         <f>IF($H104="","",P104-Y104)</f>
       </c>
     </row>
-    <row r="105" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="D105" s="2"/>
       <c r="G105" s="3"/>
@@ -14183,7 +14183,7 @@
         <f>IF($H105="","",P105-Y105)</f>
       </c>
     </row>
-    <row r="106" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="D106" s="2"/>
       <c r="G106" s="3"/>
@@ -14220,7 +14220,7 @@
         <f>IF($H106="","",P106-Y106)</f>
       </c>
     </row>
-    <row r="107" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="D107" s="2"/>
       <c r="G107" s="3"/>
@@ -14257,7 +14257,7 @@
         <f>IF($H107="","",P107-Y107)</f>
       </c>
     </row>
-    <row r="108" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="D108" s="2"/>
       <c r="G108" s="3"/>
@@ -14294,7 +14294,7 @@
         <f>IF($H108="","",P108-Y108)</f>
       </c>
     </row>
-    <row r="109" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="D109" s="2"/>
       <c r="G109" s="3"/>
@@ -14331,7 +14331,7 @@
         <f>IF($H109="","",P109-Y109)</f>
       </c>
     </row>
-    <row r="110" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="D110" s="2"/>
       <c r="G110" s="3"/>
@@ -14368,7 +14368,7 @@
         <f>IF($H110="","",P110-Y110)</f>
       </c>
     </row>
-    <row r="111" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
       <c r="D111" s="2"/>
       <c r="G111" s="3"/>
@@ -14405,7 +14405,7 @@
         <f>IF($H111="","",P111-Y111)</f>
       </c>
     </row>
-    <row r="112" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="D112" s="2"/>
       <c r="G112" s="3"/>
@@ -14442,7 +14442,7 @@
         <f>IF($H112="","",P112-Y112)</f>
       </c>
     </row>
-    <row r="113" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="D113" s="2"/>
       <c r="G113" s="3"/>
@@ -14479,7 +14479,7 @@
         <f>IF($H113="","",P113-Y113)</f>
       </c>
     </row>
-    <row r="114" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="D114" s="2"/>
       <c r="G114" s="3"/>
@@ -14516,7 +14516,7 @@
         <f>IF($H114="","",P114-Y114)</f>
       </c>
     </row>
-    <row r="115" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="D115" s="2"/>
       <c r="G115" s="3"/>
@@ -14553,7 +14553,7 @@
         <f>IF($H115="","",P115-Y115)</f>
       </c>
     </row>
-    <row r="116" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="D116" s="2"/>
       <c r="G116" s="3"/>
@@ -14590,7 +14590,7 @@
         <f>IF($H116="","",P116-Y116)</f>
       </c>
     </row>
-    <row r="117" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="D117" s="2"/>
       <c r="G117" s="3"/>
@@ -14627,7 +14627,7 @@
         <f>IF($H117="","",P117-Y117)</f>
       </c>
     </row>
-    <row r="118" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="D118" s="2"/>
       <c r="G118" s="3"/>
@@ -14664,7 +14664,7 @@
         <f>IF($H118="","",P118-Y118)</f>
       </c>
     </row>
-    <row r="119" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="D119" s="2"/>
       <c r="G119" s="3"/>
@@ -14701,7 +14701,7 @@
         <f>IF($H119="","",P119-Y119)</f>
       </c>
     </row>
-    <row r="120" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="D120" s="2"/>
       <c r="G120" s="3"/>
@@ -14738,7 +14738,7 @@
         <f>IF($H120="","",P120-Y120)</f>
       </c>
     </row>
-    <row r="121" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="D121" s="2"/>
       <c r="G121" s="3"/>
@@ -14775,7 +14775,7 @@
         <f>IF($H121="","",P121-Y121)</f>
       </c>
     </row>
-    <row r="122" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="D122" s="2"/>
       <c r="G122" s="3"/>
@@ -14812,7 +14812,7 @@
         <f>IF($H122="","",P122-Y122)</f>
       </c>
     </row>
-    <row r="123" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="D123" s="2"/>
       <c r="G123" s="3"/>
@@ -14849,7 +14849,7 @@
         <f>IF($H123="","",P123-Y123)</f>
       </c>
     </row>
-    <row r="124" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="D124" s="2"/>
       <c r="G124" s="3"/>
@@ -14886,7 +14886,7 @@
         <f>IF($H124="","",P124-Y124)</f>
       </c>
     </row>
-    <row r="125" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="D125" s="2"/>
       <c r="G125" s="3"/>
@@ -14923,7 +14923,7 @@
         <f>IF($H125="","",P125-Y125)</f>
       </c>
     </row>
-    <row r="126" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="D126" s="2"/>
       <c r="G126" s="3"/>
@@ -14960,7 +14960,7 @@
         <f>IF($H126="","",P126-Y126)</f>
       </c>
     </row>
-    <row r="127" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="D127" s="2"/>
       <c r="G127" s="3"/>
@@ -14997,7 +14997,7 @@
         <f>IF($H127="","",P127-Y127)</f>
       </c>
     </row>
-    <row r="128" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A128" s="1"/>
       <c r="D128" s="2"/>
       <c r="G128" s="3"/>
@@ -15034,7 +15034,7 @@
         <f>IF($H128="","",P128-Y128)</f>
       </c>
     </row>
-    <row r="129" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A129" s="1"/>
       <c r="D129" s="2"/>
       <c r="G129" s="3"/>
@@ -15071,7 +15071,7 @@
         <f>IF($H129="","",P129-Y129)</f>
       </c>
     </row>
-    <row r="130" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A130" s="1"/>
       <c r="D130" s="2"/>
       <c r="G130" s="3"/>
@@ -15108,7 +15108,7 @@
         <f>IF($H130="","",P130-Y130)</f>
       </c>
     </row>
-    <row r="131" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A131" s="1"/>
       <c r="D131" s="2"/>
       <c r="G131" s="3"/>
@@ -15145,7 +15145,7 @@
         <f>IF($H131="","",P131-Y131)</f>
       </c>
     </row>
-    <row r="132" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A132" s="1"/>
       <c r="D132" s="2"/>
       <c r="G132" s="3"/>
@@ -15182,7 +15182,7 @@
         <f>IF($H132="","",P132-Y132)</f>
       </c>
     </row>
-    <row r="133" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
       <c r="D133" s="2"/>
       <c r="G133" s="3"/>
@@ -15219,7 +15219,7 @@
         <f>IF($H133="","",P133-Y133)</f>
       </c>
     </row>
-    <row r="134" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
       <c r="D134" s="2"/>
       <c r="G134" s="3"/>
@@ -15256,7 +15256,7 @@
         <f>IF($H134="","",P134-Y134)</f>
       </c>
     </row>
-    <row r="135" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A135" s="1"/>
       <c r="D135" s="2"/>
       <c r="G135" s="3"/>
@@ -15293,7 +15293,7 @@
         <f>IF($H135="","",P135-Y135)</f>
       </c>
     </row>
-    <row r="136" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A136" s="1"/>
       <c r="D136" s="2"/>
       <c r="G136" s="3"/>
@@ -15330,7 +15330,7 @@
         <f>IF($H136="","",P136-Y136)</f>
       </c>
     </row>
-    <row r="137" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A137" s="1"/>
       <c r="D137" s="2"/>
       <c r="G137" s="3"/>
@@ -15367,7 +15367,7 @@
         <f>IF($H137="","",P137-Y137)</f>
       </c>
     </row>
-    <row r="138" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A138" s="1"/>
       <c r="D138" s="2"/>
       <c r="G138" s="3"/>
@@ -15404,7 +15404,7 @@
         <f>IF($H138="","",P138-Y138)</f>
       </c>
     </row>
-    <row r="139" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A139" s="1"/>
       <c r="D139" s="2"/>
       <c r="G139" s="3"/>
@@ -15441,7 +15441,7 @@
         <f>IF($H139="","",P139-Y139)</f>
       </c>
     </row>
-    <row r="140" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A140" s="1"/>
       <c r="D140" s="2"/>
       <c r="G140" s="3"/>
@@ -15478,7 +15478,7 @@
         <f>IF($H140="","",P140-Y140)</f>
       </c>
     </row>
-    <row r="141" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="D141" s="2"/>
       <c r="G141" s="3"/>
@@ -15515,7 +15515,7 @@
         <f>IF($H141="","",P141-Y141)</f>
       </c>
     </row>
-    <row r="142" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A142" s="1"/>
       <c r="D142" s="2"/>
       <c r="G142" s="3"/>
@@ -15552,7 +15552,7 @@
         <f>IF($H142="","",P142-Y142)</f>
       </c>
     </row>
-    <row r="143" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="D143" s="2"/>
       <c r="G143" s="3"/>
@@ -15589,7 +15589,7 @@
         <f>IF($H143="","",P143-Y143)</f>
       </c>
     </row>
-    <row r="144" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="D144" s="2"/>
       <c r="G144" s="3"/>
@@ -15626,7 +15626,7 @@
         <f>IF($H144="","",P144-Y144)</f>
       </c>
     </row>
-    <row r="145" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A145" s="1"/>
       <c r="D145" s="2"/>
       <c r="G145" s="3"/>
@@ -15663,7 +15663,7 @@
         <f>IF($H145="","",P145-Y145)</f>
       </c>
     </row>
-    <row r="146" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
       <c r="D146" s="2"/>
       <c r="G146" s="3"/>
@@ -15700,7 +15700,7 @@
         <f>IF($H146="","",P146-Y146)</f>
       </c>
     </row>
-    <row r="147" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A147" s="1"/>
       <c r="D147" s="2"/>
       <c r="G147" s="3"/>
@@ -15737,7 +15737,7 @@
         <f>IF($H147="","",P147-Y147)</f>
       </c>
     </row>
-    <row r="148" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A148" s="1"/>
       <c r="D148" s="2"/>
       <c r="G148" s="3"/>
@@ -15774,7 +15774,7 @@
         <f>IF($H148="","",P148-Y148)</f>
       </c>
     </row>
-    <row r="149" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
       <c r="D149" s="2"/>
       <c r="G149" s="3"/>
@@ -15811,7 +15811,7 @@
         <f>IF($H149="","",P149-Y149)</f>
       </c>
     </row>
-    <row r="150" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A150" s="1"/>
       <c r="D150" s="2"/>
       <c r="G150" s="3"/>
@@ -15848,7 +15848,7 @@
         <f>IF($H150="","",P150-Y150)</f>
       </c>
     </row>
-    <row r="151" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
       <c r="D151" s="2"/>
       <c r="G151" s="3"/>
@@ -15885,7 +15885,7 @@
         <f>IF($H151="","",P151-Y151)</f>
       </c>
     </row>
-    <row r="152" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A152" s="1"/>
       <c r="D152" s="2"/>
       <c r="G152" s="3"/>
@@ -15922,7 +15922,7 @@
         <f>IF($H152="","",P152-Y152)</f>
       </c>
     </row>
-    <row r="153" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
       <c r="D153" s="2"/>
       <c r="G153" s="3"/>
@@ -15959,7 +15959,7 @@
         <f>IF($H153="","",P153-Y153)</f>
       </c>
     </row>
-    <row r="154" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
       <c r="D154" s="2"/>
       <c r="G154" s="3"/>
@@ -15996,7 +15996,7 @@
         <f>IF($H154="","",P154-Y154)</f>
       </c>
     </row>
-    <row r="155" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A155" s="1"/>
       <c r="D155" s="2"/>
       <c r="G155" s="3"/>
@@ -16033,7 +16033,7 @@
         <f>IF($H155="","",P155-Y155)</f>
       </c>
     </row>
-    <row r="156" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A156" s="1"/>
       <c r="D156" s="2"/>
       <c r="G156" s="3"/>
@@ -16070,7 +16070,7 @@
         <f>IF($H156="","",P156-Y156)</f>
       </c>
     </row>
-    <row r="157" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A157" s="1"/>
       <c r="D157" s="2"/>
       <c r="G157" s="3"/>
@@ -16107,7 +16107,7 @@
         <f>IF($H157="","",P157-Y157)</f>
       </c>
     </row>
-    <row r="158" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A158" s="1"/>
       <c r="D158" s="2"/>
       <c r="G158" s="3"/>
@@ -16144,7 +16144,7 @@
         <f>IF($H158="","",P158-Y158)</f>
       </c>
     </row>
-    <row r="159" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A159" s="1"/>
       <c r="D159" s="2"/>
       <c r="G159" s="3"/>
@@ -16181,7 +16181,7 @@
         <f>IF($H159="","",P159-Y159)</f>
       </c>
     </row>
-    <row r="160" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A160" s="1"/>
       <c r="D160" s="2"/>
       <c r="G160" s="3"/>
@@ -16218,7 +16218,7 @@
         <f>IF($H160="","",P160-Y160)</f>
       </c>
     </row>
-    <row r="161" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A161" s="1"/>
       <c r="D161" s="2"/>
       <c r="G161" s="3"/>
@@ -16255,7 +16255,7 @@
         <f>IF($H161="","",P161-Y161)</f>
       </c>
     </row>
-    <row r="162" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A162" s="1"/>
       <c r="D162" s="2"/>
       <c r="G162" s="3"/>
@@ -16292,7 +16292,7 @@
         <f>IF($H162="","",P162-Y162)</f>
       </c>
     </row>
-    <row r="163" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A163" s="1"/>
       <c r="D163" s="2"/>
       <c r="G163" s="3"/>
@@ -16329,7 +16329,7 @@
         <f>IF($H163="","",P163-Y163)</f>
       </c>
     </row>
-    <row r="164" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A164" s="1"/>
       <c r="D164" s="2"/>
       <c r="G164" s="3"/>
@@ -16366,7 +16366,7 @@
         <f>IF($H164="","",P164-Y164)</f>
       </c>
     </row>
-    <row r="165" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A165" s="1"/>
       <c r="D165" s="2"/>
       <c r="G165" s="3"/>
@@ -16403,7 +16403,7 @@
         <f>IF($H165="","",P165-Y165)</f>
       </c>
     </row>
-    <row r="166" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A166" s="1"/>
       <c r="D166" s="2"/>
       <c r="G166" s="3"/>
@@ -16440,7 +16440,7 @@
         <f>IF($H166="","",P166-Y166)</f>
       </c>
     </row>
-    <row r="167" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A167" s="1"/>
       <c r="D167" s="2"/>
       <c r="G167" s="3"/>
@@ -16477,7 +16477,7 @@
         <f>IF($H167="","",P167-Y167)</f>
       </c>
     </row>
-    <row r="168" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A168" s="1"/>
       <c r="D168" s="2"/>
       <c r="G168" s="3"/>
@@ -16514,7 +16514,7 @@
         <f>IF($H168="","",P168-Y168)</f>
       </c>
     </row>
-    <row r="169" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A169" s="1"/>
       <c r="D169" s="2"/>
       <c r="G169" s="3"/>
@@ -16551,7 +16551,7 @@
         <f>IF($H169="","",P169-Y169)</f>
       </c>
     </row>
-    <row r="170" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A170" s="1"/>
       <c r="D170" s="2"/>
       <c r="G170" s="3"/>
@@ -16588,7 +16588,7 @@
         <f>IF($H170="","",P170-Y170)</f>
       </c>
     </row>
-    <row r="171" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A171" s="1"/>
       <c r="D171" s="2"/>
       <c r="G171" s="3"/>
@@ -16625,7 +16625,7 @@
         <f>IF($H171="","",P171-Y171)</f>
       </c>
     </row>
-    <row r="172" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A172" s="1"/>
       <c r="D172" s="2"/>
       <c r="G172" s="3"/>
@@ -16662,7 +16662,7 @@
         <f>IF($H172="","",P172-Y172)</f>
       </c>
     </row>
-    <row r="173" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A173" s="1"/>
       <c r="D173" s="2"/>
       <c r="G173" s="3"/>
@@ -16699,7 +16699,7 @@
         <f>IF($H173="","",P173-Y173)</f>
       </c>
     </row>
-    <row r="174" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A174" s="1"/>
       <c r="D174" s="2"/>
       <c r="G174" s="3"/>
@@ -16736,7 +16736,7 @@
         <f>IF($H174="","",P174-Y174)</f>
       </c>
     </row>
-    <row r="175" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A175" s="1"/>
       <c r="D175" s="2"/>
       <c r="G175" s="3"/>
@@ -16773,7 +16773,7 @@
         <f>IF($H175="","",P175-Y175)</f>
       </c>
     </row>
-    <row r="176" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A176" s="1"/>
       <c r="D176" s="2"/>
       <c r="G176" s="3"/>
@@ -16810,7 +16810,7 @@
         <f>IF($H176="","",P176-Y176)</f>
       </c>
     </row>
-    <row r="177" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A177" s="1"/>
       <c r="D177" s="2"/>
       <c r="G177" s="3"/>
@@ -16847,7 +16847,7 @@
         <f>IF($H177="","",P177-Y177)</f>
       </c>
     </row>
-    <row r="178" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A178" s="1"/>
       <c r="D178" s="2"/>
       <c r="G178" s="3"/>
@@ -16884,7 +16884,7 @@
         <f>IF($H178="","",P178-Y178)</f>
       </c>
     </row>
-    <row r="179" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A179" s="1"/>
       <c r="D179" s="2"/>
       <c r="G179" s="3"/>
@@ -16921,7 +16921,7 @@
         <f>IF($H179="","",P179-Y179)</f>
       </c>
     </row>
-    <row r="180" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A180" s="1"/>
       <c r="D180" s="2"/>
       <c r="G180" s="3"/>
@@ -16958,7 +16958,7 @@
         <f>IF($H180="","",P180-Y180)</f>
       </c>
     </row>
-    <row r="181" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A181" s="1"/>
       <c r="D181" s="2"/>
       <c r="G181" s="3"/>
@@ -16995,7 +16995,7 @@
         <f>IF($H181="","",P181-Y181)</f>
       </c>
     </row>
-    <row r="182" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A182" s="1"/>
       <c r="D182" s="2"/>
       <c r="G182" s="3"/>
@@ -17032,7 +17032,7 @@
         <f>IF($H182="","",P182-Y182)</f>
       </c>
     </row>
-    <row r="183" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A183" s="1"/>
       <c r="D183" s="2"/>
       <c r="G183" s="3"/>
@@ -17069,7 +17069,7 @@
         <f>IF($H183="","",P183-Y183)</f>
       </c>
     </row>
-    <row r="184" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A184" s="1"/>
       <c r="D184" s="2"/>
       <c r="G184" s="3"/>
@@ -17106,7 +17106,7 @@
         <f>IF($H184="","",P184-Y184)</f>
       </c>
     </row>
-    <row r="185" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A185" s="1"/>
       <c r="D185" s="2"/>
       <c r="G185" s="3"/>
@@ -17143,7 +17143,7 @@
         <f>IF($H185="","",P185-Y185)</f>
       </c>
     </row>
-    <row r="186" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A186" s="1"/>
       <c r="D186" s="2"/>
       <c r="G186" s="3"/>
@@ -17180,7 +17180,7 @@
         <f>IF($H186="","",P186-Y186)</f>
       </c>
     </row>
-    <row r="187" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A187" s="1"/>
       <c r="D187" s="2"/>
       <c r="G187" s="3"/>
@@ -17217,7 +17217,7 @@
         <f>IF($H187="","",P187-Y187)</f>
       </c>
     </row>
-    <row r="188" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A188" s="1"/>
       <c r="D188" s="2"/>
       <c r="G188" s="3"/>
@@ -17254,7 +17254,7 @@
         <f>IF($H188="","",P188-Y188)</f>
       </c>
     </row>
-    <row r="189" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A189" s="1"/>
       <c r="D189" s="2"/>
       <c r="G189" s="3"/>
@@ -17291,7 +17291,7 @@
         <f>IF($H189="","",P189-Y189)</f>
       </c>
     </row>
-    <row r="190" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A190" s="1"/>
       <c r="D190" s="2"/>
       <c r="G190" s="3"/>
@@ -17328,7 +17328,7 @@
         <f>IF($H190="","",P190-Y190)</f>
       </c>
     </row>
-    <row r="191" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A191" s="1"/>
       <c r="D191" s="2"/>
       <c r="G191" s="3"/>
@@ -17365,7 +17365,7 @@
         <f>IF($H191="","",P191-Y191)</f>
       </c>
     </row>
-    <row r="192" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A192" s="1"/>
       <c r="D192" s="2"/>
       <c r="G192" s="3"/>
@@ -17402,7 +17402,7 @@
         <f>IF($H192="","",P192-Y192)</f>
       </c>
     </row>
-    <row r="193" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A193" s="1"/>
       <c r="D193" s="2"/>
       <c r="G193" s="3"/>
@@ -17439,7 +17439,7 @@
         <f>IF($H193="","",P193-Y193)</f>
       </c>
     </row>
-    <row r="194" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A194" s="1"/>
       <c r="D194" s="2"/>
       <c r="G194" s="3"/>
@@ -17476,7 +17476,7 @@
         <f>IF($H194="","",P194-Y194)</f>
       </c>
     </row>
-    <row r="195" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A195" s="1"/>
       <c r="D195" s="2"/>
       <c r="G195" s="3"/>
@@ -17513,7 +17513,7 @@
         <f>IF($H195="","",P195-Y195)</f>
       </c>
     </row>
-    <row r="196" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A196" s="1"/>
       <c r="D196" s="2"/>
       <c r="G196" s="3"/>
@@ -17550,7 +17550,7 @@
         <f>IF($H196="","",P196-Y196)</f>
       </c>
     </row>
-    <row r="197" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A197" s="1"/>
       <c r="D197" s="2"/>
       <c r="G197" s="3"/>
@@ -17587,7 +17587,7 @@
         <f>IF($H197="","",P197-Y197)</f>
       </c>
     </row>
-    <row r="198" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A198" s="1"/>
       <c r="D198" s="2"/>
       <c r="G198" s="3"/>
@@ -17624,7 +17624,7 @@
         <f>IF($H198="","",P198-Y198)</f>
       </c>
     </row>
-    <row r="199" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A199" s="1"/>
       <c r="D199" s="2"/>
       <c r="G199" s="3"/>
@@ -17661,7 +17661,7 @@
         <f>IF($H199="","",P199-Y199)</f>
       </c>
     </row>
-    <row r="200" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A200" s="1"/>
       <c r="D200" s="2"/>
       <c r="G200" s="3"/>
@@ -17698,7 +17698,7 @@
         <f>IF($H200="","",P200-Y200)</f>
       </c>
     </row>
-    <row r="201" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A201" s="1"/>
       <c r="D201" s="2"/>
       <c r="G201" s="3"/>
@@ -17735,7 +17735,7 @@
         <f>IF($H201="","",P201-Y201)</f>
       </c>
     </row>
-    <row r="202" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A202" s="1"/>
       <c r="D202" s="2"/>
       <c r="G202" s="3"/>
@@ -17975,25 +17975,25 @@
         <v>679</v>
       </c>
       <c r="I2" s="3">
-        <f>IF($H2="","",H2-G2)</f>
+        <f>H2-G2</f>
       </c>
       <c r="J2" s="3">
-        <f>IF($H2="","",I2*16.67%)</f>
+        <f>I2*16.67%</f>
       </c>
       <c r="K2" s="3">
-        <f>IF($H2="","",(H2*6.9%)-(H2*6.9%)*10%)</f>
+        <f>(H2*6.9%)-(H2*6.9%)*10%</f>
       </c>
       <c r="L2" s="3">
-        <f>IF($H2="","",H2*0.35%)</f>
+        <f>H2*0.35%</f>
       </c>
       <c r="M2" s="3">
         <v>0.4</v>
       </c>
       <c r="N2" s="3">
-        <f>IF($H2="","",(K2+L2+M2)*20%)</f>
+        <f>(K2+L2+M2)*20%</f>
       </c>
       <c r="O2" s="3">
-        <f>IF($H2="","",K2+L2+M2+N2)</f>
+        <f>K2+L2+M2+N2</f>
       </c>
       <c r="P2" s="3">
         <v>8</v>
@@ -18005,22 +18005,22 @@
         <v>0</v>
       </c>
       <c r="S2" s="3">
-        <f>IF($H2="","",R2*20%)</f>
+        <f>R2*20%</f>
       </c>
       <c r="T2" s="3">
         <v>1</v>
       </c>
       <c r="U2" s="3">
-        <f>IF($H2="","",N2+Q2+S2)</f>
+        <f>N2+Q2+S2</f>
       </c>
       <c r="V2" s="3">
-        <f>IF($H2="","",I2-J2-O2-P2-Q2-R2-S2-T2)</f>
+        <f>I2-J2-O2-P2-Q2-R2-S2-T2</f>
       </c>
       <c r="W2" s="3">
-        <f>IF($H2="","",(V2-AE2)/H2*100)</f>
+        <f>(V2-AE2)/H2*100</f>
       </c>
       <c r="X2" s="3">
-        <f>IF($H2="","",J2-U2)</f>
+        <f>J2-U2</f>
       </c>
       <c r="Y2" t="s">
         <v>35</v>
@@ -18029,7 +18029,7 @@
         <v>54</v>
       </c>
       <c r="AF2" s="3">
-        <f>IF($H2="","",V2-AE2)</f>
+        <f>V2-AE2</f>
       </c>
       <c r="AG2" t="s">
         <v>35</v>
@@ -18038,7 +18038,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="D3" s="2"/>
       <c r="G3" s="3"/>
@@ -18089,7 +18089,7 @@
         <f>IF($H3="","",V3-AE3)</f>
       </c>
     </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="D4" s="2"/>
       <c r="G4" s="3"/>
@@ -18140,7 +18140,7 @@
         <f>IF($H4="","",V4-AE4)</f>
       </c>
     </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="D5" s="2"/>
       <c r="G5" s="3"/>
@@ -18191,7 +18191,7 @@
         <f>IF($H5="","",V5-AE5)</f>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="D6" s="2"/>
       <c r="G6" s="3"/>
@@ -18242,7 +18242,7 @@
         <f>IF($H6="","",V6-AE6)</f>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="D7" s="2"/>
       <c r="G7" s="3"/>
@@ -18293,7 +18293,7 @@
         <f>IF($H7="","",V7-AE7)</f>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="D8" s="2"/>
       <c r="G8" s="3"/>
@@ -18344,7 +18344,7 @@
         <f>IF($H8="","",V8-AE8)</f>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="D9" s="2"/>
       <c r="G9" s="3"/>
@@ -18395,7 +18395,7 @@
         <f>IF($H9="","",V9-AE9)</f>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="D10" s="2"/>
       <c r="G10" s="3"/>
@@ -18446,7 +18446,7 @@
         <f>IF($H10="","",V10-AE10)</f>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="D11" s="2"/>
       <c r="G11" s="3"/>
@@ -18497,7 +18497,7 @@
         <f>IF($H11="","",V11-AE11)</f>
       </c>
     </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="D12" s="2"/>
       <c r="G12" s="3"/>
@@ -18548,7 +18548,7 @@
         <f>IF($H12="","",V12-AE12)</f>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="D13" s="2"/>
       <c r="G13" s="3"/>
@@ -18599,7 +18599,7 @@
         <f>IF($H13="","",V13-AE13)</f>
       </c>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="D14" s="2"/>
       <c r="G14" s="3"/>
@@ -18650,7 +18650,7 @@
         <f>IF($H14="","",V14-AE14)</f>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="D15" s="2"/>
       <c r="G15" s="3"/>
@@ -18701,7 +18701,7 @@
         <f>IF($H15="","",V15-AE15)</f>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="D16" s="2"/>
       <c r="G16" s="3"/>
@@ -18752,7 +18752,7 @@
         <f>IF($H16="","",V16-AE16)</f>
       </c>
     </row>
-    <row r="17" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="D17" s="2"/>
       <c r="G17" s="3"/>
@@ -18803,7 +18803,7 @@
         <f>IF($H17="","",V17-AE17)</f>
       </c>
     </row>
-    <row r="18" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="D18" s="2"/>
       <c r="G18" s="3"/>
@@ -18854,7 +18854,7 @@
         <f>IF($H18="","",V18-AE18)</f>
       </c>
     </row>
-    <row r="19" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="D19" s="2"/>
       <c r="G19" s="3"/>
@@ -18905,7 +18905,7 @@
         <f>IF($H19="","",V19-AE19)</f>
       </c>
     </row>
-    <row r="20" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="D20" s="2"/>
       <c r="G20" s="3"/>
@@ -18956,7 +18956,7 @@
         <f>IF($H20="","",V20-AE20)</f>
       </c>
     </row>
-    <row r="21" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="D21" s="2"/>
       <c r="G21" s="3"/>
@@ -19007,7 +19007,7 @@
         <f>IF($H21="","",V21-AE21)</f>
       </c>
     </row>
-    <row r="22" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="D22" s="2"/>
       <c r="G22" s="3"/>
@@ -19058,7 +19058,7 @@
         <f>IF($H22="","",V22-AE22)</f>
       </c>
     </row>
-    <row r="23" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="D23" s="2"/>
       <c r="G23" s="3"/>
@@ -19109,7 +19109,7 @@
         <f>IF($H23="","",V23-AE23)</f>
       </c>
     </row>
-    <row r="24" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="D24" s="2"/>
       <c r="G24" s="3"/>
@@ -19160,7 +19160,7 @@
         <f>IF($H24="","",V24-AE24)</f>
       </c>
     </row>
-    <row r="25" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="D25" s="2"/>
       <c r="G25" s="3"/>
@@ -19211,7 +19211,7 @@
         <f>IF($H25="","",V25-AE25)</f>
       </c>
     </row>
-    <row r="26" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="D26" s="2"/>
       <c r="G26" s="3"/>
@@ -19262,7 +19262,7 @@
         <f>IF($H26="","",V26-AE26)</f>
       </c>
     </row>
-    <row r="27" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="D27" s="2"/>
       <c r="G27" s="3"/>
@@ -19313,7 +19313,7 @@
         <f>IF($H27="","",V27-AE27)</f>
       </c>
     </row>
-    <row r="28" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="D28" s="2"/>
       <c r="G28" s="3"/>
@@ -19364,7 +19364,7 @@
         <f>IF($H28="","",V28-AE28)</f>
       </c>
     </row>
-    <row r="29" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="D29" s="2"/>
       <c r="G29" s="3"/>
@@ -19415,7 +19415,7 @@
         <f>IF($H29="","",V29-AE29)</f>
       </c>
     </row>
-    <row r="30" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="D30" s="2"/>
       <c r="G30" s="3"/>
@@ -19466,7 +19466,7 @@
         <f>IF($H30="","",V30-AE30)</f>
       </c>
     </row>
-    <row r="31" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="D31" s="2"/>
       <c r="G31" s="3"/>
@@ -19517,7 +19517,7 @@
         <f>IF($H31="","",V31-AE31)</f>
       </c>
     </row>
-    <row r="32" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="D32" s="2"/>
       <c r="G32" s="3"/>
@@ -19568,7 +19568,7 @@
         <f>IF($H32="","",V32-AE32)</f>
       </c>
     </row>
-    <row r="33" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="D33" s="2"/>
       <c r="G33" s="3"/>
@@ -19619,7 +19619,7 @@
         <f>IF($H33="","",V33-AE33)</f>
       </c>
     </row>
-    <row r="34" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="D34" s="2"/>
       <c r="G34" s="3"/>
@@ -19670,7 +19670,7 @@
         <f>IF($H34="","",V34-AE34)</f>
       </c>
     </row>
-    <row r="35" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="D35" s="2"/>
       <c r="G35" s="3"/>
@@ -19721,7 +19721,7 @@
         <f>IF($H35="","",V35-AE35)</f>
       </c>
     </row>
-    <row r="36" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="D36" s="2"/>
       <c r="G36" s="3"/>
@@ -19772,7 +19772,7 @@
         <f>IF($H36="","",V36-AE36)</f>
       </c>
     </row>
-    <row r="37" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="D37" s="2"/>
       <c r="G37" s="3"/>
@@ -19823,7 +19823,7 @@
         <f>IF($H37="","",V37-AE37)</f>
       </c>
     </row>
-    <row r="38" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="D38" s="2"/>
       <c r="G38" s="3"/>
@@ -19874,7 +19874,7 @@
         <f>IF($H38="","",V38-AE38)</f>
       </c>
     </row>
-    <row r="39" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="D39" s="2"/>
       <c r="G39" s="3"/>
@@ -19925,7 +19925,7 @@
         <f>IF($H39="","",V39-AE39)</f>
       </c>
     </row>
-    <row r="40" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="D40" s="2"/>
       <c r="G40" s="3"/>
@@ -19976,7 +19976,7 @@
         <f>IF($H40="","",V40-AE40)</f>
       </c>
     </row>
-    <row r="41" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="D41" s="2"/>
       <c r="G41" s="3"/>
@@ -20027,7 +20027,7 @@
         <f>IF($H41="","",V41-AE41)</f>
       </c>
     </row>
-    <row r="42" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="D42" s="2"/>
       <c r="G42" s="3"/>
@@ -20078,7 +20078,7 @@
         <f>IF($H42="","",V42-AE42)</f>
       </c>
     </row>
-    <row r="43" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="D43" s="2"/>
       <c r="G43" s="3"/>
@@ -20129,7 +20129,7 @@
         <f>IF($H43="","",V43-AE43)</f>
       </c>
     </row>
-    <row r="44" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="D44" s="2"/>
       <c r="G44" s="3"/>
@@ -20180,7 +20180,7 @@
         <f>IF($H44="","",V44-AE44)</f>
       </c>
     </row>
-    <row r="45" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="D45" s="2"/>
       <c r="G45" s="3"/>
@@ -20231,7 +20231,7 @@
         <f>IF($H45="","",V45-AE45)</f>
       </c>
     </row>
-    <row r="46" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="D46" s="2"/>
       <c r="G46" s="3"/>
@@ -20282,7 +20282,7 @@
         <f>IF($H46="","",V46-AE46)</f>
       </c>
     </row>
-    <row r="47" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="D47" s="2"/>
       <c r="G47" s="3"/>
@@ -20333,7 +20333,7 @@
         <f>IF($H47="","",V47-AE47)</f>
       </c>
     </row>
-    <row r="48" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="D48" s="2"/>
       <c r="G48" s="3"/>
@@ -20384,7 +20384,7 @@
         <f>IF($H48="","",V48-AE48)</f>
       </c>
     </row>
-    <row r="49" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
       <c r="D49" s="2"/>
       <c r="G49" s="3"/>
@@ -20435,7 +20435,7 @@
         <f>IF($H49="","",V49-AE49)</f>
       </c>
     </row>
-    <row r="50" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
       <c r="D50" s="2"/>
       <c r="G50" s="3"/>
@@ -20486,7 +20486,7 @@
         <f>IF($H50="","",V50-AE50)</f>
       </c>
     </row>
-    <row r="51" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
       <c r="D51" s="2"/>
       <c r="G51" s="3"/>
@@ -20537,7 +20537,7 @@
         <f>IF($H51="","",V51-AE51)</f>
       </c>
     </row>
-    <row r="52" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
       <c r="D52" s="2"/>
       <c r="G52" s="3"/>
@@ -20588,7 +20588,7 @@
         <f>IF($H52="","",V52-AE52)</f>
       </c>
     </row>
-    <row r="53" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
       <c r="D53" s="2"/>
       <c r="G53" s="3"/>
@@ -20639,7 +20639,7 @@
         <f>IF($H53="","",V53-AE53)</f>
       </c>
     </row>
-    <row r="54" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
       <c r="D54" s="2"/>
       <c r="G54" s="3"/>
@@ -20690,7 +20690,7 @@
         <f>IF($H54="","",V54-AE54)</f>
       </c>
     </row>
-    <row r="55" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
       <c r="D55" s="2"/>
       <c r="G55" s="3"/>
@@ -20741,7 +20741,7 @@
         <f>IF($H55="","",V55-AE55)</f>
       </c>
     </row>
-    <row r="56" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
       <c r="D56" s="2"/>
       <c r="G56" s="3"/>
@@ -20792,7 +20792,7 @@
         <f>IF($H56="","",V56-AE56)</f>
       </c>
     </row>
-    <row r="57" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
       <c r="D57" s="2"/>
       <c r="G57" s="3"/>
@@ -20843,7 +20843,7 @@
         <f>IF($H57="","",V57-AE57)</f>
       </c>
     </row>
-    <row r="58" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
       <c r="D58" s="2"/>
       <c r="G58" s="3"/>
@@ -20894,7 +20894,7 @@
         <f>IF($H58="","",V58-AE58)</f>
       </c>
     </row>
-    <row r="59" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
       <c r="D59" s="2"/>
       <c r="G59" s="3"/>
@@ -20945,7 +20945,7 @@
         <f>IF($H59="","",V59-AE59)</f>
       </c>
     </row>
-    <row r="60" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
       <c r="D60" s="2"/>
       <c r="G60" s="3"/>
@@ -20996,7 +20996,7 @@
         <f>IF($H60="","",V60-AE60)</f>
       </c>
     </row>
-    <row r="61" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
       <c r="D61" s="2"/>
       <c r="G61" s="3"/>
@@ -21047,7 +21047,7 @@
         <f>IF($H61="","",V61-AE61)</f>
       </c>
     </row>
-    <row r="62" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
       <c r="D62" s="2"/>
       <c r="G62" s="3"/>
@@ -21098,7 +21098,7 @@
         <f>IF($H62="","",V62-AE62)</f>
       </c>
     </row>
-    <row r="63" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
       <c r="D63" s="2"/>
       <c r="G63" s="3"/>
@@ -21149,7 +21149,7 @@
         <f>IF($H63="","",V63-AE63)</f>
       </c>
     </row>
-    <row r="64" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
       <c r="D64" s="2"/>
       <c r="G64" s="3"/>
@@ -21200,7 +21200,7 @@
         <f>IF($H64="","",V64-AE64)</f>
       </c>
     </row>
-    <row r="65" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
       <c r="D65" s="2"/>
       <c r="G65" s="3"/>
@@ -21251,7 +21251,7 @@
         <f>IF($H65="","",V65-AE65)</f>
       </c>
     </row>
-    <row r="66" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
       <c r="D66" s="2"/>
       <c r="G66" s="3"/>
@@ -21302,7 +21302,7 @@
         <f>IF($H66="","",V66-AE66)</f>
       </c>
     </row>
-    <row r="67" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
       <c r="D67" s="2"/>
       <c r="G67" s="3"/>
@@ -21353,7 +21353,7 @@
         <f>IF($H67="","",V67-AE67)</f>
       </c>
     </row>
-    <row r="68" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
       <c r="D68" s="2"/>
       <c r="G68" s="3"/>
@@ -21404,7 +21404,7 @@
         <f>IF($H68="","",V68-AE68)</f>
       </c>
     </row>
-    <row r="69" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
       <c r="D69" s="2"/>
       <c r="G69" s="3"/>
@@ -21455,7 +21455,7 @@
         <f>IF($H69="","",V69-AE69)</f>
       </c>
     </row>
-    <row r="70" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
       <c r="D70" s="2"/>
       <c r="G70" s="3"/>
@@ -21506,7 +21506,7 @@
         <f>IF($H70="","",V70-AE70)</f>
       </c>
     </row>
-    <row r="71" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
       <c r="D71" s="2"/>
       <c r="G71" s="3"/>
@@ -21557,7 +21557,7 @@
         <f>IF($H71="","",V71-AE71)</f>
       </c>
     </row>
-    <row r="72" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
       <c r="D72" s="2"/>
       <c r="G72" s="3"/>
@@ -21608,7 +21608,7 @@
         <f>IF($H72="","",V72-AE72)</f>
       </c>
     </row>
-    <row r="73" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
       <c r="D73" s="2"/>
       <c r="G73" s="3"/>
@@ -21659,7 +21659,7 @@
         <f>IF($H73="","",V73-AE73)</f>
       </c>
     </row>
-    <row r="74" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
       <c r="D74" s="2"/>
       <c r="G74" s="3"/>
@@ -21710,7 +21710,7 @@
         <f>IF($H74="","",V74-AE74)</f>
       </c>
     </row>
-    <row r="75" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
       <c r="D75" s="2"/>
       <c r="G75" s="3"/>
@@ -21761,7 +21761,7 @@
         <f>IF($H75="","",V75-AE75)</f>
       </c>
     </row>
-    <row r="76" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
       <c r="D76" s="2"/>
       <c r="G76" s="3"/>
@@ -21812,7 +21812,7 @@
         <f>IF($H76="","",V76-AE76)</f>
       </c>
     </row>
-    <row r="77" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
       <c r="D77" s="2"/>
       <c r="G77" s="3"/>
@@ -21863,7 +21863,7 @@
         <f>IF($H77="","",V77-AE77)</f>
       </c>
     </row>
-    <row r="78" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
       <c r="D78" s="2"/>
       <c r="G78" s="3"/>
@@ -21914,7 +21914,7 @@
         <f>IF($H78="","",V78-AE78)</f>
       </c>
     </row>
-    <row r="79" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="D79" s="2"/>
       <c r="G79" s="3"/>
@@ -21965,7 +21965,7 @@
         <f>IF($H79="","",V79-AE79)</f>
       </c>
     </row>
-    <row r="80" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
       <c r="D80" s="2"/>
       <c r="G80" s="3"/>
@@ -22016,7 +22016,7 @@
         <f>IF($H80="","",V80-AE80)</f>
       </c>
     </row>
-    <row r="81" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
       <c r="D81" s="2"/>
       <c r="G81" s="3"/>
@@ -22067,7 +22067,7 @@
         <f>IF($H81="","",V81-AE81)</f>
       </c>
     </row>
-    <row r="82" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
       <c r="D82" s="2"/>
       <c r="G82" s="3"/>
@@ -22118,7 +22118,7 @@
         <f>IF($H82="","",V82-AE82)</f>
       </c>
     </row>
-    <row r="83" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
       <c r="D83" s="2"/>
       <c r="G83" s="3"/>
@@ -22169,7 +22169,7 @@
         <f>IF($H83="","",V83-AE83)</f>
       </c>
     </row>
-    <row r="84" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
       <c r="D84" s="2"/>
       <c r="G84" s="3"/>
@@ -22220,7 +22220,7 @@
         <f>IF($H84="","",V84-AE84)</f>
       </c>
     </row>
-    <row r="85" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="D85" s="2"/>
       <c r="G85" s="3"/>
@@ -22271,7 +22271,7 @@
         <f>IF($H85="","",V85-AE85)</f>
       </c>
     </row>
-    <row r="86" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="D86" s="2"/>
       <c r="G86" s="3"/>
@@ -22322,7 +22322,7 @@
         <f>IF($H86="","",V86-AE86)</f>
       </c>
     </row>
-    <row r="87" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="D87" s="2"/>
       <c r="G87" s="3"/>
@@ -22373,7 +22373,7 @@
         <f>IF($H87="","",V87-AE87)</f>
       </c>
     </row>
-    <row r="88" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="D88" s="2"/>
       <c r="G88" s="3"/>
@@ -22424,7 +22424,7 @@
         <f>IF($H88="","",V88-AE88)</f>
       </c>
     </row>
-    <row r="89" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="D89" s="2"/>
       <c r="G89" s="3"/>
@@ -22475,7 +22475,7 @@
         <f>IF($H89="","",V89-AE89)</f>
       </c>
     </row>
-    <row r="90" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="D90" s="2"/>
       <c r="G90" s="3"/>
@@ -22526,7 +22526,7 @@
         <f>IF($H90="","",V90-AE90)</f>
       </c>
     </row>
-    <row r="91" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="D91" s="2"/>
       <c r="G91" s="3"/>
@@ -22577,7 +22577,7 @@
         <f>IF($H91="","",V91-AE91)</f>
       </c>
     </row>
-    <row r="92" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="D92" s="2"/>
       <c r="G92" s="3"/>
@@ -22628,7 +22628,7 @@
         <f>IF($H92="","",V92-AE92)</f>
       </c>
     </row>
-    <row r="93" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="D93" s="2"/>
       <c r="G93" s="3"/>
@@ -22679,7 +22679,7 @@
         <f>IF($H93="","",V93-AE93)</f>
       </c>
     </row>
-    <row r="94" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="D94" s="2"/>
       <c r="G94" s="3"/>
@@ -22730,7 +22730,7 @@
         <f>IF($H94="","",V94-AE94)</f>
       </c>
     </row>
-    <row r="95" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="D95" s="2"/>
       <c r="G95" s="3"/>
@@ -22781,7 +22781,7 @@
         <f>IF($H95="","",V95-AE95)</f>
       </c>
     </row>
-    <row r="96" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="D96" s="2"/>
       <c r="G96" s="3"/>
@@ -22832,7 +22832,7 @@
         <f>IF($H96="","",V96-AE96)</f>
       </c>
     </row>
-    <row r="97" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="D97" s="2"/>
       <c r="G97" s="3"/>
@@ -22883,7 +22883,7 @@
         <f>IF($H97="","",V97-AE97)</f>
       </c>
     </row>
-    <row r="98" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="D98" s="2"/>
       <c r="G98" s="3"/>
@@ -22934,7 +22934,7 @@
         <f>IF($H98="","",V98-AE98)</f>
       </c>
     </row>
-    <row r="99" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="D99" s="2"/>
       <c r="G99" s="3"/>
@@ -22985,7 +22985,7 @@
         <f>IF($H99="","",V99-AE99)</f>
       </c>
     </row>
-    <row r="100" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
       <c r="D100" s="2"/>
       <c r="G100" s="3"/>
@@ -23036,7 +23036,7 @@
         <f>IF($H100="","",V100-AE100)</f>
       </c>
     </row>
-    <row r="101" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="D101" s="2"/>
       <c r="G101" s="3"/>
@@ -23087,7 +23087,7 @@
         <f>IF($H101="","",V101-AE101)</f>
       </c>
     </row>
-    <row r="102" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="D102" s="2"/>
       <c r="G102" s="3"/>
@@ -23138,7 +23138,7 @@
         <f>IF($H102="","",V102-AE102)</f>
       </c>
     </row>
-    <row r="103" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="D103" s="2"/>
       <c r="G103" s="3"/>
@@ -23189,7 +23189,7 @@
         <f>IF($H103="","",V103-AE103)</f>
       </c>
     </row>
-    <row r="104" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="D104" s="2"/>
       <c r="G104" s="3"/>
@@ -23240,7 +23240,7 @@
         <f>IF($H104="","",V104-AE104)</f>
       </c>
     </row>
-    <row r="105" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="D105" s="2"/>
       <c r="G105" s="3"/>
@@ -23291,7 +23291,7 @@
         <f>IF($H105="","",V105-AE105)</f>
       </c>
     </row>
-    <row r="106" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="D106" s="2"/>
       <c r="G106" s="3"/>
@@ -23342,7 +23342,7 @@
         <f>IF($H106="","",V106-AE106)</f>
       </c>
     </row>
-    <row r="107" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="D107" s="2"/>
       <c r="G107" s="3"/>
@@ -23393,7 +23393,7 @@
         <f>IF($H107="","",V107-AE107)</f>
       </c>
     </row>
-    <row r="108" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="D108" s="2"/>
       <c r="G108" s="3"/>
@@ -23444,7 +23444,7 @@
         <f>IF($H108="","",V108-AE108)</f>
       </c>
     </row>
-    <row r="109" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="D109" s="2"/>
       <c r="G109" s="3"/>
@@ -23495,7 +23495,7 @@
         <f>IF($H109="","",V109-AE109)</f>
       </c>
     </row>
-    <row r="110" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="D110" s="2"/>
       <c r="G110" s="3"/>
@@ -23546,7 +23546,7 @@
         <f>IF($H110="","",V110-AE110)</f>
       </c>
     </row>
-    <row r="111" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
       <c r="D111" s="2"/>
       <c r="G111" s="3"/>
@@ -23597,7 +23597,7 @@
         <f>IF($H111="","",V111-AE111)</f>
       </c>
     </row>
-    <row r="112" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="D112" s="2"/>
       <c r="G112" s="3"/>
@@ -23648,7 +23648,7 @@
         <f>IF($H112="","",V112-AE112)</f>
       </c>
     </row>
-    <row r="113" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="D113" s="2"/>
       <c r="G113" s="3"/>
@@ -23699,7 +23699,7 @@
         <f>IF($H113="","",V113-AE113)</f>
       </c>
     </row>
-    <row r="114" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="D114" s="2"/>
       <c r="G114" s="3"/>
@@ -23750,7 +23750,7 @@
         <f>IF($H114="","",V114-AE114)</f>
       </c>
     </row>
-    <row r="115" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="D115" s="2"/>
       <c r="G115" s="3"/>
@@ -23801,7 +23801,7 @@
         <f>IF($H115="","",V115-AE115)</f>
       </c>
     </row>
-    <row r="116" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="D116" s="2"/>
       <c r="G116" s="3"/>
@@ -23852,7 +23852,7 @@
         <f>IF($H116="","",V116-AE116)</f>
       </c>
     </row>
-    <row r="117" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="D117" s="2"/>
       <c r="G117" s="3"/>
@@ -23903,7 +23903,7 @@
         <f>IF($H117="","",V117-AE117)</f>
       </c>
     </row>
-    <row r="118" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="D118" s="2"/>
       <c r="G118" s="3"/>
@@ -23954,7 +23954,7 @@
         <f>IF($H118="","",V118-AE118)</f>
       </c>
     </row>
-    <row r="119" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="D119" s="2"/>
       <c r="G119" s="3"/>
@@ -24005,7 +24005,7 @@
         <f>IF($H119="","",V119-AE119)</f>
       </c>
     </row>
-    <row r="120" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="D120" s="2"/>
       <c r="G120" s="3"/>
@@ -24056,7 +24056,7 @@
         <f>IF($H120="","",V120-AE120)</f>
       </c>
     </row>
-    <row r="121" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="D121" s="2"/>
       <c r="G121" s="3"/>
@@ -24107,7 +24107,7 @@
         <f>IF($H121="","",V121-AE121)</f>
       </c>
     </row>
-    <row r="122" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="D122" s="2"/>
       <c r="G122" s="3"/>
@@ -24158,7 +24158,7 @@
         <f>IF($H122="","",V122-AE122)</f>
       </c>
     </row>
-    <row r="123" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="D123" s="2"/>
       <c r="G123" s="3"/>
@@ -24209,7 +24209,7 @@
         <f>IF($H123="","",V123-AE123)</f>
       </c>
     </row>
-    <row r="124" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="D124" s="2"/>
       <c r="G124" s="3"/>
@@ -24260,7 +24260,7 @@
         <f>IF($H124="","",V124-AE124)</f>
       </c>
     </row>
-    <row r="125" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="D125" s="2"/>
       <c r="G125" s="3"/>
@@ -24311,7 +24311,7 @@
         <f>IF($H125="","",V125-AE125)</f>
       </c>
     </row>
-    <row r="126" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="D126" s="2"/>
       <c r="G126" s="3"/>
@@ -24362,7 +24362,7 @@
         <f>IF($H126="","",V126-AE126)</f>
       </c>
     </row>
-    <row r="127" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="D127" s="2"/>
       <c r="G127" s="3"/>
@@ -24413,7 +24413,7 @@
         <f>IF($H127="","",V127-AE127)</f>
       </c>
     </row>
-    <row r="128" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A128" s="1"/>
       <c r="D128" s="2"/>
       <c r="G128" s="3"/>
@@ -24464,7 +24464,7 @@
         <f>IF($H128="","",V128-AE128)</f>
       </c>
     </row>
-    <row r="129" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A129" s="1"/>
       <c r="D129" s="2"/>
       <c r="G129" s="3"/>
@@ -24515,7 +24515,7 @@
         <f>IF($H129="","",V129-AE129)</f>
       </c>
     </row>
-    <row r="130" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A130" s="1"/>
       <c r="D130" s="2"/>
       <c r="G130" s="3"/>
@@ -24566,7 +24566,7 @@
         <f>IF($H130="","",V130-AE130)</f>
       </c>
     </row>
-    <row r="131" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A131" s="1"/>
       <c r="D131" s="2"/>
       <c r="G131" s="3"/>
@@ -24617,7 +24617,7 @@
         <f>IF($H131="","",V131-AE131)</f>
       </c>
     </row>
-    <row r="132" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A132" s="1"/>
       <c r="D132" s="2"/>
       <c r="G132" s="3"/>
@@ -24668,7 +24668,7 @@
         <f>IF($H132="","",V132-AE132)</f>
       </c>
     </row>
-    <row r="133" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
       <c r="D133" s="2"/>
       <c r="G133" s="3"/>
@@ -24719,7 +24719,7 @@
         <f>IF($H133="","",V133-AE133)</f>
       </c>
     </row>
-    <row r="134" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
       <c r="D134" s="2"/>
       <c r="G134" s="3"/>
@@ -24770,7 +24770,7 @@
         <f>IF($H134="","",V134-AE134)</f>
       </c>
     </row>
-    <row r="135" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A135" s="1"/>
       <c r="D135" s="2"/>
       <c r="G135" s="3"/>
@@ -24821,7 +24821,7 @@
         <f>IF($H135="","",V135-AE135)</f>
       </c>
     </row>
-    <row r="136" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A136" s="1"/>
       <c r="D136" s="2"/>
       <c r="G136" s="3"/>
@@ -24872,7 +24872,7 @@
         <f>IF($H136="","",V136-AE136)</f>
       </c>
     </row>
-    <row r="137" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A137" s="1"/>
       <c r="D137" s="2"/>
       <c r="G137" s="3"/>
@@ -24923,7 +24923,7 @@
         <f>IF($H137="","",V137-AE137)</f>
       </c>
     </row>
-    <row r="138" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A138" s="1"/>
       <c r="D138" s="2"/>
       <c r="G138" s="3"/>
@@ -24974,7 +24974,7 @@
         <f>IF($H138="","",V138-AE138)</f>
       </c>
     </row>
-    <row r="139" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A139" s="1"/>
       <c r="D139" s="2"/>
       <c r="G139" s="3"/>
@@ -25025,7 +25025,7 @@
         <f>IF($H139="","",V139-AE139)</f>
       </c>
     </row>
-    <row r="140" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A140" s="1"/>
       <c r="D140" s="2"/>
       <c r="G140" s="3"/>
@@ -25076,7 +25076,7 @@
         <f>IF($H140="","",V140-AE140)</f>
       </c>
     </row>
-    <row r="141" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="D141" s="2"/>
       <c r="G141" s="3"/>
@@ -25127,7 +25127,7 @@
         <f>IF($H141="","",V141-AE141)</f>
       </c>
     </row>
-    <row r="142" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A142" s="1"/>
       <c r="D142" s="2"/>
       <c r="G142" s="3"/>
@@ -25178,7 +25178,7 @@
         <f>IF($H142="","",V142-AE142)</f>
       </c>
     </row>
-    <row r="143" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="D143" s="2"/>
       <c r="G143" s="3"/>
@@ -25229,7 +25229,7 @@
         <f>IF($H143="","",V143-AE143)</f>
       </c>
     </row>
-    <row r="144" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="D144" s="2"/>
       <c r="G144" s="3"/>
@@ -25280,7 +25280,7 @@
         <f>IF($H144="","",V144-AE144)</f>
       </c>
     </row>
-    <row r="145" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A145" s="1"/>
       <c r="D145" s="2"/>
       <c r="G145" s="3"/>
@@ -25331,7 +25331,7 @@
         <f>IF($H145="","",V145-AE145)</f>
       </c>
     </row>
-    <row r="146" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
       <c r="D146" s="2"/>
       <c r="G146" s="3"/>
@@ -25382,7 +25382,7 @@
         <f>IF($H146="","",V146-AE146)</f>
       </c>
     </row>
-    <row r="147" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A147" s="1"/>
       <c r="D147" s="2"/>
       <c r="G147" s="3"/>
@@ -25433,7 +25433,7 @@
         <f>IF($H147="","",V147-AE147)</f>
       </c>
     </row>
-    <row r="148" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A148" s="1"/>
       <c r="D148" s="2"/>
       <c r="G148" s="3"/>
@@ -25484,7 +25484,7 @@
         <f>IF($H148="","",V148-AE148)</f>
       </c>
     </row>
-    <row r="149" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
       <c r="D149" s="2"/>
       <c r="G149" s="3"/>
@@ -25535,7 +25535,7 @@
         <f>IF($H149="","",V149-AE149)</f>
       </c>
     </row>
-    <row r="150" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A150" s="1"/>
       <c r="D150" s="2"/>
       <c r="G150" s="3"/>
@@ -25586,7 +25586,7 @@
         <f>IF($H150="","",V150-AE150)</f>
       </c>
     </row>
-    <row r="151" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
       <c r="D151" s="2"/>
       <c r="G151" s="3"/>
@@ -25637,7 +25637,7 @@
         <f>IF($H151="","",V151-AE151)</f>
       </c>
     </row>
-    <row r="152" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A152" s="1"/>
       <c r="D152" s="2"/>
       <c r="G152" s="3"/>
@@ -25688,7 +25688,7 @@
         <f>IF($H152="","",V152-AE152)</f>
       </c>
     </row>
-    <row r="153" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
       <c r="D153" s="2"/>
       <c r="G153" s="3"/>
@@ -25739,7 +25739,7 @@
         <f>IF($H153="","",V153-AE153)</f>
       </c>
     </row>
-    <row r="154" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
       <c r="D154" s="2"/>
       <c r="G154" s="3"/>
@@ -25790,7 +25790,7 @@
         <f>IF($H154="","",V154-AE154)</f>
       </c>
     </row>
-    <row r="155" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A155" s="1"/>
       <c r="D155" s="2"/>
       <c r="G155" s="3"/>
@@ -25841,7 +25841,7 @@
         <f>IF($H155="","",V155-AE155)</f>
       </c>
     </row>
-    <row r="156" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A156" s="1"/>
       <c r="D156" s="2"/>
       <c r="G156" s="3"/>
@@ -25892,7 +25892,7 @@
         <f>IF($H156="","",V156-AE156)</f>
       </c>
     </row>
-    <row r="157" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A157" s="1"/>
       <c r="D157" s="2"/>
       <c r="G157" s="3"/>
@@ -25943,7 +25943,7 @@
         <f>IF($H157="","",V157-AE157)</f>
       </c>
     </row>
-    <row r="158" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A158" s="1"/>
       <c r="D158" s="2"/>
       <c r="G158" s="3"/>
@@ -25994,7 +25994,7 @@
         <f>IF($H158="","",V158-AE158)</f>
       </c>
     </row>
-    <row r="159" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A159" s="1"/>
       <c r="D159" s="2"/>
       <c r="G159" s="3"/>
@@ -26045,7 +26045,7 @@
         <f>IF($H159="","",V159-AE159)</f>
       </c>
     </row>
-    <row r="160" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A160" s="1"/>
       <c r="D160" s="2"/>
       <c r="G160" s="3"/>
@@ -26096,7 +26096,7 @@
         <f>IF($H160="","",V160-AE160)</f>
       </c>
     </row>
-    <row r="161" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A161" s="1"/>
       <c r="D161" s="2"/>
       <c r="G161" s="3"/>
@@ -26147,7 +26147,7 @@
         <f>IF($H161="","",V161-AE161)</f>
       </c>
     </row>
-    <row r="162" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A162" s="1"/>
       <c r="D162" s="2"/>
       <c r="G162" s="3"/>
@@ -26198,7 +26198,7 @@
         <f>IF($H162="","",V162-AE162)</f>
       </c>
     </row>
-    <row r="163" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A163" s="1"/>
       <c r="D163" s="2"/>
       <c r="G163" s="3"/>
@@ -26249,7 +26249,7 @@
         <f>IF($H163="","",V163-AE163)</f>
       </c>
     </row>
-    <row r="164" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A164" s="1"/>
       <c r="D164" s="2"/>
       <c r="G164" s="3"/>
@@ -26300,7 +26300,7 @@
         <f>IF($H164="","",V164-AE164)</f>
       </c>
     </row>
-    <row r="165" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A165" s="1"/>
       <c r="D165" s="2"/>
       <c r="G165" s="3"/>
@@ -26351,7 +26351,7 @@
         <f>IF($H165="","",V165-AE165)</f>
       </c>
     </row>
-    <row r="166" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A166" s="1"/>
       <c r="D166" s="2"/>
       <c r="G166" s="3"/>
@@ -26402,7 +26402,7 @@
         <f>IF($H166="","",V166-AE166)</f>
       </c>
     </row>
-    <row r="167" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A167" s="1"/>
       <c r="D167" s="2"/>
       <c r="G167" s="3"/>
@@ -26453,7 +26453,7 @@
         <f>IF($H167="","",V167-AE167)</f>
       </c>
     </row>
-    <row r="168" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A168" s="1"/>
       <c r="D168" s="2"/>
       <c r="G168" s="3"/>
@@ -26504,7 +26504,7 @@
         <f>IF($H168="","",V168-AE168)</f>
       </c>
     </row>
-    <row r="169" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A169" s="1"/>
       <c r="D169" s="2"/>
       <c r="G169" s="3"/>
@@ -26555,7 +26555,7 @@
         <f>IF($H169="","",V169-AE169)</f>
       </c>
     </row>
-    <row r="170" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A170" s="1"/>
       <c r="D170" s="2"/>
       <c r="G170" s="3"/>
@@ -26606,7 +26606,7 @@
         <f>IF($H170="","",V170-AE170)</f>
       </c>
     </row>
-    <row r="171" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A171" s="1"/>
       <c r="D171" s="2"/>
       <c r="G171" s="3"/>
@@ -26657,7 +26657,7 @@
         <f>IF($H171="","",V171-AE171)</f>
       </c>
     </row>
-    <row r="172" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A172" s="1"/>
       <c r="D172" s="2"/>
       <c r="G172" s="3"/>
@@ -26708,7 +26708,7 @@
         <f>IF($H172="","",V172-AE172)</f>
       </c>
     </row>
-    <row r="173" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A173" s="1"/>
       <c r="D173" s="2"/>
       <c r="G173" s="3"/>
@@ -26759,7 +26759,7 @@
         <f>IF($H173="","",V173-AE173)</f>
       </c>
     </row>
-    <row r="174" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A174" s="1"/>
       <c r="D174" s="2"/>
       <c r="G174" s="3"/>
@@ -26810,7 +26810,7 @@
         <f>IF($H174="","",V174-AE174)</f>
       </c>
     </row>
-    <row r="175" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A175" s="1"/>
       <c r="D175" s="2"/>
       <c r="G175" s="3"/>
@@ -26861,7 +26861,7 @@
         <f>IF($H175="","",V175-AE175)</f>
       </c>
     </row>
-    <row r="176" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A176" s="1"/>
       <c r="D176" s="2"/>
       <c r="G176" s="3"/>
@@ -26912,7 +26912,7 @@
         <f>IF($H176="","",V176-AE176)</f>
       </c>
     </row>
-    <row r="177" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A177" s="1"/>
       <c r="D177" s="2"/>
       <c r="G177" s="3"/>
@@ -26963,7 +26963,7 @@
         <f>IF($H177="","",V177-AE177)</f>
       </c>
     </row>
-    <row r="178" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A178" s="1"/>
       <c r="D178" s="2"/>
       <c r="G178" s="3"/>
@@ -27014,7 +27014,7 @@
         <f>IF($H178="","",V178-AE178)</f>
       </c>
     </row>
-    <row r="179" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A179" s="1"/>
       <c r="D179" s="2"/>
       <c r="G179" s="3"/>
@@ -27065,7 +27065,7 @@
         <f>IF($H179="","",V179-AE179)</f>
       </c>
     </row>
-    <row r="180" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A180" s="1"/>
       <c r="D180" s="2"/>
       <c r="G180" s="3"/>
@@ -27116,7 +27116,7 @@
         <f>IF($H180="","",V180-AE180)</f>
       </c>
     </row>
-    <row r="181" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A181" s="1"/>
       <c r="D181" s="2"/>
       <c r="G181" s="3"/>
@@ -27167,7 +27167,7 @@
         <f>IF($H181="","",V181-AE181)</f>
       </c>
     </row>
-    <row r="182" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A182" s="1"/>
       <c r="D182" s="2"/>
       <c r="G182" s="3"/>
@@ -27218,7 +27218,7 @@
         <f>IF($H182="","",V182-AE182)</f>
       </c>
     </row>
-    <row r="183" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A183" s="1"/>
       <c r="D183" s="2"/>
       <c r="G183" s="3"/>
@@ -27269,7 +27269,7 @@
         <f>IF($H183="","",V183-AE183)</f>
       </c>
     </row>
-    <row r="184" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A184" s="1"/>
       <c r="D184" s="2"/>
       <c r="G184" s="3"/>
@@ -27320,7 +27320,7 @@
         <f>IF($H184="","",V184-AE184)</f>
       </c>
     </row>
-    <row r="185" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A185" s="1"/>
       <c r="D185" s="2"/>
       <c r="G185" s="3"/>
@@ -27371,7 +27371,7 @@
         <f>IF($H185="","",V185-AE185)</f>
       </c>
     </row>
-    <row r="186" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A186" s="1"/>
       <c r="D186" s="2"/>
       <c r="G186" s="3"/>
@@ -27422,7 +27422,7 @@
         <f>IF($H186="","",V186-AE186)</f>
       </c>
     </row>
-    <row r="187" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A187" s="1"/>
       <c r="D187" s="2"/>
       <c r="G187" s="3"/>
@@ -27473,7 +27473,7 @@
         <f>IF($H187="","",V187-AE187)</f>
       </c>
     </row>
-    <row r="188" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A188" s="1"/>
       <c r="D188" s="2"/>
       <c r="G188" s="3"/>
@@ -27524,7 +27524,7 @@
         <f>IF($H188="","",V188-AE188)</f>
       </c>
     </row>
-    <row r="189" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A189" s="1"/>
       <c r="D189" s="2"/>
       <c r="G189" s="3"/>
@@ -27575,7 +27575,7 @@
         <f>IF($H189="","",V189-AE189)</f>
       </c>
     </row>
-    <row r="190" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A190" s="1"/>
       <c r="D190" s="2"/>
       <c r="G190" s="3"/>
@@ -27626,7 +27626,7 @@
         <f>IF($H190="","",V190-AE190)</f>
       </c>
     </row>
-    <row r="191" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A191" s="1"/>
       <c r="D191" s="2"/>
       <c r="G191" s="3"/>
@@ -27677,7 +27677,7 @@
         <f>IF($H191="","",V191-AE191)</f>
       </c>
     </row>
-    <row r="192" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A192" s="1"/>
       <c r="D192" s="2"/>
       <c r="G192" s="3"/>
@@ -27728,7 +27728,7 @@
         <f>IF($H192="","",V192-AE192)</f>
       </c>
     </row>
-    <row r="193" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A193" s="1"/>
       <c r="D193" s="2"/>
       <c r="G193" s="3"/>
@@ -27779,7 +27779,7 @@
         <f>IF($H193="","",V193-AE193)</f>
       </c>
     </row>
-    <row r="194" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A194" s="1"/>
       <c r="D194" s="2"/>
       <c r="G194" s="3"/>
@@ -27830,7 +27830,7 @@
         <f>IF($H194="","",V194-AE194)</f>
       </c>
     </row>
-    <row r="195" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A195" s="1"/>
       <c r="D195" s="2"/>
       <c r="G195" s="3"/>
@@ -27881,7 +27881,7 @@
         <f>IF($H195="","",V195-AE195)</f>
       </c>
     </row>
-    <row r="196" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A196" s="1"/>
       <c r="D196" s="2"/>
       <c r="G196" s="3"/>
@@ -27932,7 +27932,7 @@
         <f>IF($H196="","",V196-AE196)</f>
       </c>
     </row>
-    <row r="197" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A197" s="1"/>
       <c r="D197" s="2"/>
       <c r="G197" s="3"/>
@@ -27983,7 +27983,7 @@
         <f>IF($H197="","",V197-AE197)</f>
       </c>
     </row>
-    <row r="198" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A198" s="1"/>
       <c r="D198" s="2"/>
       <c r="G198" s="3"/>
@@ -28034,7 +28034,7 @@
         <f>IF($H198="","",V198-AE198)</f>
       </c>
     </row>
-    <row r="199" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A199" s="1"/>
       <c r="D199" s="2"/>
       <c r="G199" s="3"/>
@@ -28085,7 +28085,7 @@
         <f>IF($H199="","",V199-AE199)</f>
       </c>
     </row>
-    <row r="200" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A200" s="1"/>
       <c r="D200" s="2"/>
       <c r="G200" s="3"/>
@@ -28136,7 +28136,7 @@
         <f>IF($H200="","",V200-AE200)</f>
       </c>
     </row>
-    <row r="201" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A201" s="1"/>
       <c r="D201" s="2"/>
       <c r="G201" s="3"/>
@@ -28187,7 +28187,7 @@
         <f>IF($H201="","",V201-AE201)</f>
       </c>
     </row>
-    <row r="202" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A202" s="1"/>
       <c r="D202" s="2"/>
       <c r="G202" s="3"/>
@@ -28438,37 +28438,37 @@
         <v>359</v>
       </c>
       <c r="H2" s="3">
-        <f>IF($G2="","",G2-F2)</f>
+        <f>G2-F2</f>
       </c>
       <c r="I2" s="3">
-        <f>IF($G2="","",H2*16.67%)</f>
+        <f>H2*16.67%</f>
       </c>
       <c r="J2" s="3">
-        <f>IF($G2="","",G2*7%)</f>
+        <f>G2*7%</f>
       </c>
       <c r="K2" s="3">
-        <f>IF($G2="","",J2*20%)</f>
+        <f>J2*20%</f>
       </c>
       <c r="L2" s="3">
         <v>8</v>
       </c>
       <c r="M2" s="3">
-        <f>IF($G2="","",L2*20%)</f>
+        <f>L2*20%</f>
       </c>
       <c r="N2" s="3">
         <v>1</v>
       </c>
       <c r="O2" s="3">
-        <f>IF($G2="","",K2+M2)</f>
+        <f>K2+M2</f>
       </c>
       <c r="P2" s="3">
-        <f>IF($G2="","",H2-I2-J2-K2-L2-M2-N2)</f>
+        <f>H2-I2-J2-K2-L2-M2-N2</f>
       </c>
       <c r="Q2" s="3">
-        <f>IF($G2="","",(P2-Y2)/F2*100)</f>
+        <f>(P2-Y2)/F2*100</f>
       </c>
       <c r="R2" s="3">
-        <f>IF($G2="","",I2-O2)</f>
+        <f>I2-O2</f>
       </c>
       <c r="S2" t="s">
         <v>35</v>
@@ -28477,7 +28477,7 @@
         <v>57</v>
       </c>
       <c r="Z2" s="3">
-        <f>IF($G2="","",P2-Y2)</f>
+        <f>P2-Y2</f>
       </c>
       <c r="AA2" t="s">
         <v>35</v>
@@ -28486,7 +28486,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="D3" s="2"/>
       <c r="F3" s="3"/>
@@ -28526,7 +28526,7 @@
         <f>IF($G3="","",P3-Y3)</f>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="D4" s="2"/>
       <c r="F4" s="3"/>
@@ -28566,7 +28566,7 @@
         <f>IF($G4="","",P4-Y4)</f>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="D5" s="2"/>
       <c r="F5" s="3"/>
@@ -28606,7 +28606,7 @@
         <f>IF($G5="","",P5-Y5)</f>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="D6" s="2"/>
       <c r="F6" s="3"/>
@@ -28646,7 +28646,7 @@
         <f>IF($G6="","",P6-Y6)</f>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="D7" s="2"/>
       <c r="F7" s="3"/>
@@ -28686,7 +28686,7 @@
         <f>IF($G7="","",P7-Y7)</f>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="D8" s="2"/>
       <c r="F8" s="3"/>
@@ -28726,7 +28726,7 @@
         <f>IF($G8="","",P8-Y8)</f>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="D9" s="2"/>
       <c r="F9" s="3"/>
@@ -28766,7 +28766,7 @@
         <f>IF($G9="","",P9-Y9)</f>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="D10" s="2"/>
       <c r="F10" s="3"/>
@@ -28806,7 +28806,7 @@
         <f>IF($G10="","",P10-Y10)</f>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="D11" s="2"/>
       <c r="F11" s="3"/>
@@ -28846,7 +28846,7 @@
         <f>IF($G11="","",P11-Y11)</f>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="D12" s="2"/>
       <c r="F12" s="3"/>
@@ -28886,7 +28886,7 @@
         <f>IF($G12="","",P12-Y12)</f>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="D13" s="2"/>
       <c r="F13" s="3"/>
@@ -28926,7 +28926,7 @@
         <f>IF($G13="","",P13-Y13)</f>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="D14" s="2"/>
       <c r="F14" s="3"/>
@@ -28966,7 +28966,7 @@
         <f>IF($G14="","",P14-Y14)</f>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="D15" s="2"/>
       <c r="F15" s="3"/>
@@ -29006,7 +29006,7 @@
         <f>IF($G15="","",P15-Y15)</f>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="D16" s="2"/>
       <c r="F16" s="3"/>
@@ -29046,7 +29046,7 @@
         <f>IF($G16="","",P16-Y16)</f>
       </c>
     </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="D17" s="2"/>
       <c r="F17" s="3"/>
@@ -29086,7 +29086,7 @@
         <f>IF($G17="","",P17-Y17)</f>
       </c>
     </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="D18" s="2"/>
       <c r="F18" s="3"/>
@@ -29126,7 +29126,7 @@
         <f>IF($G18="","",P18-Y18)</f>
       </c>
     </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="D19" s="2"/>
       <c r="F19" s="3"/>
@@ -29166,7 +29166,7 @@
         <f>IF($G19="","",P19-Y19)</f>
       </c>
     </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="D20" s="2"/>
       <c r="F20" s="3"/>
@@ -29206,7 +29206,7 @@
         <f>IF($G20="","",P20-Y20)</f>
       </c>
     </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="D21" s="2"/>
       <c r="F21" s="3"/>
@@ -29246,7 +29246,7 @@
         <f>IF($G21="","",P21-Y21)</f>
       </c>
     </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="D22" s="2"/>
       <c r="F22" s="3"/>
@@ -29286,7 +29286,7 @@
         <f>IF($G22="","",P22-Y22)</f>
       </c>
     </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="D23" s="2"/>
       <c r="F23" s="3"/>
@@ -29326,7 +29326,7 @@
         <f>IF($G23="","",P23-Y23)</f>
       </c>
     </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="D24" s="2"/>
       <c r="F24" s="3"/>
@@ -29366,7 +29366,7 @@
         <f>IF($G24="","",P24-Y24)</f>
       </c>
     </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="D25" s="2"/>
       <c r="F25" s="3"/>
@@ -29406,7 +29406,7 @@
         <f>IF($G25="","",P25-Y25)</f>
       </c>
     </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="D26" s="2"/>
       <c r="F26" s="3"/>
@@ -29446,7 +29446,7 @@
         <f>IF($G26="","",P26-Y26)</f>
       </c>
     </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="D27" s="2"/>
       <c r="F27" s="3"/>
@@ -29486,7 +29486,7 @@
         <f>IF($G27="","",P27-Y27)</f>
       </c>
     </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="D28" s="2"/>
       <c r="F28" s="3"/>
@@ -29526,7 +29526,7 @@
         <f>IF($G28="","",P28-Y28)</f>
       </c>
     </row>
-    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="D29" s="2"/>
       <c r="F29" s="3"/>
@@ -29566,7 +29566,7 @@
         <f>IF($G29="","",P29-Y29)</f>
       </c>
     </row>
-    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="D30" s="2"/>
       <c r="F30" s="3"/>
@@ -29606,7 +29606,7 @@
         <f>IF($G30="","",P30-Y30)</f>
       </c>
     </row>
-    <row r="31" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="D31" s="2"/>
       <c r="F31" s="3"/>
@@ -29646,7 +29646,7 @@
         <f>IF($G31="","",P31-Y31)</f>
       </c>
     </row>
-    <row r="32" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="D32" s="2"/>
       <c r="F32" s="3"/>
@@ -29686,7 +29686,7 @@
         <f>IF($G32="","",P32-Y32)</f>
       </c>
     </row>
-    <row r="33" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="D33" s="2"/>
       <c r="F33" s="3"/>
@@ -29726,7 +29726,7 @@
         <f>IF($G33="","",P33-Y33)</f>
       </c>
     </row>
-    <row r="34" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="D34" s="2"/>
       <c r="F34" s="3"/>
@@ -29766,7 +29766,7 @@
         <f>IF($G34="","",P34-Y34)</f>
       </c>
     </row>
-    <row r="35" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="D35" s="2"/>
       <c r="F35" s="3"/>
@@ -29806,7 +29806,7 @@
         <f>IF($G35="","",P35-Y35)</f>
       </c>
     </row>
-    <row r="36" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="D36" s="2"/>
       <c r="F36" s="3"/>
@@ -29846,7 +29846,7 @@
         <f>IF($G36="","",P36-Y36)</f>
       </c>
     </row>
-    <row r="37" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="D37" s="2"/>
       <c r="F37" s="3"/>
@@ -29886,7 +29886,7 @@
         <f>IF($G37="","",P37-Y37)</f>
       </c>
     </row>
-    <row r="38" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="D38" s="2"/>
       <c r="F38" s="3"/>
@@ -29926,7 +29926,7 @@
         <f>IF($G38="","",P38-Y38)</f>
       </c>
     </row>
-    <row r="39" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="D39" s="2"/>
       <c r="F39" s="3"/>
@@ -29966,7 +29966,7 @@
         <f>IF($G39="","",P39-Y39)</f>
       </c>
     </row>
-    <row r="40" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="D40" s="2"/>
       <c r="F40" s="3"/>
@@ -30006,7 +30006,7 @@
         <f>IF($G40="","",P40-Y40)</f>
       </c>
     </row>
-    <row r="41" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="D41" s="2"/>
       <c r="F41" s="3"/>
@@ -30046,7 +30046,7 @@
         <f>IF($G41="","",P41-Y41)</f>
       </c>
     </row>
-    <row r="42" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="D42" s="2"/>
       <c r="F42" s="3"/>
@@ -30086,7 +30086,7 @@
         <f>IF($G42="","",P42-Y42)</f>
       </c>
     </row>
-    <row r="43" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="D43" s="2"/>
       <c r="F43" s="3"/>
@@ -30126,7 +30126,7 @@
         <f>IF($G43="","",P43-Y43)</f>
       </c>
     </row>
-    <row r="44" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="D44" s="2"/>
       <c r="F44" s="3"/>
@@ -30166,7 +30166,7 @@
         <f>IF($G44="","",P44-Y44)</f>
       </c>
     </row>
-    <row r="45" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="D45" s="2"/>
       <c r="F45" s="3"/>
@@ -30206,7 +30206,7 @@
         <f>IF($G45="","",P45-Y45)</f>
       </c>
     </row>
-    <row r="46" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="D46" s="2"/>
       <c r="F46" s="3"/>
@@ -30246,7 +30246,7 @@
         <f>IF($G46="","",P46-Y46)</f>
       </c>
     </row>
-    <row r="47" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="D47" s="2"/>
       <c r="F47" s="3"/>
@@ -30286,7 +30286,7 @@
         <f>IF($G47="","",P47-Y47)</f>
       </c>
     </row>
-    <row r="48" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="D48" s="2"/>
       <c r="F48" s="3"/>
@@ -30326,7 +30326,7 @@
         <f>IF($G48="","",P48-Y48)</f>
       </c>
     </row>
-    <row r="49" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
       <c r="D49" s="2"/>
       <c r="F49" s="3"/>
@@ -30366,7 +30366,7 @@
         <f>IF($G49="","",P49-Y49)</f>
       </c>
     </row>
-    <row r="50" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
       <c r="D50" s="2"/>
       <c r="F50" s="3"/>
@@ -30406,7 +30406,7 @@
         <f>IF($G50="","",P50-Y50)</f>
       </c>
     </row>
-    <row r="51" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
       <c r="D51" s="2"/>
       <c r="F51" s="3"/>
@@ -30446,7 +30446,7 @@
         <f>IF($G51="","",P51-Y51)</f>
       </c>
     </row>
-    <row r="52" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
       <c r="D52" s="2"/>
       <c r="F52" s="3"/>
@@ -30486,7 +30486,7 @@
         <f>IF($G52="","",P52-Y52)</f>
       </c>
     </row>
-    <row r="53" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
       <c r="D53" s="2"/>
       <c r="F53" s="3"/>
@@ -30526,7 +30526,7 @@
         <f>IF($G53="","",P53-Y53)</f>
       </c>
     </row>
-    <row r="54" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
       <c r="D54" s="2"/>
       <c r="F54" s="3"/>
@@ -30566,7 +30566,7 @@
         <f>IF($G54="","",P54-Y54)</f>
       </c>
     </row>
-    <row r="55" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
       <c r="D55" s="2"/>
       <c r="F55" s="3"/>
@@ -30606,7 +30606,7 @@
         <f>IF($G55="","",P55-Y55)</f>
       </c>
     </row>
-    <row r="56" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
       <c r="D56" s="2"/>
       <c r="F56" s="3"/>
@@ -30646,7 +30646,7 @@
         <f>IF($G56="","",P56-Y56)</f>
       </c>
     </row>
-    <row r="57" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
       <c r="D57" s="2"/>
       <c r="F57" s="3"/>
@@ -30686,7 +30686,7 @@
         <f>IF($G57="","",P57-Y57)</f>
       </c>
     </row>
-    <row r="58" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
       <c r="D58" s="2"/>
       <c r="F58" s="3"/>
@@ -30726,7 +30726,7 @@
         <f>IF($G58="","",P58-Y58)</f>
       </c>
     </row>
-    <row r="59" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
       <c r="D59" s="2"/>
       <c r="F59" s="3"/>
@@ -30766,7 +30766,7 @@
         <f>IF($G59="","",P59-Y59)</f>
       </c>
     </row>
-    <row r="60" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
       <c r="D60" s="2"/>
       <c r="F60" s="3"/>
@@ -30806,7 +30806,7 @@
         <f>IF($G60="","",P60-Y60)</f>
       </c>
     </row>
-    <row r="61" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
       <c r="D61" s="2"/>
       <c r="F61" s="3"/>
@@ -30846,7 +30846,7 @@
         <f>IF($G61="","",P61-Y61)</f>
       </c>
     </row>
-    <row r="62" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
       <c r="D62" s="2"/>
       <c r="F62" s="3"/>
@@ -30886,7 +30886,7 @@
         <f>IF($G62="","",P62-Y62)</f>
       </c>
     </row>
-    <row r="63" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
       <c r="D63" s="2"/>
       <c r="F63" s="3"/>
@@ -30926,7 +30926,7 @@
         <f>IF($G63="","",P63-Y63)</f>
       </c>
     </row>
-    <row r="64" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
       <c r="D64" s="2"/>
       <c r="F64" s="3"/>
@@ -30966,7 +30966,7 @@
         <f>IF($G64="","",P64-Y64)</f>
       </c>
     </row>
-    <row r="65" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
       <c r="D65" s="2"/>
       <c r="F65" s="3"/>
@@ -31006,7 +31006,7 @@
         <f>IF($G65="","",P65-Y65)</f>
       </c>
     </row>
-    <row r="66" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
       <c r="D66" s="2"/>
       <c r="F66" s="3"/>
@@ -31046,7 +31046,7 @@
         <f>IF($G66="","",P66-Y66)</f>
       </c>
     </row>
-    <row r="67" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
       <c r="D67" s="2"/>
       <c r="F67" s="3"/>
@@ -31086,7 +31086,7 @@
         <f>IF($G67="","",P67-Y67)</f>
       </c>
     </row>
-    <row r="68" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
       <c r="D68" s="2"/>
       <c r="F68" s="3"/>
@@ -31126,7 +31126,7 @@
         <f>IF($G68="","",P68-Y68)</f>
       </c>
     </row>
-    <row r="69" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
       <c r="D69" s="2"/>
       <c r="F69" s="3"/>
@@ -31166,7 +31166,7 @@
         <f>IF($G69="","",P69-Y69)</f>
       </c>
     </row>
-    <row r="70" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
       <c r="D70" s="2"/>
       <c r="F70" s="3"/>
@@ -31206,7 +31206,7 @@
         <f>IF($G70="","",P70-Y70)</f>
       </c>
     </row>
-    <row r="71" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
       <c r="D71" s="2"/>
       <c r="F71" s="3"/>
@@ -31246,7 +31246,7 @@
         <f>IF($G71="","",P71-Y71)</f>
       </c>
     </row>
-    <row r="72" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
       <c r="D72" s="2"/>
       <c r="F72" s="3"/>
@@ -31286,7 +31286,7 @@
         <f>IF($G72="","",P72-Y72)</f>
       </c>
     </row>
-    <row r="73" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
       <c r="D73" s="2"/>
       <c r="F73" s="3"/>
@@ -31326,7 +31326,7 @@
         <f>IF($G73="","",P73-Y73)</f>
       </c>
     </row>
-    <row r="74" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
       <c r="D74" s="2"/>
       <c r="F74" s="3"/>
@@ -31366,7 +31366,7 @@
         <f>IF($G74="","",P74-Y74)</f>
       </c>
     </row>
-    <row r="75" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
       <c r="D75" s="2"/>
       <c r="F75" s="3"/>
@@ -31406,7 +31406,7 @@
         <f>IF($G75="","",P75-Y75)</f>
       </c>
     </row>
-    <row r="76" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
       <c r="D76" s="2"/>
       <c r="F76" s="3"/>
@@ -31446,7 +31446,7 @@
         <f>IF($G76="","",P76-Y76)</f>
       </c>
     </row>
-    <row r="77" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
       <c r="D77" s="2"/>
       <c r="F77" s="3"/>
@@ -31486,7 +31486,7 @@
         <f>IF($G77="","",P77-Y77)</f>
       </c>
     </row>
-    <row r="78" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
       <c r="D78" s="2"/>
       <c r="F78" s="3"/>
@@ -31526,7 +31526,7 @@
         <f>IF($G78="","",P78-Y78)</f>
       </c>
     </row>
-    <row r="79" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="D79" s="2"/>
       <c r="F79" s="3"/>
@@ -31566,7 +31566,7 @@
         <f>IF($G79="","",P79-Y79)</f>
       </c>
     </row>
-    <row r="80" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
       <c r="D80" s="2"/>
       <c r="F80" s="3"/>
@@ -31606,7 +31606,7 @@
         <f>IF($G80="","",P80-Y80)</f>
       </c>
     </row>
-    <row r="81" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
       <c r="D81" s="2"/>
       <c r="F81" s="3"/>
@@ -31646,7 +31646,7 @@
         <f>IF($G81="","",P81-Y81)</f>
       </c>
     </row>
-    <row r="82" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
       <c r="D82" s="2"/>
       <c r="F82" s="3"/>
@@ -31686,7 +31686,7 @@
         <f>IF($G82="","",P82-Y82)</f>
       </c>
     </row>
-    <row r="83" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
       <c r="D83" s="2"/>
       <c r="F83" s="3"/>
@@ -31726,7 +31726,7 @@
         <f>IF($G83="","",P83-Y83)</f>
       </c>
     </row>
-    <row r="84" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
       <c r="D84" s="2"/>
       <c r="F84" s="3"/>
@@ -31766,7 +31766,7 @@
         <f>IF($G84="","",P84-Y84)</f>
       </c>
     </row>
-    <row r="85" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="D85" s="2"/>
       <c r="F85" s="3"/>
@@ -31806,7 +31806,7 @@
         <f>IF($G85="","",P85-Y85)</f>
       </c>
     </row>
-    <row r="86" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="D86" s="2"/>
       <c r="F86" s="3"/>
@@ -31846,7 +31846,7 @@
         <f>IF($G86="","",P86-Y86)</f>
       </c>
     </row>
-    <row r="87" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="D87" s="2"/>
       <c r="F87" s="3"/>
@@ -31886,7 +31886,7 @@
         <f>IF($G87="","",P87-Y87)</f>
       </c>
     </row>
-    <row r="88" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="D88" s="2"/>
       <c r="F88" s="3"/>
@@ -31926,7 +31926,7 @@
         <f>IF($G88="","",P88-Y88)</f>
       </c>
     </row>
-    <row r="89" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="D89" s="2"/>
       <c r="F89" s="3"/>
@@ -31966,7 +31966,7 @@
         <f>IF($G89="","",P89-Y89)</f>
       </c>
     </row>
-    <row r="90" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="D90" s="2"/>
       <c r="F90" s="3"/>
@@ -32006,7 +32006,7 @@
         <f>IF($G90="","",P90-Y90)</f>
       </c>
     </row>
-    <row r="91" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="D91" s="2"/>
       <c r="F91" s="3"/>
@@ -32046,7 +32046,7 @@
         <f>IF($G91="","",P91-Y91)</f>
       </c>
     </row>
-    <row r="92" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="D92" s="2"/>
       <c r="F92" s="3"/>
@@ -32086,7 +32086,7 @@
         <f>IF($G92="","",P92-Y92)</f>
       </c>
     </row>
-    <row r="93" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="D93" s="2"/>
       <c r="F93" s="3"/>
@@ -32126,7 +32126,7 @@
         <f>IF($G93="","",P93-Y93)</f>
       </c>
     </row>
-    <row r="94" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="D94" s="2"/>
       <c r="F94" s="3"/>
@@ -32166,7 +32166,7 @@
         <f>IF($G94="","",P94-Y94)</f>
       </c>
     </row>
-    <row r="95" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="D95" s="2"/>
       <c r="F95" s="3"/>
@@ -32206,7 +32206,7 @@
         <f>IF($G95="","",P95-Y95)</f>
       </c>
     </row>
-    <row r="96" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="D96" s="2"/>
       <c r="F96" s="3"/>
@@ -32246,7 +32246,7 @@
         <f>IF($G96="","",P96-Y96)</f>
       </c>
     </row>
-    <row r="97" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="D97" s="2"/>
       <c r="F97" s="3"/>
@@ -32286,7 +32286,7 @@
         <f>IF($G97="","",P97-Y97)</f>
       </c>
     </row>
-    <row r="98" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="D98" s="2"/>
       <c r="F98" s="3"/>
@@ -32326,7 +32326,7 @@
         <f>IF($G98="","",P98-Y98)</f>
       </c>
     </row>
-    <row r="99" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="D99" s="2"/>
       <c r="F99" s="3"/>
@@ -32366,7 +32366,7 @@
         <f>IF($G99="","",P99-Y99)</f>
       </c>
     </row>
-    <row r="100" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
       <c r="D100" s="2"/>
       <c r="F100" s="3"/>
@@ -32406,7 +32406,7 @@
         <f>IF($G100="","",P100-Y100)</f>
       </c>
     </row>
-    <row r="101" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="D101" s="2"/>
       <c r="F101" s="3"/>
@@ -32446,7 +32446,7 @@
         <f>IF($G101="","",P101-Y101)</f>
       </c>
     </row>
-    <row r="102" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="D102" s="2"/>
       <c r="F102" s="3"/>
@@ -32486,7 +32486,7 @@
         <f>IF($G102="","",P102-Y102)</f>
       </c>
     </row>
-    <row r="103" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="D103" s="2"/>
       <c r="F103" s="3"/>
@@ -32526,7 +32526,7 @@
         <f>IF($G103="","",P103-Y103)</f>
       </c>
     </row>
-    <row r="104" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="D104" s="2"/>
       <c r="F104" s="3"/>
@@ -32566,7 +32566,7 @@
         <f>IF($G104="","",P104-Y104)</f>
       </c>
     </row>
-    <row r="105" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="D105" s="2"/>
       <c r="F105" s="3"/>
@@ -32606,7 +32606,7 @@
         <f>IF($G105="","",P105-Y105)</f>
       </c>
     </row>
-    <row r="106" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="D106" s="2"/>
       <c r="F106" s="3"/>
@@ -32646,7 +32646,7 @@
         <f>IF($G106="","",P106-Y106)</f>
       </c>
     </row>
-    <row r="107" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="D107" s="2"/>
       <c r="F107" s="3"/>
@@ -32686,7 +32686,7 @@
         <f>IF($G107="","",P107-Y107)</f>
       </c>
     </row>
-    <row r="108" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="D108" s="2"/>
       <c r="F108" s="3"/>
@@ -32726,7 +32726,7 @@
         <f>IF($G108="","",P108-Y108)</f>
       </c>
     </row>
-    <row r="109" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="D109" s="2"/>
       <c r="F109" s="3"/>
@@ -32766,7 +32766,7 @@
         <f>IF($G109="","",P109-Y109)</f>
       </c>
     </row>
-    <row r="110" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="D110" s="2"/>
       <c r="F110" s="3"/>
@@ -32806,7 +32806,7 @@
         <f>IF($G110="","",P110-Y110)</f>
       </c>
     </row>
-    <row r="111" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
       <c r="D111" s="2"/>
       <c r="F111" s="3"/>
@@ -32846,7 +32846,7 @@
         <f>IF($G111="","",P111-Y111)</f>
       </c>
     </row>
-    <row r="112" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="D112" s="2"/>
       <c r="F112" s="3"/>
@@ -32886,7 +32886,7 @@
         <f>IF($G112="","",P112-Y112)</f>
       </c>
     </row>
-    <row r="113" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="D113" s="2"/>
       <c r="F113" s="3"/>
@@ -32926,7 +32926,7 @@
         <f>IF($G113="","",P113-Y113)</f>
       </c>
     </row>
-    <row r="114" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="D114" s="2"/>
       <c r="F114" s="3"/>
@@ -32966,7 +32966,7 @@
         <f>IF($G114="","",P114-Y114)</f>
       </c>
     </row>
-    <row r="115" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="D115" s="2"/>
       <c r="F115" s="3"/>
@@ -33006,7 +33006,7 @@
         <f>IF($G115="","",P115-Y115)</f>
       </c>
     </row>
-    <row r="116" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="D116" s="2"/>
       <c r="F116" s="3"/>
@@ -33046,7 +33046,7 @@
         <f>IF($G116="","",P116-Y116)</f>
       </c>
     </row>
-    <row r="117" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="D117" s="2"/>
       <c r="F117" s="3"/>
@@ -33086,7 +33086,7 @@
         <f>IF($G117="","",P117-Y117)</f>
       </c>
     </row>
-    <row r="118" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="D118" s="2"/>
       <c r="F118" s="3"/>
@@ -33126,7 +33126,7 @@
         <f>IF($G118="","",P118-Y118)</f>
       </c>
     </row>
-    <row r="119" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="D119" s="2"/>
       <c r="F119" s="3"/>
@@ -33166,7 +33166,7 @@
         <f>IF($G119="","",P119-Y119)</f>
       </c>
     </row>
-    <row r="120" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="D120" s="2"/>
       <c r="F120" s="3"/>
@@ -33206,7 +33206,7 @@
         <f>IF($G120="","",P120-Y120)</f>
       </c>
     </row>
-    <row r="121" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="D121" s="2"/>
       <c r="F121" s="3"/>
@@ -33246,7 +33246,7 @@
         <f>IF($G121="","",P121-Y121)</f>
       </c>
     </row>
-    <row r="122" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="D122" s="2"/>
       <c r="F122" s="3"/>
@@ -33286,7 +33286,7 @@
         <f>IF($G122="","",P122-Y122)</f>
       </c>
     </row>
-    <row r="123" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="D123" s="2"/>
       <c r="F123" s="3"/>
@@ -33326,7 +33326,7 @@
         <f>IF($G123="","",P123-Y123)</f>
       </c>
     </row>
-    <row r="124" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="D124" s="2"/>
       <c r="F124" s="3"/>
@@ -33366,7 +33366,7 @@
         <f>IF($G124="","",P124-Y124)</f>
       </c>
     </row>
-    <row r="125" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="D125" s="2"/>
       <c r="F125" s="3"/>
@@ -33406,7 +33406,7 @@
         <f>IF($G125="","",P125-Y125)</f>
       </c>
     </row>
-    <row r="126" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="D126" s="2"/>
       <c r="F126" s="3"/>
@@ -33446,7 +33446,7 @@
         <f>IF($G126="","",P126-Y126)</f>
       </c>
     </row>
-    <row r="127" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="D127" s="2"/>
       <c r="F127" s="3"/>
@@ -33486,7 +33486,7 @@
         <f>IF($G127="","",P127-Y127)</f>
       </c>
     </row>
-    <row r="128" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A128" s="1"/>
       <c r="D128" s="2"/>
       <c r="F128" s="3"/>
@@ -33526,7 +33526,7 @@
         <f>IF($G128="","",P128-Y128)</f>
       </c>
     </row>
-    <row r="129" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A129" s="1"/>
       <c r="D129" s="2"/>
       <c r="F129" s="3"/>
@@ -33566,7 +33566,7 @@
         <f>IF($G129="","",P129-Y129)</f>
       </c>
     </row>
-    <row r="130" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A130" s="1"/>
       <c r="D130" s="2"/>
       <c r="F130" s="3"/>
@@ -33606,7 +33606,7 @@
         <f>IF($G130="","",P130-Y130)</f>
       </c>
     </row>
-    <row r="131" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A131" s="1"/>
       <c r="D131" s="2"/>
       <c r="F131" s="3"/>
@@ -33646,7 +33646,7 @@
         <f>IF($G131="","",P131-Y131)</f>
       </c>
     </row>
-    <row r="132" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A132" s="1"/>
       <c r="D132" s="2"/>
       <c r="F132" s="3"/>
@@ -33686,7 +33686,7 @@
         <f>IF($G132="","",P132-Y132)</f>
       </c>
     </row>
-    <row r="133" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
       <c r="D133" s="2"/>
       <c r="F133" s="3"/>
@@ -33726,7 +33726,7 @@
         <f>IF($G133="","",P133-Y133)</f>
       </c>
     </row>
-    <row r="134" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
       <c r="D134" s="2"/>
       <c r="F134" s="3"/>
@@ -33766,7 +33766,7 @@
         <f>IF($G134="","",P134-Y134)</f>
       </c>
     </row>
-    <row r="135" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A135" s="1"/>
       <c r="D135" s="2"/>
       <c r="F135" s="3"/>
@@ -33806,7 +33806,7 @@
         <f>IF($G135="","",P135-Y135)</f>
       </c>
     </row>
-    <row r="136" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A136" s="1"/>
       <c r="D136" s="2"/>
       <c r="F136" s="3"/>
@@ -33846,7 +33846,7 @@
         <f>IF($G136="","",P136-Y136)</f>
       </c>
     </row>
-    <row r="137" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A137" s="1"/>
       <c r="D137" s="2"/>
       <c r="F137" s="3"/>
@@ -33886,7 +33886,7 @@
         <f>IF($G137="","",P137-Y137)</f>
       </c>
     </row>
-    <row r="138" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A138" s="1"/>
       <c r="D138" s="2"/>
       <c r="F138" s="3"/>
@@ -33926,7 +33926,7 @@
         <f>IF($G138="","",P138-Y138)</f>
       </c>
     </row>
-    <row r="139" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A139" s="1"/>
       <c r="D139" s="2"/>
       <c r="F139" s="3"/>
@@ -33966,7 +33966,7 @@
         <f>IF($G139="","",P139-Y139)</f>
       </c>
     </row>
-    <row r="140" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A140" s="1"/>
       <c r="D140" s="2"/>
       <c r="F140" s="3"/>
@@ -34006,7 +34006,7 @@
         <f>IF($G140="","",P140-Y140)</f>
       </c>
     </row>
-    <row r="141" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="D141" s="2"/>
       <c r="F141" s="3"/>
@@ -34046,7 +34046,7 @@
         <f>IF($G141="","",P141-Y141)</f>
       </c>
     </row>
-    <row r="142" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A142" s="1"/>
       <c r="D142" s="2"/>
       <c r="F142" s="3"/>
@@ -34086,7 +34086,7 @@
         <f>IF($G142="","",P142-Y142)</f>
       </c>
     </row>
-    <row r="143" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="D143" s="2"/>
       <c r="F143" s="3"/>
@@ -34126,7 +34126,7 @@
         <f>IF($G143="","",P143-Y143)</f>
       </c>
     </row>
-    <row r="144" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="D144" s="2"/>
       <c r="F144" s="3"/>
@@ -34166,7 +34166,7 @@
         <f>IF($G144="","",P144-Y144)</f>
       </c>
     </row>
-    <row r="145" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A145" s="1"/>
       <c r="D145" s="2"/>
       <c r="F145" s="3"/>
@@ -34206,7 +34206,7 @@
         <f>IF($G145="","",P145-Y145)</f>
       </c>
     </row>
-    <row r="146" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
       <c r="D146" s="2"/>
       <c r="F146" s="3"/>
@@ -34246,7 +34246,7 @@
         <f>IF($G146="","",P146-Y146)</f>
       </c>
     </row>
-    <row r="147" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A147" s="1"/>
       <c r="D147" s="2"/>
       <c r="F147" s="3"/>
@@ -34286,7 +34286,7 @@
         <f>IF($G147="","",P147-Y147)</f>
       </c>
     </row>
-    <row r="148" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A148" s="1"/>
       <c r="D148" s="2"/>
       <c r="F148" s="3"/>
@@ -34326,7 +34326,7 @@
         <f>IF($G148="","",P148-Y148)</f>
       </c>
     </row>
-    <row r="149" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
       <c r="D149" s="2"/>
       <c r="F149" s="3"/>
@@ -34366,7 +34366,7 @@
         <f>IF($G149="","",P149-Y149)</f>
       </c>
     </row>
-    <row r="150" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A150" s="1"/>
       <c r="D150" s="2"/>
       <c r="F150" s="3"/>
@@ -34406,7 +34406,7 @@
         <f>IF($G150="","",P150-Y150)</f>
       </c>
     </row>
-    <row r="151" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
       <c r="D151" s="2"/>
       <c r="F151" s="3"/>
@@ -34446,7 +34446,7 @@
         <f>IF($G151="","",P151-Y151)</f>
       </c>
     </row>
-    <row r="152" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A152" s="1"/>
       <c r="D152" s="2"/>
       <c r="F152" s="3"/>
@@ -34486,7 +34486,7 @@
         <f>IF($G152="","",P152-Y152)</f>
       </c>
     </row>
-    <row r="153" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
       <c r="D153" s="2"/>
       <c r="F153" s="3"/>
@@ -34526,7 +34526,7 @@
         <f>IF($G153="","",P153-Y153)</f>
       </c>
     </row>
-    <row r="154" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
       <c r="D154" s="2"/>
       <c r="F154" s="3"/>
@@ -34566,7 +34566,7 @@
         <f>IF($G154="","",P154-Y154)</f>
       </c>
     </row>
-    <row r="155" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A155" s="1"/>
       <c r="D155" s="2"/>
       <c r="F155" s="3"/>
@@ -34606,7 +34606,7 @@
         <f>IF($G155="","",P155-Y155)</f>
       </c>
     </row>
-    <row r="156" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A156" s="1"/>
       <c r="D156" s="2"/>
       <c r="F156" s="3"/>
@@ -34646,7 +34646,7 @@
         <f>IF($G156="","",P156-Y156)</f>
       </c>
     </row>
-    <row r="157" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A157" s="1"/>
       <c r="D157" s="2"/>
       <c r="F157" s="3"/>
@@ -34686,7 +34686,7 @@
         <f>IF($G157="","",P157-Y157)</f>
       </c>
     </row>
-    <row r="158" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A158" s="1"/>
       <c r="D158" s="2"/>
       <c r="F158" s="3"/>
@@ -34726,7 +34726,7 @@
         <f>IF($G158="","",P158-Y158)</f>
       </c>
     </row>
-    <row r="159" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A159" s="1"/>
       <c r="D159" s="2"/>
       <c r="F159" s="3"/>
@@ -34766,7 +34766,7 @@
         <f>IF($G159="","",P159-Y159)</f>
       </c>
     </row>
-    <row r="160" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A160" s="1"/>
       <c r="D160" s="2"/>
       <c r="F160" s="3"/>
@@ -34806,7 +34806,7 @@
         <f>IF($G160="","",P160-Y160)</f>
       </c>
     </row>
-    <row r="161" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A161" s="1"/>
       <c r="D161" s="2"/>
       <c r="F161" s="3"/>
@@ -34846,7 +34846,7 @@
         <f>IF($G161="","",P161-Y161)</f>
       </c>
     </row>
-    <row r="162" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A162" s="1"/>
       <c r="D162" s="2"/>
       <c r="F162" s="3"/>
@@ -34886,7 +34886,7 @@
         <f>IF($G162="","",P162-Y162)</f>
       </c>
     </row>
-    <row r="163" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A163" s="1"/>
       <c r="D163" s="2"/>
       <c r="F163" s="3"/>
@@ -34926,7 +34926,7 @@
         <f>IF($G163="","",P163-Y163)</f>
       </c>
     </row>
-    <row r="164" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A164" s="1"/>
       <c r="D164" s="2"/>
       <c r="F164" s="3"/>
@@ -34966,7 +34966,7 @@
         <f>IF($G164="","",P164-Y164)</f>
       </c>
     </row>
-    <row r="165" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A165" s="1"/>
       <c r="D165" s="2"/>
       <c r="F165" s="3"/>
@@ -35006,7 +35006,7 @@
         <f>IF($G165="","",P165-Y165)</f>
       </c>
     </row>
-    <row r="166" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A166" s="1"/>
       <c r="D166" s="2"/>
       <c r="F166" s="3"/>
@@ -35046,7 +35046,7 @@
         <f>IF($G166="","",P166-Y166)</f>
       </c>
     </row>
-    <row r="167" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A167" s="1"/>
       <c r="D167" s="2"/>
       <c r="F167" s="3"/>
@@ -35086,7 +35086,7 @@
         <f>IF($G167="","",P167-Y167)</f>
       </c>
     </row>
-    <row r="168" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A168" s="1"/>
       <c r="D168" s="2"/>
       <c r="F168" s="3"/>
@@ -35126,7 +35126,7 @@
         <f>IF($G168="","",P168-Y168)</f>
       </c>
     </row>
-    <row r="169" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A169" s="1"/>
       <c r="D169" s="2"/>
       <c r="F169" s="3"/>
@@ -35166,7 +35166,7 @@
         <f>IF($G169="","",P169-Y169)</f>
       </c>
     </row>
-    <row r="170" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A170" s="1"/>
       <c r="D170" s="2"/>
       <c r="F170" s="3"/>
@@ -35206,7 +35206,7 @@
         <f>IF($G170="","",P170-Y170)</f>
       </c>
     </row>
-    <row r="171" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A171" s="1"/>
       <c r="D171" s="2"/>
       <c r="F171" s="3"/>
@@ -35246,7 +35246,7 @@
         <f>IF($G171="","",P171-Y171)</f>
       </c>
     </row>
-    <row r="172" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A172" s="1"/>
       <c r="D172" s="2"/>
       <c r="F172" s="3"/>
@@ -35286,7 +35286,7 @@
         <f>IF($G172="","",P172-Y172)</f>
       </c>
     </row>
-    <row r="173" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A173" s="1"/>
       <c r="D173" s="2"/>
       <c r="F173" s="3"/>
@@ -35326,7 +35326,7 @@
         <f>IF($G173="","",P173-Y173)</f>
       </c>
     </row>
-    <row r="174" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A174" s="1"/>
       <c r="D174" s="2"/>
       <c r="F174" s="3"/>
@@ -35366,7 +35366,7 @@
         <f>IF($G174="","",P174-Y174)</f>
       </c>
     </row>
-    <row r="175" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A175" s="1"/>
       <c r="D175" s="2"/>
       <c r="F175" s="3"/>
@@ -35406,7 +35406,7 @@
         <f>IF($G175="","",P175-Y175)</f>
       </c>
     </row>
-    <row r="176" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A176" s="1"/>
       <c r="D176" s="2"/>
       <c r="F176" s="3"/>
@@ -35446,7 +35446,7 @@
         <f>IF($G176="","",P176-Y176)</f>
       </c>
     </row>
-    <row r="177" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A177" s="1"/>
       <c r="D177" s="2"/>
       <c r="F177" s="3"/>
@@ -35486,7 +35486,7 @@
         <f>IF($G177="","",P177-Y177)</f>
       </c>
     </row>
-    <row r="178" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A178" s="1"/>
       <c r="D178" s="2"/>
       <c r="F178" s="3"/>
@@ -35526,7 +35526,7 @@
         <f>IF($G178="","",P178-Y178)</f>
       </c>
     </row>
-    <row r="179" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A179" s="1"/>
       <c r="D179" s="2"/>
       <c r="F179" s="3"/>
@@ -35566,7 +35566,7 @@
         <f>IF($G179="","",P179-Y179)</f>
       </c>
     </row>
-    <row r="180" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A180" s="1"/>
       <c r="D180" s="2"/>
       <c r="F180" s="3"/>
@@ -35606,7 +35606,7 @@
         <f>IF($G180="","",P180-Y180)</f>
       </c>
     </row>
-    <row r="181" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A181" s="1"/>
       <c r="D181" s="2"/>
       <c r="F181" s="3"/>
@@ -35646,7 +35646,7 @@
         <f>IF($G181="","",P181-Y181)</f>
       </c>
     </row>
-    <row r="182" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A182" s="1"/>
       <c r="D182" s="2"/>
       <c r="F182" s="3"/>
@@ -35686,7 +35686,7 @@
         <f>IF($G182="","",P182-Y182)</f>
       </c>
     </row>
-    <row r="183" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A183" s="1"/>
       <c r="D183" s="2"/>
       <c r="F183" s="3"/>
@@ -35726,7 +35726,7 @@
         <f>IF($G183="","",P183-Y183)</f>
       </c>
     </row>
-    <row r="184" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A184" s="1"/>
       <c r="D184" s="2"/>
       <c r="F184" s="3"/>
@@ -35766,7 +35766,7 @@
         <f>IF($G184="","",P184-Y184)</f>
       </c>
     </row>
-    <row r="185" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A185" s="1"/>
       <c r="D185" s="2"/>
       <c r="F185" s="3"/>
@@ -35806,7 +35806,7 @@
         <f>IF($G185="","",P185-Y185)</f>
       </c>
     </row>
-    <row r="186" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A186" s="1"/>
       <c r="D186" s="2"/>
       <c r="F186" s="3"/>
@@ -35846,7 +35846,7 @@
         <f>IF($G186="","",P186-Y186)</f>
       </c>
     </row>
-    <row r="187" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A187" s="1"/>
       <c r="D187" s="2"/>
       <c r="F187" s="3"/>
@@ -35886,7 +35886,7 @@
         <f>IF($G187="","",P187-Y187)</f>
       </c>
     </row>
-    <row r="188" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A188" s="1"/>
       <c r="D188" s="2"/>
       <c r="F188" s="3"/>
@@ -35926,7 +35926,7 @@
         <f>IF($G188="","",P188-Y188)</f>
       </c>
     </row>
-    <row r="189" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A189" s="1"/>
       <c r="D189" s="2"/>
       <c r="F189" s="3"/>
@@ -35966,7 +35966,7 @@
         <f>IF($G189="","",P189-Y189)</f>
       </c>
     </row>
-    <row r="190" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A190" s="1"/>
       <c r="D190" s="2"/>
       <c r="F190" s="3"/>
@@ -36006,7 +36006,7 @@
         <f>IF($G190="","",P190-Y190)</f>
       </c>
     </row>
-    <row r="191" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A191" s="1"/>
       <c r="D191" s="2"/>
       <c r="F191" s="3"/>
@@ -36046,7 +36046,7 @@
         <f>IF($G191="","",P191-Y191)</f>
       </c>
     </row>
-    <row r="192" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A192" s="1"/>
       <c r="D192" s="2"/>
       <c r="F192" s="3"/>
@@ -36086,7 +36086,7 @@
         <f>IF($G192="","",P192-Y192)</f>
       </c>
     </row>
-    <row r="193" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A193" s="1"/>
       <c r="D193" s="2"/>
       <c r="F193" s="3"/>
@@ -36126,7 +36126,7 @@
         <f>IF($G193="","",P193-Y193)</f>
       </c>
     </row>
-    <row r="194" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A194" s="1"/>
       <c r="D194" s="2"/>
       <c r="F194" s="3"/>
@@ -36166,7 +36166,7 @@
         <f>IF($G194="","",P194-Y194)</f>
       </c>
     </row>
-    <row r="195" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A195" s="1"/>
       <c r="D195" s="2"/>
       <c r="F195" s="3"/>
@@ -36206,7 +36206,7 @@
         <f>IF($G195="","",P195-Y195)</f>
       </c>
     </row>
-    <row r="196" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A196" s="1"/>
       <c r="D196" s="2"/>
       <c r="F196" s="3"/>
@@ -36246,7 +36246,7 @@
         <f>IF($G196="","",P196-Y196)</f>
       </c>
     </row>
-    <row r="197" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A197" s="1"/>
       <c r="D197" s="2"/>
       <c r="F197" s="3"/>
@@ -36286,7 +36286,7 @@
         <f>IF($G197="","",P197-Y197)</f>
       </c>
     </row>
-    <row r="198" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A198" s="1"/>
       <c r="D198" s="2"/>
       <c r="F198" s="3"/>
@@ -36326,7 +36326,7 @@
         <f>IF($G198="","",P198-Y198)</f>
       </c>
     </row>
-    <row r="199" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A199" s="1"/>
       <c r="D199" s="2"/>
       <c r="F199" s="3"/>
@@ -36366,7 +36366,7 @@
         <f>IF($G199="","",P199-Y199)</f>
       </c>
     </row>
-    <row r="200" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A200" s="1"/>
       <c r="D200" s="2"/>
       <c r="F200" s="3"/>
@@ -36406,7 +36406,7 @@
         <f>IF($G200="","",P200-Y200)</f>
       </c>
     </row>
-    <row r="201" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A201" s="1"/>
       <c r="D201" s="2"/>
       <c r="F201" s="3"/>
@@ -36446,7 +36446,7 @@
         <f>IF($G201="","",P201-Y201)</f>
       </c>
     </row>
-    <row r="202" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A202" s="1"/>
       <c r="D202" s="2"/>
       <c r="F202" s="3"/>
@@ -36674,37 +36674,37 @@
         <v>83.99</v>
       </c>
       <c r="I2" s="3">
-        <f>IF($H2="","",H2-G2)</f>
+        <f>H2-G2</f>
       </c>
       <c r="J2" s="3">
-        <f>IF($H2="","",I2*16.67%)</f>
+        <f>I2*16.67%</f>
       </c>
       <c r="K2" s="3">
         <v>3.87</v>
       </c>
       <c r="L2" s="3">
-        <f>IF($H2="","",K2*20%)</f>
+        <f>K2*20%</f>
       </c>
       <c r="M2" s="3">
         <v>6.3</v>
       </c>
       <c r="N2" s="3">
-        <f>IF($H2="","",M2*20%)</f>
+        <f>M2*20%</f>
       </c>
       <c r="O2" s="3">
         <v>1</v>
       </c>
       <c r="P2" s="3">
-        <f>IF($H2="","",N2)</f>
+        <f>N2</f>
       </c>
       <c r="Q2" s="3">
-        <f>IF($H2="","",I2-J2-K2-M2-N2-O2)</f>
+        <f>I2-J2-K2-M2-N2-O2</f>
       </c>
       <c r="R2" s="3">
-        <f>IF($H2="","",(Q2-Z2)/G2*100)</f>
+        <f>(Q2-Z2)/G2*100</f>
       </c>
       <c r="S2" s="3">
-        <f>IF($H2="","",J2-P2)</f>
+        <f>J2-P2</f>
       </c>
       <c r="T2" t="s">
         <v>35</v>
@@ -36713,7 +36713,7 @@
         <v>65</v>
       </c>
       <c r="AA2" s="3">
-        <f>IF($H2="","",Q2-Z2)</f>
+        <f>Q2-Z2</f>
       </c>
       <c r="AB2" t="s">
         <v>35</v>
@@ -36722,7 +36722,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="D3" s="2"/>
       <c r="G3" s="3"/>
@@ -36760,7 +36760,7 @@
         <f>IF($H3="","",Q3-Z3)</f>
       </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="D4" s="2"/>
       <c r="G4" s="3"/>
@@ -36798,7 +36798,7 @@
         <f>IF($H4="","",Q4-Z4)</f>
       </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="D5" s="2"/>
       <c r="G5" s="3"/>
@@ -36836,7 +36836,7 @@
         <f>IF($H5="","",Q5-Z5)</f>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="D6" s="2"/>
       <c r="G6" s="3"/>
@@ -36874,7 +36874,7 @@
         <f>IF($H6="","",Q6-Z6)</f>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="D7" s="2"/>
       <c r="G7" s="3"/>
@@ -36912,7 +36912,7 @@
         <f>IF($H7="","",Q7-Z7)</f>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="D8" s="2"/>
       <c r="G8" s="3"/>
@@ -36950,7 +36950,7 @@
         <f>IF($H8="","",Q8-Z8)</f>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="D9" s="2"/>
       <c r="G9" s="3"/>
@@ -36988,7 +36988,7 @@
         <f>IF($H9="","",Q9-Z9)</f>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="D10" s="2"/>
       <c r="G10" s="3"/>
@@ -37026,7 +37026,7 @@
         <f>IF($H10="","",Q10-Z10)</f>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="D11" s="2"/>
       <c r="G11" s="3"/>
@@ -37064,7 +37064,7 @@
         <f>IF($H11="","",Q11-Z11)</f>
       </c>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="D12" s="2"/>
       <c r="G12" s="3"/>
@@ -37102,7 +37102,7 @@
         <f>IF($H12="","",Q12-Z12)</f>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="D13" s="2"/>
       <c r="G13" s="3"/>
@@ -37140,7 +37140,7 @@
         <f>IF($H13="","",Q13-Z13)</f>
       </c>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="D14" s="2"/>
       <c r="G14" s="3"/>
@@ -37178,7 +37178,7 @@
         <f>IF($H14="","",Q14-Z14)</f>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="D15" s="2"/>
       <c r="G15" s="3"/>
@@ -37216,7 +37216,7 @@
         <f>IF($H15="","",Q15-Z15)</f>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="D16" s="2"/>
       <c r="G16" s="3"/>
@@ -37254,7 +37254,7 @@
         <f>IF($H16="","",Q16-Z16)</f>
       </c>
     </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="D17" s="2"/>
       <c r="G17" s="3"/>
@@ -37292,7 +37292,7 @@
         <f>IF($H17="","",Q17-Z17)</f>
       </c>
     </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="D18" s="2"/>
       <c r="G18" s="3"/>
@@ -37330,7 +37330,7 @@
         <f>IF($H18="","",Q18-Z18)</f>
       </c>
     </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="D19" s="2"/>
       <c r="G19" s="3"/>
@@ -37368,7 +37368,7 @@
         <f>IF($H19="","",Q19-Z19)</f>
       </c>
     </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="D20" s="2"/>
       <c r="G20" s="3"/>
@@ -37406,7 +37406,7 @@
         <f>IF($H20="","",Q20-Z20)</f>
       </c>
     </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="D21" s="2"/>
       <c r="G21" s="3"/>
@@ -37444,7 +37444,7 @@
         <f>IF($H21="","",Q21-Z21)</f>
       </c>
     </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="D22" s="2"/>
       <c r="G22" s="3"/>
@@ -37482,7 +37482,7 @@
         <f>IF($H22="","",Q22-Z22)</f>
       </c>
     </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="D23" s="2"/>
       <c r="G23" s="3"/>
@@ -37520,7 +37520,7 @@
         <f>IF($H23="","",Q23-Z23)</f>
       </c>
     </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="D24" s="2"/>
       <c r="G24" s="3"/>
@@ -37558,7 +37558,7 @@
         <f>IF($H24="","",Q24-Z24)</f>
       </c>
     </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="D25" s="2"/>
       <c r="G25" s="3"/>
@@ -37596,7 +37596,7 @@
         <f>IF($H25="","",Q25-Z25)</f>
       </c>
     </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="D26" s="2"/>
       <c r="G26" s="3"/>
@@ -37634,7 +37634,7 @@
         <f>IF($H26="","",Q26-Z26)</f>
       </c>
     </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="D27" s="2"/>
       <c r="G27" s="3"/>
@@ -37672,7 +37672,7 @@
         <f>IF($H27="","",Q27-Z27)</f>
       </c>
     </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="D28" s="2"/>
       <c r="G28" s="3"/>
@@ -37710,7 +37710,7 @@
         <f>IF($H28="","",Q28-Z28)</f>
       </c>
     </row>
-    <row r="29" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="D29" s="2"/>
       <c r="G29" s="3"/>
@@ -37748,7 +37748,7 @@
         <f>IF($H29="","",Q29-Z29)</f>
       </c>
     </row>
-    <row r="30" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="D30" s="2"/>
       <c r="G30" s="3"/>
@@ -37786,7 +37786,7 @@
         <f>IF($H30="","",Q30-Z30)</f>
       </c>
     </row>
-    <row r="31" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="D31" s="2"/>
       <c r="G31" s="3"/>
@@ -37824,7 +37824,7 @@
         <f>IF($H31="","",Q31-Z31)</f>
       </c>
     </row>
-    <row r="32" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="D32" s="2"/>
       <c r="G32" s="3"/>
@@ -37862,7 +37862,7 @@
         <f>IF($H32="","",Q32-Z32)</f>
       </c>
     </row>
-    <row r="33" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="D33" s="2"/>
       <c r="G33" s="3"/>
@@ -37900,7 +37900,7 @@
         <f>IF($H33="","",Q33-Z33)</f>
       </c>
     </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="D34" s="2"/>
       <c r="G34" s="3"/>
@@ -37938,7 +37938,7 @@
         <f>IF($H34="","",Q34-Z34)</f>
       </c>
     </row>
-    <row r="35" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="D35" s="2"/>
       <c r="G35" s="3"/>
@@ -37976,7 +37976,7 @@
         <f>IF($H35="","",Q35-Z35)</f>
       </c>
     </row>
-    <row r="36" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="D36" s="2"/>
       <c r="G36" s="3"/>
@@ -38014,7 +38014,7 @@
         <f>IF($H36="","",Q36-Z36)</f>
       </c>
     </row>
-    <row r="37" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="D37" s="2"/>
       <c r="G37" s="3"/>
@@ -38052,7 +38052,7 @@
         <f>IF($H37="","",Q37-Z37)</f>
       </c>
     </row>
-    <row r="38" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="D38" s="2"/>
       <c r="G38" s="3"/>
@@ -38090,7 +38090,7 @@
         <f>IF($H38="","",Q38-Z38)</f>
       </c>
     </row>
-    <row r="39" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="D39" s="2"/>
       <c r="G39" s="3"/>
@@ -38128,7 +38128,7 @@
         <f>IF($H39="","",Q39-Z39)</f>
       </c>
     </row>
-    <row r="40" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="D40" s="2"/>
       <c r="G40" s="3"/>
@@ -38166,7 +38166,7 @@
         <f>IF($H40="","",Q40-Z40)</f>
       </c>
     </row>
-    <row r="41" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="D41" s="2"/>
       <c r="G41" s="3"/>
@@ -38204,7 +38204,7 @@
         <f>IF($H41="","",Q41-Z41)</f>
       </c>
     </row>
-    <row r="42" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="D42" s="2"/>
       <c r="G42" s="3"/>
@@ -38242,7 +38242,7 @@
         <f>IF($H42="","",Q42-Z42)</f>
       </c>
     </row>
-    <row r="43" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="D43" s="2"/>
       <c r="G43" s="3"/>
@@ -38280,7 +38280,7 @@
         <f>IF($H43="","",Q43-Z43)</f>
       </c>
     </row>
-    <row r="44" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="D44" s="2"/>
       <c r="G44" s="3"/>
@@ -38318,7 +38318,7 @@
         <f>IF($H44="","",Q44-Z44)</f>
       </c>
     </row>
-    <row r="45" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="D45" s="2"/>
       <c r="G45" s="3"/>
@@ -38356,7 +38356,7 @@
         <f>IF($H45="","",Q45-Z45)</f>
       </c>
     </row>
-    <row r="46" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="D46" s="2"/>
       <c r="G46" s="3"/>
@@ -38394,7 +38394,7 @@
         <f>IF($H46="","",Q46-Z46)</f>
       </c>
     </row>
-    <row r="47" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="D47" s="2"/>
       <c r="G47" s="3"/>
@@ -38432,7 +38432,7 @@
         <f>IF($H47="","",Q47-Z47)</f>
       </c>
     </row>
-    <row r="48" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="D48" s="2"/>
       <c r="G48" s="3"/>
@@ -38470,7 +38470,7 @@
         <f>IF($H48="","",Q48-Z48)</f>
       </c>
     </row>
-    <row r="49" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
       <c r="D49" s="2"/>
       <c r="G49" s="3"/>
@@ -38508,7 +38508,7 @@
         <f>IF($H49="","",Q49-Z49)</f>
       </c>
     </row>
-    <row r="50" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
       <c r="D50" s="2"/>
       <c r="G50" s="3"/>
@@ -38546,7 +38546,7 @@
         <f>IF($H50="","",Q50-Z50)</f>
       </c>
     </row>
-    <row r="51" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
       <c r="D51" s="2"/>
       <c r="G51" s="3"/>
@@ -38584,7 +38584,7 @@
         <f>IF($H51="","",Q51-Z51)</f>
       </c>
     </row>
-    <row r="52" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
       <c r="D52" s="2"/>
       <c r="G52" s="3"/>
@@ -38622,7 +38622,7 @@
         <f>IF($H52="","",Q52-Z52)</f>
       </c>
     </row>
-    <row r="53" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
       <c r="D53" s="2"/>
       <c r="G53" s="3"/>
@@ -38660,7 +38660,7 @@
         <f>IF($H53="","",Q53-Z53)</f>
       </c>
     </row>
-    <row r="54" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
       <c r="D54" s="2"/>
       <c r="G54" s="3"/>
@@ -38698,7 +38698,7 @@
         <f>IF($H54="","",Q54-Z54)</f>
       </c>
     </row>
-    <row r="55" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
       <c r="D55" s="2"/>
       <c r="G55" s="3"/>
@@ -38736,7 +38736,7 @@
         <f>IF($H55="","",Q55-Z55)</f>
       </c>
     </row>
-    <row r="56" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
       <c r="D56" s="2"/>
       <c r="G56" s="3"/>
@@ -38774,7 +38774,7 @@
         <f>IF($H56="","",Q56-Z56)</f>
       </c>
     </row>
-    <row r="57" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
       <c r="D57" s="2"/>
       <c r="G57" s="3"/>
@@ -38812,7 +38812,7 @@
         <f>IF($H57="","",Q57-Z57)</f>
       </c>
     </row>
-    <row r="58" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
       <c r="D58" s="2"/>
       <c r="G58" s="3"/>
@@ -38850,7 +38850,7 @@
         <f>IF($H58="","",Q58-Z58)</f>
       </c>
     </row>
-    <row r="59" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
       <c r="D59" s="2"/>
       <c r="G59" s="3"/>
@@ -38888,7 +38888,7 @@
         <f>IF($H59="","",Q59-Z59)</f>
       </c>
     </row>
-    <row r="60" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
       <c r="D60" s="2"/>
       <c r="G60" s="3"/>
@@ -38926,7 +38926,7 @@
         <f>IF($H60="","",Q60-Z60)</f>
       </c>
     </row>
-    <row r="61" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
       <c r="D61" s="2"/>
       <c r="G61" s="3"/>
@@ -38964,7 +38964,7 @@
         <f>IF($H61="","",Q61-Z61)</f>
       </c>
     </row>
-    <row r="62" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
       <c r="D62" s="2"/>
       <c r="G62" s="3"/>
@@ -39002,7 +39002,7 @@
         <f>IF($H62="","",Q62-Z62)</f>
       </c>
     </row>
-    <row r="63" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
       <c r="D63" s="2"/>
       <c r="G63" s="3"/>
@@ -39040,7 +39040,7 @@
         <f>IF($H63="","",Q63-Z63)</f>
       </c>
     </row>
-    <row r="64" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
       <c r="D64" s="2"/>
       <c r="G64" s="3"/>
@@ -39078,7 +39078,7 @@
         <f>IF($H64="","",Q64-Z64)</f>
       </c>
     </row>
-    <row r="65" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
       <c r="D65" s="2"/>
       <c r="G65" s="3"/>
@@ -39116,7 +39116,7 @@
         <f>IF($H65="","",Q65-Z65)</f>
       </c>
     </row>
-    <row r="66" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
       <c r="D66" s="2"/>
       <c r="G66" s="3"/>
@@ -39154,7 +39154,7 @@
         <f>IF($H66="","",Q66-Z66)</f>
       </c>
     </row>
-    <row r="67" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
       <c r="D67" s="2"/>
       <c r="G67" s="3"/>
@@ -39192,7 +39192,7 @@
         <f>IF($H67="","",Q67-Z67)</f>
       </c>
     </row>
-    <row r="68" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
       <c r="D68" s="2"/>
       <c r="G68" s="3"/>
@@ -39230,7 +39230,7 @@
         <f>IF($H68="","",Q68-Z68)</f>
       </c>
     </row>
-    <row r="69" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
       <c r="D69" s="2"/>
       <c r="G69" s="3"/>
@@ -39268,7 +39268,7 @@
         <f>IF($H69="","",Q69-Z69)</f>
       </c>
     </row>
-    <row r="70" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
       <c r="D70" s="2"/>
       <c r="G70" s="3"/>
@@ -39306,7 +39306,7 @@
         <f>IF($H70="","",Q70-Z70)</f>
       </c>
     </row>
-    <row r="71" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
       <c r="D71" s="2"/>
       <c r="G71" s="3"/>
@@ -39344,7 +39344,7 @@
         <f>IF($H71="","",Q71-Z71)</f>
       </c>
     </row>
-    <row r="72" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
       <c r="D72" s="2"/>
       <c r="G72" s="3"/>
@@ -39382,7 +39382,7 @@
         <f>IF($H72="","",Q72-Z72)</f>
       </c>
     </row>
-    <row r="73" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
       <c r="D73" s="2"/>
       <c r="G73" s="3"/>
@@ -39420,7 +39420,7 @@
         <f>IF($H73="","",Q73-Z73)</f>
       </c>
     </row>
-    <row r="74" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
       <c r="D74" s="2"/>
       <c r="G74" s="3"/>
@@ -39458,7 +39458,7 @@
         <f>IF($H74="","",Q74-Z74)</f>
       </c>
     </row>
-    <row r="75" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
       <c r="D75" s="2"/>
       <c r="G75" s="3"/>
@@ -39496,7 +39496,7 @@
         <f>IF($H75="","",Q75-Z75)</f>
       </c>
     </row>
-    <row r="76" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
       <c r="D76" s="2"/>
       <c r="G76" s="3"/>
@@ -39534,7 +39534,7 @@
         <f>IF($H76="","",Q76-Z76)</f>
       </c>
     </row>
-    <row r="77" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
       <c r="D77" s="2"/>
       <c r="G77" s="3"/>
@@ -39572,7 +39572,7 @@
         <f>IF($H77="","",Q77-Z77)</f>
       </c>
     </row>
-    <row r="78" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
       <c r="D78" s="2"/>
       <c r="G78" s="3"/>
@@ -39610,7 +39610,7 @@
         <f>IF($H78="","",Q78-Z78)</f>
       </c>
     </row>
-    <row r="79" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="D79" s="2"/>
       <c r="G79" s="3"/>
@@ -39648,7 +39648,7 @@
         <f>IF($H79="","",Q79-Z79)</f>
       </c>
     </row>
-    <row r="80" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
       <c r="D80" s="2"/>
       <c r="G80" s="3"/>
@@ -39686,7 +39686,7 @@
         <f>IF($H80="","",Q80-Z80)</f>
       </c>
     </row>
-    <row r="81" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
       <c r="D81" s="2"/>
       <c r="G81" s="3"/>
@@ -39724,7 +39724,7 @@
         <f>IF($H81="","",Q81-Z81)</f>
       </c>
     </row>
-    <row r="82" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
       <c r="D82" s="2"/>
       <c r="G82" s="3"/>
@@ -39762,7 +39762,7 @@
         <f>IF($H82="","",Q82-Z82)</f>
       </c>
     </row>
-    <row r="83" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
       <c r="D83" s="2"/>
       <c r="G83" s="3"/>
@@ -39800,7 +39800,7 @@
         <f>IF($H83="","",Q83-Z83)</f>
       </c>
     </row>
-    <row r="84" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
       <c r="D84" s="2"/>
       <c r="G84" s="3"/>
@@ -39838,7 +39838,7 @@
         <f>IF($H84="","",Q84-Z84)</f>
       </c>
     </row>
-    <row r="85" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="D85" s="2"/>
       <c r="G85" s="3"/>
@@ -39876,7 +39876,7 @@
         <f>IF($H85="","",Q85-Z85)</f>
       </c>
     </row>
-    <row r="86" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="D86" s="2"/>
       <c r="G86" s="3"/>
@@ -39914,7 +39914,7 @@
         <f>IF($H86="","",Q86-Z86)</f>
       </c>
     </row>
-    <row r="87" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="D87" s="2"/>
       <c r="G87" s="3"/>
@@ -39952,7 +39952,7 @@
         <f>IF($H87="","",Q87-Z87)</f>
       </c>
     </row>
-    <row r="88" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="D88" s="2"/>
       <c r="G88" s="3"/>
@@ -39990,7 +39990,7 @@
         <f>IF($H88="","",Q88-Z88)</f>
       </c>
     </row>
-    <row r="89" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="D89" s="2"/>
       <c r="G89" s="3"/>
@@ -40028,7 +40028,7 @@
         <f>IF($H89="","",Q89-Z89)</f>
       </c>
     </row>
-    <row r="90" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="D90" s="2"/>
       <c r="G90" s="3"/>
@@ -40066,7 +40066,7 @@
         <f>IF($H90="","",Q90-Z90)</f>
       </c>
     </row>
-    <row r="91" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="D91" s="2"/>
       <c r="G91" s="3"/>
@@ -40104,7 +40104,7 @@
         <f>IF($H91="","",Q91-Z91)</f>
       </c>
     </row>
-    <row r="92" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="D92" s="2"/>
       <c r="G92" s="3"/>
@@ -40142,7 +40142,7 @@
         <f>IF($H92="","",Q92-Z92)</f>
       </c>
     </row>
-    <row r="93" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="D93" s="2"/>
       <c r="G93" s="3"/>
@@ -40180,7 +40180,7 @@
         <f>IF($H93="","",Q93-Z93)</f>
       </c>
     </row>
-    <row r="94" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="D94" s="2"/>
       <c r="G94" s="3"/>
@@ -40218,7 +40218,7 @@
         <f>IF($H94="","",Q94-Z94)</f>
       </c>
     </row>
-    <row r="95" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="D95" s="2"/>
       <c r="G95" s="3"/>
@@ -40256,7 +40256,7 @@
         <f>IF($H95="","",Q95-Z95)</f>
       </c>
     </row>
-    <row r="96" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="D96" s="2"/>
       <c r="G96" s="3"/>
@@ -40294,7 +40294,7 @@
         <f>IF($H96="","",Q96-Z96)</f>
       </c>
     </row>
-    <row r="97" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="D97" s="2"/>
       <c r="G97" s="3"/>
@@ -40332,7 +40332,7 @@
         <f>IF($H97="","",Q97-Z97)</f>
       </c>
     </row>
-    <row r="98" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="D98" s="2"/>
       <c r="G98" s="3"/>
@@ -40370,7 +40370,7 @@
         <f>IF($H98="","",Q98-Z98)</f>
       </c>
     </row>
-    <row r="99" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="D99" s="2"/>
       <c r="G99" s="3"/>
@@ -40408,7 +40408,7 @@
         <f>IF($H99="","",Q99-Z99)</f>
       </c>
     </row>
-    <row r="100" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
       <c r="D100" s="2"/>
       <c r="G100" s="3"/>
@@ -40446,7 +40446,7 @@
         <f>IF($H100="","",Q100-Z100)</f>
       </c>
     </row>
-    <row r="101" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="D101" s="2"/>
       <c r="G101" s="3"/>
@@ -40484,7 +40484,7 @@
         <f>IF($H101="","",Q101-Z101)</f>
       </c>
     </row>
-    <row r="102" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="D102" s="2"/>
       <c r="G102" s="3"/>
@@ -40522,7 +40522,7 @@
         <f>IF($H102="","",Q102-Z102)</f>
       </c>
     </row>
-    <row r="103" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="D103" s="2"/>
       <c r="G103" s="3"/>
@@ -40560,7 +40560,7 @@
         <f>IF($H103="","",Q103-Z103)</f>
       </c>
     </row>
-    <row r="104" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="D104" s="2"/>
       <c r="G104" s="3"/>
@@ -40598,7 +40598,7 @@
         <f>IF($H104="","",Q104-Z104)</f>
       </c>
     </row>
-    <row r="105" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="D105" s="2"/>
       <c r="G105" s="3"/>
@@ -40636,7 +40636,7 @@
         <f>IF($H105="","",Q105-Z105)</f>
       </c>
     </row>
-    <row r="106" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="D106" s="2"/>
       <c r="G106" s="3"/>
@@ -40674,7 +40674,7 @@
         <f>IF($H106="","",Q106-Z106)</f>
       </c>
     </row>
-    <row r="107" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="D107" s="2"/>
       <c r="G107" s="3"/>
@@ -40712,7 +40712,7 @@
         <f>IF($H107="","",Q107-Z107)</f>
       </c>
     </row>
-    <row r="108" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="D108" s="2"/>
       <c r="G108" s="3"/>
@@ -40750,7 +40750,7 @@
         <f>IF($H108="","",Q108-Z108)</f>
       </c>
     </row>
-    <row r="109" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="D109" s="2"/>
       <c r="G109" s="3"/>
@@ -40788,7 +40788,7 @@
         <f>IF($H109="","",Q109-Z109)</f>
       </c>
     </row>
-    <row r="110" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="D110" s="2"/>
       <c r="G110" s="3"/>
@@ -40826,7 +40826,7 @@
         <f>IF($H110="","",Q110-Z110)</f>
       </c>
     </row>
-    <row r="111" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
       <c r="D111" s="2"/>
       <c r="G111" s="3"/>
@@ -40864,7 +40864,7 @@
         <f>IF($H111="","",Q111-Z111)</f>
       </c>
     </row>
-    <row r="112" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="D112" s="2"/>
       <c r="G112" s="3"/>
@@ -40902,7 +40902,7 @@
         <f>IF($H112="","",Q112-Z112)</f>
       </c>
     </row>
-    <row r="113" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="D113" s="2"/>
       <c r="G113" s="3"/>
@@ -40940,7 +40940,7 @@
         <f>IF($H113="","",Q113-Z113)</f>
       </c>
     </row>
-    <row r="114" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="D114" s="2"/>
       <c r="G114" s="3"/>
@@ -40978,7 +40978,7 @@
         <f>IF($H114="","",Q114-Z114)</f>
       </c>
     </row>
-    <row r="115" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="D115" s="2"/>
       <c r="G115" s="3"/>
@@ -41016,7 +41016,7 @@
         <f>IF($H115="","",Q115-Z115)</f>
       </c>
     </row>
-    <row r="116" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="D116" s="2"/>
       <c r="G116" s="3"/>
@@ -41054,7 +41054,7 @@
         <f>IF($H116="","",Q116-Z116)</f>
       </c>
     </row>
-    <row r="117" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="D117" s="2"/>
       <c r="G117" s="3"/>
@@ -41092,7 +41092,7 @@
         <f>IF($H117="","",Q117-Z117)</f>
       </c>
     </row>
-    <row r="118" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="D118" s="2"/>
       <c r="G118" s="3"/>
@@ -41130,7 +41130,7 @@
         <f>IF($H118="","",Q118-Z118)</f>
       </c>
     </row>
-    <row r="119" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="D119" s="2"/>
       <c r="G119" s="3"/>
@@ -41168,7 +41168,7 @@
         <f>IF($H119="","",Q119-Z119)</f>
       </c>
     </row>
-    <row r="120" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="D120" s="2"/>
       <c r="G120" s="3"/>
@@ -41206,7 +41206,7 @@
         <f>IF($H120="","",Q120-Z120)</f>
       </c>
     </row>
-    <row r="121" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="D121" s="2"/>
       <c r="G121" s="3"/>
@@ -41244,7 +41244,7 @@
         <f>IF($H121="","",Q121-Z121)</f>
       </c>
     </row>
-    <row r="122" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="D122" s="2"/>
       <c r="G122" s="3"/>
@@ -41282,7 +41282,7 @@
         <f>IF($H122="","",Q122-Z122)</f>
       </c>
     </row>
-    <row r="123" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="D123" s="2"/>
       <c r="G123" s="3"/>
@@ -41320,7 +41320,7 @@
         <f>IF($H123="","",Q123-Z123)</f>
       </c>
     </row>
-    <row r="124" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="D124" s="2"/>
       <c r="G124" s="3"/>
@@ -41358,7 +41358,7 @@
         <f>IF($H124="","",Q124-Z124)</f>
       </c>
     </row>
-    <row r="125" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="D125" s="2"/>
       <c r="G125" s="3"/>
@@ -41396,7 +41396,7 @@
         <f>IF($H125="","",Q125-Z125)</f>
       </c>
     </row>
-    <row r="126" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="D126" s="2"/>
       <c r="G126" s="3"/>
@@ -41434,7 +41434,7 @@
         <f>IF($H126="","",Q126-Z126)</f>
       </c>
     </row>
-    <row r="127" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="D127" s="2"/>
       <c r="G127" s="3"/>
@@ -41472,7 +41472,7 @@
         <f>IF($H127="","",Q127-Z127)</f>
       </c>
     </row>
-    <row r="128" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A128" s="1"/>
       <c r="D128" s="2"/>
       <c r="G128" s="3"/>
@@ -41510,7 +41510,7 @@
         <f>IF($H128="","",Q128-Z128)</f>
       </c>
     </row>
-    <row r="129" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A129" s="1"/>
       <c r="D129" s="2"/>
       <c r="G129" s="3"/>
@@ -41548,7 +41548,7 @@
         <f>IF($H129="","",Q129-Z129)</f>
       </c>
     </row>
-    <row r="130" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A130" s="1"/>
       <c r="D130" s="2"/>
       <c r="G130" s="3"/>
@@ -41586,7 +41586,7 @@
         <f>IF($H130="","",Q130-Z130)</f>
       </c>
     </row>
-    <row r="131" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A131" s="1"/>
       <c r="D131" s="2"/>
       <c r="G131" s="3"/>
@@ -41624,7 +41624,7 @@
         <f>IF($H131="","",Q131-Z131)</f>
       </c>
     </row>
-    <row r="132" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A132" s="1"/>
       <c r="D132" s="2"/>
       <c r="G132" s="3"/>
@@ -41662,7 +41662,7 @@
         <f>IF($H132="","",Q132-Z132)</f>
       </c>
     </row>
-    <row r="133" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
       <c r="D133" s="2"/>
       <c r="G133" s="3"/>
@@ -41700,7 +41700,7 @@
         <f>IF($H133="","",Q133-Z133)</f>
       </c>
     </row>
-    <row r="134" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
       <c r="D134" s="2"/>
       <c r="G134" s="3"/>
@@ -41738,7 +41738,7 @@
         <f>IF($H134="","",Q134-Z134)</f>
       </c>
     </row>
-    <row r="135" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A135" s="1"/>
       <c r="D135" s="2"/>
       <c r="G135" s="3"/>
@@ -41776,7 +41776,7 @@
         <f>IF($H135="","",Q135-Z135)</f>
       </c>
     </row>
-    <row r="136" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A136" s="1"/>
       <c r="D136" s="2"/>
       <c r="G136" s="3"/>
@@ -41814,7 +41814,7 @@
         <f>IF($H136="","",Q136-Z136)</f>
       </c>
     </row>
-    <row r="137" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A137" s="1"/>
       <c r="D137" s="2"/>
       <c r="G137" s="3"/>
@@ -41852,7 +41852,7 @@
         <f>IF($H137="","",Q137-Z137)</f>
       </c>
     </row>
-    <row r="138" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A138" s="1"/>
       <c r="D138" s="2"/>
       <c r="G138" s="3"/>
@@ -41890,7 +41890,7 @@
         <f>IF($H138="","",Q138-Z138)</f>
       </c>
     </row>
-    <row r="139" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A139" s="1"/>
       <c r="D139" s="2"/>
       <c r="G139" s="3"/>
@@ -41928,7 +41928,7 @@
         <f>IF($H139="","",Q139-Z139)</f>
       </c>
     </row>
-    <row r="140" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A140" s="1"/>
       <c r="D140" s="2"/>
       <c r="G140" s="3"/>
@@ -41966,7 +41966,7 @@
         <f>IF($H140="","",Q140-Z140)</f>
       </c>
     </row>
-    <row r="141" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="D141" s="2"/>
       <c r="G141" s="3"/>
@@ -42004,7 +42004,7 @@
         <f>IF($H141="","",Q141-Z141)</f>
       </c>
     </row>
-    <row r="142" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A142" s="1"/>
       <c r="D142" s="2"/>
       <c r="G142" s="3"/>
@@ -42042,7 +42042,7 @@
         <f>IF($H142="","",Q142-Z142)</f>
       </c>
     </row>
-    <row r="143" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="D143" s="2"/>
       <c r="G143" s="3"/>
@@ -42080,7 +42080,7 @@
         <f>IF($H143="","",Q143-Z143)</f>
       </c>
     </row>
-    <row r="144" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="D144" s="2"/>
       <c r="G144" s="3"/>
@@ -42118,7 +42118,7 @@
         <f>IF($H144="","",Q144-Z144)</f>
       </c>
     </row>
-    <row r="145" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A145" s="1"/>
       <c r="D145" s="2"/>
       <c r="G145" s="3"/>
@@ -42156,7 +42156,7 @@
         <f>IF($H145="","",Q145-Z145)</f>
       </c>
     </row>
-    <row r="146" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
       <c r="D146" s="2"/>
       <c r="G146" s="3"/>
@@ -42194,7 +42194,7 @@
         <f>IF($H146="","",Q146-Z146)</f>
       </c>
     </row>
-    <row r="147" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A147" s="1"/>
       <c r="D147" s="2"/>
       <c r="G147" s="3"/>
@@ -42232,7 +42232,7 @@
         <f>IF($H147="","",Q147-Z147)</f>
       </c>
     </row>
-    <row r="148" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A148" s="1"/>
       <c r="D148" s="2"/>
       <c r="G148" s="3"/>
@@ -42270,7 +42270,7 @@
         <f>IF($H148="","",Q148-Z148)</f>
       </c>
     </row>
-    <row r="149" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
       <c r="D149" s="2"/>
       <c r="G149" s="3"/>
@@ -42308,7 +42308,7 @@
         <f>IF($H149="","",Q149-Z149)</f>
       </c>
     </row>
-    <row r="150" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A150" s="1"/>
       <c r="D150" s="2"/>
       <c r="G150" s="3"/>
@@ -42346,7 +42346,7 @@
         <f>IF($H150="","",Q150-Z150)</f>
       </c>
     </row>
-    <row r="151" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
       <c r="D151" s="2"/>
       <c r="G151" s="3"/>
@@ -42384,7 +42384,7 @@
         <f>IF($H151="","",Q151-Z151)</f>
       </c>
     </row>
-    <row r="152" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A152" s="1"/>
       <c r="D152" s="2"/>
       <c r="G152" s="3"/>
@@ -42422,7 +42422,7 @@
         <f>IF($H152="","",Q152-Z152)</f>
       </c>
     </row>
-    <row r="153" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
       <c r="D153" s="2"/>
       <c r="G153" s="3"/>
@@ -42460,7 +42460,7 @@
         <f>IF($H153="","",Q153-Z153)</f>
       </c>
     </row>
-    <row r="154" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
       <c r="D154" s="2"/>
       <c r="G154" s="3"/>
@@ -42498,7 +42498,7 @@
         <f>IF($H154="","",Q154-Z154)</f>
       </c>
     </row>
-    <row r="155" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A155" s="1"/>
       <c r="D155" s="2"/>
       <c r="G155" s="3"/>
@@ -42536,7 +42536,7 @@
         <f>IF($H155="","",Q155-Z155)</f>
       </c>
     </row>
-    <row r="156" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A156" s="1"/>
       <c r="D156" s="2"/>
       <c r="G156" s="3"/>
@@ -42574,7 +42574,7 @@
         <f>IF($H156="","",Q156-Z156)</f>
       </c>
     </row>
-    <row r="157" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A157" s="1"/>
       <c r="D157" s="2"/>
       <c r="G157" s="3"/>
@@ -42612,7 +42612,7 @@
         <f>IF($H157="","",Q157-Z157)</f>
       </c>
     </row>
-    <row r="158" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A158" s="1"/>
       <c r="D158" s="2"/>
       <c r="G158" s="3"/>
@@ -42650,7 +42650,7 @@
         <f>IF($H158="","",Q158-Z158)</f>
       </c>
     </row>
-    <row r="159" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A159" s="1"/>
       <c r="D159" s="2"/>
       <c r="G159" s="3"/>
@@ -42688,7 +42688,7 @@
         <f>IF($H159="","",Q159-Z159)</f>
       </c>
     </row>
-    <row r="160" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A160" s="1"/>
       <c r="D160" s="2"/>
       <c r="G160" s="3"/>
@@ -42726,7 +42726,7 @@
         <f>IF($H160="","",Q160-Z160)</f>
       </c>
     </row>
-    <row r="161" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A161" s="1"/>
       <c r="D161" s="2"/>
       <c r="G161" s="3"/>
@@ -42764,7 +42764,7 @@
         <f>IF($H161="","",Q161-Z161)</f>
       </c>
     </row>
-    <row r="162" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A162" s="1"/>
       <c r="D162" s="2"/>
       <c r="G162" s="3"/>
@@ -42802,7 +42802,7 @@
         <f>IF($H162="","",Q162-Z162)</f>
       </c>
     </row>
-    <row r="163" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A163" s="1"/>
       <c r="D163" s="2"/>
       <c r="G163" s="3"/>
@@ -42840,7 +42840,7 @@
         <f>IF($H163="","",Q163-Z163)</f>
       </c>
     </row>
-    <row r="164" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A164" s="1"/>
       <c r="D164" s="2"/>
       <c r="G164" s="3"/>
@@ -42878,7 +42878,7 @@
         <f>IF($H164="","",Q164-Z164)</f>
       </c>
     </row>
-    <row r="165" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A165" s="1"/>
       <c r="D165" s="2"/>
       <c r="G165" s="3"/>
@@ -42916,7 +42916,7 @@
         <f>IF($H165="","",Q165-Z165)</f>
       </c>
     </row>
-    <row r="166" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A166" s="1"/>
       <c r="D166" s="2"/>
       <c r="G166" s="3"/>
@@ -42954,7 +42954,7 @@
         <f>IF($H166="","",Q166-Z166)</f>
       </c>
     </row>
-    <row r="167" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A167" s="1"/>
       <c r="D167" s="2"/>
       <c r="G167" s="3"/>
@@ -42992,7 +42992,7 @@
         <f>IF($H167="","",Q167-Z167)</f>
       </c>
     </row>
-    <row r="168" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A168" s="1"/>
       <c r="D168" s="2"/>
       <c r="G168" s="3"/>
@@ -43030,7 +43030,7 @@
         <f>IF($H168="","",Q168-Z168)</f>
       </c>
     </row>
-    <row r="169" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A169" s="1"/>
       <c r="D169" s="2"/>
       <c r="G169" s="3"/>
@@ -43068,7 +43068,7 @@
         <f>IF($H169="","",Q169-Z169)</f>
       </c>
     </row>
-    <row r="170" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A170" s="1"/>
       <c r="D170" s="2"/>
       <c r="G170" s="3"/>
@@ -43106,7 +43106,7 @@
         <f>IF($H170="","",Q170-Z170)</f>
       </c>
     </row>
-    <row r="171" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A171" s="1"/>
       <c r="D171" s="2"/>
       <c r="G171" s="3"/>
@@ -43144,7 +43144,7 @@
         <f>IF($H171="","",Q171-Z171)</f>
       </c>
     </row>
-    <row r="172" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A172" s="1"/>
       <c r="D172" s="2"/>
       <c r="G172" s="3"/>
@@ -43182,7 +43182,7 @@
         <f>IF($H172="","",Q172-Z172)</f>
       </c>
     </row>
-    <row r="173" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A173" s="1"/>
       <c r="D173" s="2"/>
       <c r="G173" s="3"/>
@@ -43220,7 +43220,7 @@
         <f>IF($H173="","",Q173-Z173)</f>
       </c>
     </row>
-    <row r="174" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A174" s="1"/>
       <c r="D174" s="2"/>
       <c r="G174" s="3"/>
@@ -43258,7 +43258,7 @@
         <f>IF($H174="","",Q174-Z174)</f>
       </c>
     </row>
-    <row r="175" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A175" s="1"/>
       <c r="D175" s="2"/>
       <c r="G175" s="3"/>
@@ -43296,7 +43296,7 @@
         <f>IF($H175="","",Q175-Z175)</f>
       </c>
     </row>
-    <row r="176" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A176" s="1"/>
       <c r="D176" s="2"/>
       <c r="G176" s="3"/>
@@ -43334,7 +43334,7 @@
         <f>IF($H176="","",Q176-Z176)</f>
       </c>
     </row>
-    <row r="177" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A177" s="1"/>
       <c r="D177" s="2"/>
       <c r="G177" s="3"/>
@@ -43372,7 +43372,7 @@
         <f>IF($H177="","",Q177-Z177)</f>
       </c>
     </row>
-    <row r="178" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A178" s="1"/>
       <c r="D178" s="2"/>
       <c r="G178" s="3"/>
@@ -43410,7 +43410,7 @@
         <f>IF($H178="","",Q178-Z178)</f>
       </c>
     </row>
-    <row r="179" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A179" s="1"/>
       <c r="D179" s="2"/>
       <c r="G179" s="3"/>
@@ -43448,7 +43448,7 @@
         <f>IF($H179="","",Q179-Z179)</f>
       </c>
     </row>
-    <row r="180" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A180" s="1"/>
       <c r="D180" s="2"/>
       <c r="G180" s="3"/>
@@ -43486,7 +43486,7 @@
         <f>IF($H180="","",Q180-Z180)</f>
       </c>
     </row>
-    <row r="181" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A181" s="1"/>
       <c r="D181" s="2"/>
       <c r="G181" s="3"/>
@@ -43524,7 +43524,7 @@
         <f>IF($H181="","",Q181-Z181)</f>
       </c>
     </row>
-    <row r="182" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A182" s="1"/>
       <c r="D182" s="2"/>
       <c r="G182" s="3"/>
@@ -43562,7 +43562,7 @@
         <f>IF($H182="","",Q182-Z182)</f>
       </c>
     </row>
-    <row r="183" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A183" s="1"/>
       <c r="D183" s="2"/>
       <c r="G183" s="3"/>
@@ -43600,7 +43600,7 @@
         <f>IF($H183="","",Q183-Z183)</f>
       </c>
     </row>
-    <row r="184" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A184" s="1"/>
       <c r="D184" s="2"/>
       <c r="G184" s="3"/>
@@ -43638,7 +43638,7 @@
         <f>IF($H184="","",Q184-Z184)</f>
       </c>
     </row>
-    <row r="185" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A185" s="1"/>
       <c r="D185" s="2"/>
       <c r="G185" s="3"/>
@@ -43676,7 +43676,7 @@
         <f>IF($H185="","",Q185-Z185)</f>
       </c>
     </row>
-    <row r="186" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A186" s="1"/>
       <c r="D186" s="2"/>
       <c r="G186" s="3"/>
@@ -43714,7 +43714,7 @@
         <f>IF($H186="","",Q186-Z186)</f>
       </c>
     </row>
-    <row r="187" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A187" s="1"/>
       <c r="D187" s="2"/>
       <c r="G187" s="3"/>
@@ -43752,7 +43752,7 @@
         <f>IF($H187="","",Q187-Z187)</f>
       </c>
     </row>
-    <row r="188" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A188" s="1"/>
       <c r="D188" s="2"/>
       <c r="G188" s="3"/>
@@ -43790,7 +43790,7 @@
         <f>IF($H188="","",Q188-Z188)</f>
       </c>
     </row>
-    <row r="189" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A189" s="1"/>
       <c r="D189" s="2"/>
       <c r="G189" s="3"/>
@@ -43828,7 +43828,7 @@
         <f>IF($H189="","",Q189-Z189)</f>
       </c>
     </row>
-    <row r="190" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A190" s="1"/>
       <c r="D190" s="2"/>
       <c r="G190" s="3"/>
@@ -43866,7 +43866,7 @@
         <f>IF($H190="","",Q190-Z190)</f>
       </c>
     </row>
-    <row r="191" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A191" s="1"/>
       <c r="D191" s="2"/>
       <c r="G191" s="3"/>
@@ -43904,7 +43904,7 @@
         <f>IF($H191="","",Q191-Z191)</f>
       </c>
     </row>
-    <row r="192" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A192" s="1"/>
       <c r="D192" s="2"/>
       <c r="G192" s="3"/>
@@ -43942,7 +43942,7 @@
         <f>IF($H192="","",Q192-Z192)</f>
       </c>
     </row>
-    <row r="193" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A193" s="1"/>
       <c r="D193" s="2"/>
       <c r="G193" s="3"/>
@@ -43980,7 +43980,7 @@
         <f>IF($H193="","",Q193-Z193)</f>
       </c>
     </row>
-    <row r="194" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A194" s="1"/>
       <c r="D194" s="2"/>
       <c r="G194" s="3"/>
@@ -44018,7 +44018,7 @@
         <f>IF($H194="","",Q194-Z194)</f>
       </c>
     </row>
-    <row r="195" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A195" s="1"/>
       <c r="D195" s="2"/>
       <c r="G195" s="3"/>
@@ -44056,7 +44056,7 @@
         <f>IF($H195="","",Q195-Z195)</f>
       </c>
     </row>
-    <row r="196" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A196" s="1"/>
       <c r="D196" s="2"/>
       <c r="G196" s="3"/>
@@ -44094,7 +44094,7 @@
         <f>IF($H196="","",Q196-Z196)</f>
       </c>
     </row>
-    <row r="197" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A197" s="1"/>
       <c r="D197" s="2"/>
       <c r="G197" s="3"/>
@@ -44132,7 +44132,7 @@
         <f>IF($H197="","",Q197-Z197)</f>
       </c>
     </row>
-    <row r="198" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A198" s="1"/>
       <c r="D198" s="2"/>
       <c r="G198" s="3"/>
@@ -44170,7 +44170,7 @@
         <f>IF($H198="","",Q198-Z198)</f>
       </c>
     </row>
-    <row r="199" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A199" s="1"/>
       <c r="D199" s="2"/>
       <c r="G199" s="3"/>
@@ -44208,7 +44208,7 @@
         <f>IF($H199="","",Q199-Z199)</f>
       </c>
     </row>
-    <row r="200" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A200" s="1"/>
       <c r="D200" s="2"/>
       <c r="G200" s="3"/>
@@ -44246,7 +44246,7 @@
         <f>IF($H200="","",Q200-Z200)</f>
       </c>
     </row>
-    <row r="201" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A201" s="1"/>
       <c r="D201" s="2"/>
       <c r="G201" s="3"/>
@@ -44284,7 +44284,7 @@
         <f>IF($H201="","",Q201-Z201)</f>
       </c>
     </row>
-    <row r="202" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A202" s="1"/>
       <c r="D202" s="2"/>
       <c r="G202" s="3"/>

--- a/templates/SALES_REPORT_TEMPLATE.xlsx
+++ b/templates/SALES_REPORT_TEMPLATE.xlsx
@@ -18026,7 +18026,7 @@
         <f>L2-M2-R2-S2-T2-U2-V2-W2</f>
       </c>
       <c r="Z2" s="3">
-        <f>(Y2-AB2)/K2*100</f>
+        <f>(Y2-AB2)/J2*100</f>
       </c>
       <c r="AA2" s="3">
         <f>M2-X2</f>
@@ -18080,7 +18080,7 @@
         <f>IF($K3="","",L3-M3-R3-S3-T3-U3-V3-W3)</f>
       </c>
       <c r="Z3" s="3">
-        <f>IF($K3="","",(Y3-AB3)/K3*100)</f>
+        <f>IF($K3="","",(Y3-AB3)/J3*100)</f>
       </c>
       <c r="AA3" s="3">
         <f>IF($K3="","",M3-X3)</f>
@@ -18131,7 +18131,7 @@
         <f>IF($K4="","",L4-M4-R4-S4-T4-U4-V4-W4)</f>
       </c>
       <c r="Z4" s="3">
-        <f>IF($K4="","",(Y4-AB4)/K4*100)</f>
+        <f>IF($K4="","",(Y4-AB4)/J4*100)</f>
       </c>
       <c r="AA4" s="3">
         <f>IF($K4="","",M4-X4)</f>
@@ -18182,7 +18182,7 @@
         <f>IF($K5="","",L5-M5-R5-S5-T5-U5-V5-W5)</f>
       </c>
       <c r="Z5" s="3">
-        <f>IF($K5="","",(Y5-AB5)/K5*100)</f>
+        <f>IF($K5="","",(Y5-AB5)/J5*100)</f>
       </c>
       <c r="AA5" s="3">
         <f>IF($K5="","",M5-X5)</f>
@@ -18233,7 +18233,7 @@
         <f>IF($K6="","",L6-M6-R6-S6-T6-U6-V6-W6)</f>
       </c>
       <c r="Z6" s="3">
-        <f>IF($K6="","",(Y6-AB6)/K6*100)</f>
+        <f>IF($K6="","",(Y6-AB6)/J6*100)</f>
       </c>
       <c r="AA6" s="3">
         <f>IF($K6="","",M6-X6)</f>
@@ -18284,7 +18284,7 @@
         <f>IF($K7="","",L7-M7-R7-S7-T7-U7-V7-W7)</f>
       </c>
       <c r="Z7" s="3">
-        <f>IF($K7="","",(Y7-AB7)/K7*100)</f>
+        <f>IF($K7="","",(Y7-AB7)/J7*100)</f>
       </c>
       <c r="AA7" s="3">
         <f>IF($K7="","",M7-X7)</f>
@@ -18335,7 +18335,7 @@
         <f>IF($K8="","",L8-M8-R8-S8-T8-U8-V8-W8)</f>
       </c>
       <c r="Z8" s="3">
-        <f>IF($K8="","",(Y8-AB8)/K8*100)</f>
+        <f>IF($K8="","",(Y8-AB8)/J8*100)</f>
       </c>
       <c r="AA8" s="3">
         <f>IF($K8="","",M8-X8)</f>
@@ -18386,7 +18386,7 @@
         <f>IF($K9="","",L9-M9-R9-S9-T9-U9-V9-W9)</f>
       </c>
       <c r="Z9" s="3">
-        <f>IF($K9="","",(Y9-AB9)/K9*100)</f>
+        <f>IF($K9="","",(Y9-AB9)/J9*100)</f>
       </c>
       <c r="AA9" s="3">
         <f>IF($K9="","",M9-X9)</f>
@@ -18437,7 +18437,7 @@
         <f>IF($K10="","",L10-M10-R10-S10-T10-U10-V10-W10)</f>
       </c>
       <c r="Z10" s="3">
-        <f>IF($K10="","",(Y10-AB10)/K10*100)</f>
+        <f>IF($K10="","",(Y10-AB10)/J10*100)</f>
       </c>
       <c r="AA10" s="3">
         <f>IF($K10="","",M10-X10)</f>
@@ -18488,7 +18488,7 @@
         <f>IF($K11="","",L11-M11-R11-S11-T11-U11-V11-W11)</f>
       </c>
       <c r="Z11" s="3">
-        <f>IF($K11="","",(Y11-AB11)/K11*100)</f>
+        <f>IF($K11="","",(Y11-AB11)/J11*100)</f>
       </c>
       <c r="AA11" s="3">
         <f>IF($K11="","",M11-X11)</f>
@@ -18539,7 +18539,7 @@
         <f>IF($K12="","",L12-M12-R12-S12-T12-U12-V12-W12)</f>
       </c>
       <c r="Z12" s="3">
-        <f>IF($K12="","",(Y12-AB12)/K12*100)</f>
+        <f>IF($K12="","",(Y12-AB12)/J12*100)</f>
       </c>
       <c r="AA12" s="3">
         <f>IF($K12="","",M12-X12)</f>
@@ -18590,7 +18590,7 @@
         <f>IF($K13="","",L13-M13-R13-S13-T13-U13-V13-W13)</f>
       </c>
       <c r="Z13" s="3">
-        <f>IF($K13="","",(Y13-AB13)/K13*100)</f>
+        <f>IF($K13="","",(Y13-AB13)/J13*100)</f>
       </c>
       <c r="AA13" s="3">
         <f>IF($K13="","",M13-X13)</f>
@@ -18641,7 +18641,7 @@
         <f>IF($K14="","",L14-M14-R14-S14-T14-U14-V14-W14)</f>
       </c>
       <c r="Z14" s="3">
-        <f>IF($K14="","",(Y14-AB14)/K14*100)</f>
+        <f>IF($K14="","",(Y14-AB14)/J14*100)</f>
       </c>
       <c r="AA14" s="3">
         <f>IF($K14="","",M14-X14)</f>
@@ -18692,7 +18692,7 @@
         <f>IF($K15="","",L15-M15-R15-S15-T15-U15-V15-W15)</f>
       </c>
       <c r="Z15" s="3">
-        <f>IF($K15="","",(Y15-AB15)/K15*100)</f>
+        <f>IF($K15="","",(Y15-AB15)/J15*100)</f>
       </c>
       <c r="AA15" s="3">
         <f>IF($K15="","",M15-X15)</f>
@@ -18743,7 +18743,7 @@
         <f>IF($K16="","",L16-M16-R16-S16-T16-U16-V16-W16)</f>
       </c>
       <c r="Z16" s="3">
-        <f>IF($K16="","",(Y16-AB16)/K16*100)</f>
+        <f>IF($K16="","",(Y16-AB16)/J16*100)</f>
       </c>
       <c r="AA16" s="3">
         <f>IF($K16="","",M16-X16)</f>
@@ -18794,7 +18794,7 @@
         <f>IF($K17="","",L17-M17-R17-S17-T17-U17-V17-W17)</f>
       </c>
       <c r="Z17" s="3">
-        <f>IF($K17="","",(Y17-AB17)/K17*100)</f>
+        <f>IF($K17="","",(Y17-AB17)/J17*100)</f>
       </c>
       <c r="AA17" s="3">
         <f>IF($K17="","",M17-X17)</f>
@@ -18845,7 +18845,7 @@
         <f>IF($K18="","",L18-M18-R18-S18-T18-U18-V18-W18)</f>
       </c>
       <c r="Z18" s="3">
-        <f>IF($K18="","",(Y18-AB18)/K18*100)</f>
+        <f>IF($K18="","",(Y18-AB18)/J18*100)</f>
       </c>
       <c r="AA18" s="3">
         <f>IF($K18="","",M18-X18)</f>
@@ -18896,7 +18896,7 @@
         <f>IF($K19="","",L19-M19-R19-S19-T19-U19-V19-W19)</f>
       </c>
       <c r="Z19" s="3">
-        <f>IF($K19="","",(Y19-AB19)/K19*100)</f>
+        <f>IF($K19="","",(Y19-AB19)/J19*100)</f>
       </c>
       <c r="AA19" s="3">
         <f>IF($K19="","",M19-X19)</f>
@@ -18947,7 +18947,7 @@
         <f>IF($K20="","",L20-M20-R20-S20-T20-U20-V20-W20)</f>
       </c>
       <c r="Z20" s="3">
-        <f>IF($K20="","",(Y20-AB20)/K20*100)</f>
+        <f>IF($K20="","",(Y20-AB20)/J20*100)</f>
       </c>
       <c r="AA20" s="3">
         <f>IF($K20="","",M20-X20)</f>
@@ -18998,7 +18998,7 @@
         <f>IF($K21="","",L21-M21-R21-S21-T21-U21-V21-W21)</f>
       </c>
       <c r="Z21" s="3">
-        <f>IF($K21="","",(Y21-AB21)/K21*100)</f>
+        <f>IF($K21="","",(Y21-AB21)/J21*100)</f>
       </c>
       <c r="AA21" s="3">
         <f>IF($K21="","",M21-X21)</f>
@@ -19049,7 +19049,7 @@
         <f>IF($K22="","",L22-M22-R22-S22-T22-U22-V22-W22)</f>
       </c>
       <c r="Z22" s="3">
-        <f>IF($K22="","",(Y22-AB22)/K22*100)</f>
+        <f>IF($K22="","",(Y22-AB22)/J22*100)</f>
       </c>
       <c r="AA22" s="3">
         <f>IF($K22="","",M22-X22)</f>
@@ -19100,7 +19100,7 @@
         <f>IF($K23="","",L23-M23-R23-S23-T23-U23-V23-W23)</f>
       </c>
       <c r="Z23" s="3">
-        <f>IF($K23="","",(Y23-AB23)/K23*100)</f>
+        <f>IF($K23="","",(Y23-AB23)/J23*100)</f>
       </c>
       <c r="AA23" s="3">
         <f>IF($K23="","",M23-X23)</f>
@@ -19151,7 +19151,7 @@
         <f>IF($K24="","",L24-M24-R24-S24-T24-U24-V24-W24)</f>
       </c>
       <c r="Z24" s="3">
-        <f>IF($K24="","",(Y24-AB24)/K24*100)</f>
+        <f>IF($K24="","",(Y24-AB24)/J24*100)</f>
       </c>
       <c r="AA24" s="3">
         <f>IF($K24="","",M24-X24)</f>
@@ -19202,7 +19202,7 @@
         <f>IF($K25="","",L25-M25-R25-S25-T25-U25-V25-W25)</f>
       </c>
       <c r="Z25" s="3">
-        <f>IF($K25="","",(Y25-AB25)/K25*100)</f>
+        <f>IF($K25="","",(Y25-AB25)/J25*100)</f>
       </c>
       <c r="AA25" s="3">
         <f>IF($K25="","",M25-X25)</f>
@@ -19253,7 +19253,7 @@
         <f>IF($K26="","",L26-M26-R26-S26-T26-U26-V26-W26)</f>
       </c>
       <c r="Z26" s="3">
-        <f>IF($K26="","",(Y26-AB26)/K26*100)</f>
+        <f>IF($K26="","",(Y26-AB26)/J26*100)</f>
       </c>
       <c r="AA26" s="3">
         <f>IF($K26="","",M26-X26)</f>
@@ -19304,7 +19304,7 @@
         <f>IF($K27="","",L27-M27-R27-S27-T27-U27-V27-W27)</f>
       </c>
       <c r="Z27" s="3">
-        <f>IF($K27="","",(Y27-AB27)/K27*100)</f>
+        <f>IF($K27="","",(Y27-AB27)/J27*100)</f>
       </c>
       <c r="AA27" s="3">
         <f>IF($K27="","",M27-X27)</f>
@@ -19355,7 +19355,7 @@
         <f>IF($K28="","",L28-M28-R28-S28-T28-U28-V28-W28)</f>
       </c>
       <c r="Z28" s="3">
-        <f>IF($K28="","",(Y28-AB28)/K28*100)</f>
+        <f>IF($K28="","",(Y28-AB28)/J28*100)</f>
       </c>
       <c r="AA28" s="3">
         <f>IF($K28="","",M28-X28)</f>
@@ -19406,7 +19406,7 @@
         <f>IF($K29="","",L29-M29-R29-S29-T29-U29-V29-W29)</f>
       </c>
       <c r="Z29" s="3">
-        <f>IF($K29="","",(Y29-AB29)/K29*100)</f>
+        <f>IF($K29="","",(Y29-AB29)/J29*100)</f>
       </c>
       <c r="AA29" s="3">
         <f>IF($K29="","",M29-X29)</f>
@@ -19457,7 +19457,7 @@
         <f>IF($K30="","",L30-M30-R30-S30-T30-U30-V30-W30)</f>
       </c>
       <c r="Z30" s="3">
-        <f>IF($K30="","",(Y30-AB30)/K30*100)</f>
+        <f>IF($K30="","",(Y30-AB30)/J30*100)</f>
       </c>
       <c r="AA30" s="3">
         <f>IF($K30="","",M30-X30)</f>
@@ -19508,7 +19508,7 @@
         <f>IF($K31="","",L31-M31-R31-S31-T31-U31-V31-W31)</f>
       </c>
       <c r="Z31" s="3">
-        <f>IF($K31="","",(Y31-AB31)/K31*100)</f>
+        <f>IF($K31="","",(Y31-AB31)/J31*100)</f>
       </c>
       <c r="AA31" s="3">
         <f>IF($K31="","",M31-X31)</f>
@@ -19559,7 +19559,7 @@
         <f>IF($K32="","",L32-M32-R32-S32-T32-U32-V32-W32)</f>
       </c>
       <c r="Z32" s="3">
-        <f>IF($K32="","",(Y32-AB32)/K32*100)</f>
+        <f>IF($K32="","",(Y32-AB32)/J32*100)</f>
       </c>
       <c r="AA32" s="3">
         <f>IF($K32="","",M32-X32)</f>
@@ -19610,7 +19610,7 @@
         <f>IF($K33="","",L33-M33-R33-S33-T33-U33-V33-W33)</f>
       </c>
       <c r="Z33" s="3">
-        <f>IF($K33="","",(Y33-AB33)/K33*100)</f>
+        <f>IF($K33="","",(Y33-AB33)/J33*100)</f>
       </c>
       <c r="AA33" s="3">
         <f>IF($K33="","",M33-X33)</f>
@@ -19661,7 +19661,7 @@
         <f>IF($K34="","",L34-M34-R34-S34-T34-U34-V34-W34)</f>
       </c>
       <c r="Z34" s="3">
-        <f>IF($K34="","",(Y34-AB34)/K34*100)</f>
+        <f>IF($K34="","",(Y34-AB34)/J34*100)</f>
       </c>
       <c r="AA34" s="3">
         <f>IF($K34="","",M34-X34)</f>
@@ -19712,7 +19712,7 @@
         <f>IF($K35="","",L35-M35-R35-S35-T35-U35-V35-W35)</f>
       </c>
       <c r="Z35" s="3">
-        <f>IF($K35="","",(Y35-AB35)/K35*100)</f>
+        <f>IF($K35="","",(Y35-AB35)/J35*100)</f>
       </c>
       <c r="AA35" s="3">
         <f>IF($K35="","",M35-X35)</f>
@@ -19763,7 +19763,7 @@
         <f>IF($K36="","",L36-M36-R36-S36-T36-U36-V36-W36)</f>
       </c>
       <c r="Z36" s="3">
-        <f>IF($K36="","",(Y36-AB36)/K36*100)</f>
+        <f>IF($K36="","",(Y36-AB36)/J36*100)</f>
       </c>
       <c r="AA36" s="3">
         <f>IF($K36="","",M36-X36)</f>
@@ -19814,7 +19814,7 @@
         <f>IF($K37="","",L37-M37-R37-S37-T37-U37-V37-W37)</f>
       </c>
       <c r="Z37" s="3">
-        <f>IF($K37="","",(Y37-AB37)/K37*100)</f>
+        <f>IF($K37="","",(Y37-AB37)/J37*100)</f>
       </c>
       <c r="AA37" s="3">
         <f>IF($K37="","",M37-X37)</f>
@@ -19865,7 +19865,7 @@
         <f>IF($K38="","",L38-M38-R38-S38-T38-U38-V38-W38)</f>
       </c>
       <c r="Z38" s="3">
-        <f>IF($K38="","",(Y38-AB38)/K38*100)</f>
+        <f>IF($K38="","",(Y38-AB38)/J38*100)</f>
       </c>
       <c r="AA38" s="3">
         <f>IF($K38="","",M38-X38)</f>
@@ -19916,7 +19916,7 @@
         <f>IF($K39="","",L39-M39-R39-S39-T39-U39-V39-W39)</f>
       </c>
       <c r="Z39" s="3">
-        <f>IF($K39="","",(Y39-AB39)/K39*100)</f>
+        <f>IF($K39="","",(Y39-AB39)/J39*100)</f>
       </c>
       <c r="AA39" s="3">
         <f>IF($K39="","",M39-X39)</f>
@@ -19967,7 +19967,7 @@
         <f>IF($K40="","",L40-M40-R40-S40-T40-U40-V40-W40)</f>
       </c>
       <c r="Z40" s="3">
-        <f>IF($K40="","",(Y40-AB40)/K40*100)</f>
+        <f>IF($K40="","",(Y40-AB40)/J40*100)</f>
       </c>
       <c r="AA40" s="3">
         <f>IF($K40="","",M40-X40)</f>
@@ -20018,7 +20018,7 @@
         <f>IF($K41="","",L41-M41-R41-S41-T41-U41-V41-W41)</f>
       </c>
       <c r="Z41" s="3">
-        <f>IF($K41="","",(Y41-AB41)/K41*100)</f>
+        <f>IF($K41="","",(Y41-AB41)/J41*100)</f>
       </c>
       <c r="AA41" s="3">
         <f>IF($K41="","",M41-X41)</f>
@@ -20069,7 +20069,7 @@
         <f>IF($K42="","",L42-M42-R42-S42-T42-U42-V42-W42)</f>
       </c>
       <c r="Z42" s="3">
-        <f>IF($K42="","",(Y42-AB42)/K42*100)</f>
+        <f>IF($K42="","",(Y42-AB42)/J42*100)</f>
       </c>
       <c r="AA42" s="3">
         <f>IF($K42="","",M42-X42)</f>
@@ -20120,7 +20120,7 @@
         <f>IF($K43="","",L43-M43-R43-S43-T43-U43-V43-W43)</f>
       </c>
       <c r="Z43" s="3">
-        <f>IF($K43="","",(Y43-AB43)/K43*100)</f>
+        <f>IF($K43="","",(Y43-AB43)/J43*100)</f>
       </c>
       <c r="AA43" s="3">
         <f>IF($K43="","",M43-X43)</f>
@@ -20171,7 +20171,7 @@
         <f>IF($K44="","",L44-M44-R44-S44-T44-U44-V44-W44)</f>
       </c>
       <c r="Z44" s="3">
-        <f>IF($K44="","",(Y44-AB44)/K44*100)</f>
+        <f>IF($K44="","",(Y44-AB44)/J44*100)</f>
       </c>
       <c r="AA44" s="3">
         <f>IF($K44="","",M44-X44)</f>
@@ -20222,7 +20222,7 @@
         <f>IF($K45="","",L45-M45-R45-S45-T45-U45-V45-W45)</f>
       </c>
       <c r="Z45" s="3">
-        <f>IF($K45="","",(Y45-AB45)/K45*100)</f>
+        <f>IF($K45="","",(Y45-AB45)/J45*100)</f>
       </c>
       <c r="AA45" s="3">
         <f>IF($K45="","",M45-X45)</f>
@@ -20273,7 +20273,7 @@
         <f>IF($K46="","",L46-M46-R46-S46-T46-U46-V46-W46)</f>
       </c>
       <c r="Z46" s="3">
-        <f>IF($K46="","",(Y46-AB46)/K46*100)</f>
+        <f>IF($K46="","",(Y46-AB46)/J46*100)</f>
       </c>
       <c r="AA46" s="3">
         <f>IF($K46="","",M46-X46)</f>
@@ -20324,7 +20324,7 @@
         <f>IF($K47="","",L47-M47-R47-S47-T47-U47-V47-W47)</f>
       </c>
       <c r="Z47" s="3">
-        <f>IF($K47="","",(Y47-AB47)/K47*100)</f>
+        <f>IF($K47="","",(Y47-AB47)/J47*100)</f>
       </c>
       <c r="AA47" s="3">
         <f>IF($K47="","",M47-X47)</f>
@@ -20375,7 +20375,7 @@
         <f>IF($K48="","",L48-M48-R48-S48-T48-U48-V48-W48)</f>
       </c>
       <c r="Z48" s="3">
-        <f>IF($K48="","",(Y48-AB48)/K48*100)</f>
+        <f>IF($K48="","",(Y48-AB48)/J48*100)</f>
       </c>
       <c r="AA48" s="3">
         <f>IF($K48="","",M48-X48)</f>
@@ -20426,7 +20426,7 @@
         <f>IF($K49="","",L49-M49-R49-S49-T49-U49-V49-W49)</f>
       </c>
       <c r="Z49" s="3">
-        <f>IF($K49="","",(Y49-AB49)/K49*100)</f>
+        <f>IF($K49="","",(Y49-AB49)/J49*100)</f>
       </c>
       <c r="AA49" s="3">
         <f>IF($K49="","",M49-X49)</f>
@@ -20477,7 +20477,7 @@
         <f>IF($K50="","",L50-M50-R50-S50-T50-U50-V50-W50)</f>
       </c>
       <c r="Z50" s="3">
-        <f>IF($K50="","",(Y50-AB50)/K50*100)</f>
+        <f>IF($K50="","",(Y50-AB50)/J50*100)</f>
       </c>
       <c r="AA50" s="3">
         <f>IF($K50="","",M50-X50)</f>
@@ -20528,7 +20528,7 @@
         <f>IF($K51="","",L51-M51-R51-S51-T51-U51-V51-W51)</f>
       </c>
       <c r="Z51" s="3">
-        <f>IF($K51="","",(Y51-AB51)/K51*100)</f>
+        <f>IF($K51="","",(Y51-AB51)/J51*100)</f>
       </c>
       <c r="AA51" s="3">
         <f>IF($K51="","",M51-X51)</f>
@@ -20579,7 +20579,7 @@
         <f>IF($K52="","",L52-M52-R52-S52-T52-U52-V52-W52)</f>
       </c>
       <c r="Z52" s="3">
-        <f>IF($K52="","",(Y52-AB52)/K52*100)</f>
+        <f>IF($K52="","",(Y52-AB52)/J52*100)</f>
       </c>
       <c r="AA52" s="3">
         <f>IF($K52="","",M52-X52)</f>
@@ -20630,7 +20630,7 @@
         <f>IF($K53="","",L53-M53-R53-S53-T53-U53-V53-W53)</f>
       </c>
       <c r="Z53" s="3">
-        <f>IF($K53="","",(Y53-AB53)/K53*100)</f>
+        <f>IF($K53="","",(Y53-AB53)/J53*100)</f>
       </c>
       <c r="AA53" s="3">
         <f>IF($K53="","",M53-X53)</f>
@@ -20681,7 +20681,7 @@
         <f>IF($K54="","",L54-M54-R54-S54-T54-U54-V54-W54)</f>
       </c>
       <c r="Z54" s="3">
-        <f>IF($K54="","",(Y54-AB54)/K54*100)</f>
+        <f>IF($K54="","",(Y54-AB54)/J54*100)</f>
       </c>
       <c r="AA54" s="3">
         <f>IF($K54="","",M54-X54)</f>
@@ -20732,7 +20732,7 @@
         <f>IF($K55="","",L55-M55-R55-S55-T55-U55-V55-W55)</f>
       </c>
       <c r="Z55" s="3">
-        <f>IF($K55="","",(Y55-AB55)/K55*100)</f>
+        <f>IF($K55="","",(Y55-AB55)/J55*100)</f>
       </c>
       <c r="AA55" s="3">
         <f>IF($K55="","",M55-X55)</f>
@@ -20783,7 +20783,7 @@
         <f>IF($K56="","",L56-M56-R56-S56-T56-U56-V56-W56)</f>
       </c>
       <c r="Z56" s="3">
-        <f>IF($K56="","",(Y56-AB56)/K56*100)</f>
+        <f>IF($K56="","",(Y56-AB56)/J56*100)</f>
       </c>
       <c r="AA56" s="3">
         <f>IF($K56="","",M56-X56)</f>
@@ -20834,7 +20834,7 @@
         <f>IF($K57="","",L57-M57-R57-S57-T57-U57-V57-W57)</f>
       </c>
       <c r="Z57" s="3">
-        <f>IF($K57="","",(Y57-AB57)/K57*100)</f>
+        <f>IF($K57="","",(Y57-AB57)/J57*100)</f>
       </c>
       <c r="AA57" s="3">
         <f>IF($K57="","",M57-X57)</f>
@@ -20885,7 +20885,7 @@
         <f>IF($K58="","",L58-M58-R58-S58-T58-U58-V58-W58)</f>
       </c>
       <c r="Z58" s="3">
-        <f>IF($K58="","",(Y58-AB58)/K58*100)</f>
+        <f>IF($K58="","",(Y58-AB58)/J58*100)</f>
       </c>
       <c r="AA58" s="3">
         <f>IF($K58="","",M58-X58)</f>
@@ -20936,7 +20936,7 @@
         <f>IF($K59="","",L59-M59-R59-S59-T59-U59-V59-W59)</f>
       </c>
       <c r="Z59" s="3">
-        <f>IF($K59="","",(Y59-AB59)/K59*100)</f>
+        <f>IF($K59="","",(Y59-AB59)/J59*100)</f>
       </c>
       <c r="AA59" s="3">
         <f>IF($K59="","",M59-X59)</f>
@@ -20987,7 +20987,7 @@
         <f>IF($K60="","",L60-M60-R60-S60-T60-U60-V60-W60)</f>
       </c>
       <c r="Z60" s="3">
-        <f>IF($K60="","",(Y60-AB60)/K60*100)</f>
+        <f>IF($K60="","",(Y60-AB60)/J60*100)</f>
       </c>
       <c r="AA60" s="3">
         <f>IF($K60="","",M60-X60)</f>
@@ -21038,7 +21038,7 @@
         <f>IF($K61="","",L61-M61-R61-S61-T61-U61-V61-W61)</f>
       </c>
       <c r="Z61" s="3">
-        <f>IF($K61="","",(Y61-AB61)/K61*100)</f>
+        <f>IF($K61="","",(Y61-AB61)/J61*100)</f>
       </c>
       <c r="AA61" s="3">
         <f>IF($K61="","",M61-X61)</f>
@@ -21089,7 +21089,7 @@
         <f>IF($K62="","",L62-M62-R62-S62-T62-U62-V62-W62)</f>
       </c>
       <c r="Z62" s="3">
-        <f>IF($K62="","",(Y62-AB62)/K62*100)</f>
+        <f>IF($K62="","",(Y62-AB62)/J62*100)</f>
       </c>
       <c r="AA62" s="3">
         <f>IF($K62="","",M62-X62)</f>
@@ -21140,7 +21140,7 @@
         <f>IF($K63="","",L63-M63-R63-S63-T63-U63-V63-W63)</f>
       </c>
       <c r="Z63" s="3">
-        <f>IF($K63="","",(Y63-AB63)/K63*100)</f>
+        <f>IF($K63="","",(Y63-AB63)/J63*100)</f>
       </c>
       <c r="AA63" s="3">
         <f>IF($K63="","",M63-X63)</f>
@@ -21191,7 +21191,7 @@
         <f>IF($K64="","",L64-M64-R64-S64-T64-U64-V64-W64)</f>
       </c>
       <c r="Z64" s="3">
-        <f>IF($K64="","",(Y64-AB64)/K64*100)</f>
+        <f>IF($K64="","",(Y64-AB64)/J64*100)</f>
       </c>
       <c r="AA64" s="3">
         <f>IF($K64="","",M64-X64)</f>
@@ -21242,7 +21242,7 @@
         <f>IF($K65="","",L65-M65-R65-S65-T65-U65-V65-W65)</f>
       </c>
       <c r="Z65" s="3">
-        <f>IF($K65="","",(Y65-AB65)/K65*100)</f>
+        <f>IF($K65="","",(Y65-AB65)/J65*100)</f>
       </c>
       <c r="AA65" s="3">
         <f>IF($K65="","",M65-X65)</f>
@@ -21293,7 +21293,7 @@
         <f>IF($K66="","",L66-M66-R66-S66-T66-U66-V66-W66)</f>
       </c>
       <c r="Z66" s="3">
-        <f>IF($K66="","",(Y66-AB66)/K66*100)</f>
+        <f>IF($K66="","",(Y66-AB66)/J66*100)</f>
       </c>
       <c r="AA66" s="3">
         <f>IF($K66="","",M66-X66)</f>
@@ -21344,7 +21344,7 @@
         <f>IF($K67="","",L67-M67-R67-S67-T67-U67-V67-W67)</f>
       </c>
       <c r="Z67" s="3">
-        <f>IF($K67="","",(Y67-AB67)/K67*100)</f>
+        <f>IF($K67="","",(Y67-AB67)/J67*100)</f>
       </c>
       <c r="AA67" s="3">
         <f>IF($K67="","",M67-X67)</f>
@@ -21395,7 +21395,7 @@
         <f>IF($K68="","",L68-M68-R68-S68-T68-U68-V68-W68)</f>
       </c>
       <c r="Z68" s="3">
-        <f>IF($K68="","",(Y68-AB68)/K68*100)</f>
+        <f>IF($K68="","",(Y68-AB68)/J68*100)</f>
       </c>
       <c r="AA68" s="3">
         <f>IF($K68="","",M68-X68)</f>
@@ -21446,7 +21446,7 @@
         <f>IF($K69="","",L69-M69-R69-S69-T69-U69-V69-W69)</f>
       </c>
       <c r="Z69" s="3">
-        <f>IF($K69="","",(Y69-AB69)/K69*100)</f>
+        <f>IF($K69="","",(Y69-AB69)/J69*100)</f>
       </c>
       <c r="AA69" s="3">
         <f>IF($K69="","",M69-X69)</f>
@@ -21497,7 +21497,7 @@
         <f>IF($K70="","",L70-M70-R70-S70-T70-U70-V70-W70)</f>
       </c>
       <c r="Z70" s="3">
-        <f>IF($K70="","",(Y70-AB70)/K70*100)</f>
+        <f>IF($K70="","",(Y70-AB70)/J70*100)</f>
       </c>
       <c r="AA70" s="3">
         <f>IF($K70="","",M70-X70)</f>
@@ -21548,7 +21548,7 @@
         <f>IF($K71="","",L71-M71-R71-S71-T71-U71-V71-W71)</f>
       </c>
       <c r="Z71" s="3">
-        <f>IF($K71="","",(Y71-AB71)/K71*100)</f>
+        <f>IF($K71="","",(Y71-AB71)/J71*100)</f>
       </c>
       <c r="AA71" s="3">
         <f>IF($K71="","",M71-X71)</f>
@@ -21599,7 +21599,7 @@
         <f>IF($K72="","",L72-M72-R72-S72-T72-U72-V72-W72)</f>
       </c>
       <c r="Z72" s="3">
-        <f>IF($K72="","",(Y72-AB72)/K72*100)</f>
+        <f>IF($K72="","",(Y72-AB72)/J72*100)</f>
       </c>
       <c r="AA72" s="3">
         <f>IF($K72="","",M72-X72)</f>
@@ -21650,7 +21650,7 @@
         <f>IF($K73="","",L73-M73-R73-S73-T73-U73-V73-W73)</f>
       </c>
       <c r="Z73" s="3">
-        <f>IF($K73="","",(Y73-AB73)/K73*100)</f>
+        <f>IF($K73="","",(Y73-AB73)/J73*100)</f>
       </c>
       <c r="AA73" s="3">
         <f>IF($K73="","",M73-X73)</f>
@@ -21701,7 +21701,7 @@
         <f>IF($K74="","",L74-M74-R74-S74-T74-U74-V74-W74)</f>
       </c>
       <c r="Z74" s="3">
-        <f>IF($K74="","",(Y74-AB74)/K74*100)</f>
+        <f>IF($K74="","",(Y74-AB74)/J74*100)</f>
       </c>
       <c r="AA74" s="3">
         <f>IF($K74="","",M74-X74)</f>
@@ -21752,7 +21752,7 @@
         <f>IF($K75="","",L75-M75-R75-S75-T75-U75-V75-W75)</f>
       </c>
       <c r="Z75" s="3">
-        <f>IF($K75="","",(Y75-AB75)/K75*100)</f>
+        <f>IF($K75="","",(Y75-AB75)/J75*100)</f>
       </c>
       <c r="AA75" s="3">
         <f>IF($K75="","",M75-X75)</f>
@@ -21803,7 +21803,7 @@
         <f>IF($K76="","",L76-M76-R76-S76-T76-U76-V76-W76)</f>
       </c>
       <c r="Z76" s="3">
-        <f>IF($K76="","",(Y76-AB76)/K76*100)</f>
+        <f>IF($K76="","",(Y76-AB76)/J76*100)</f>
       </c>
       <c r="AA76" s="3">
         <f>IF($K76="","",M76-X76)</f>
@@ -21854,7 +21854,7 @@
         <f>IF($K77="","",L77-M77-R77-S77-T77-U77-V77-W77)</f>
       </c>
       <c r="Z77" s="3">
-        <f>IF($K77="","",(Y77-AB77)/K77*100)</f>
+        <f>IF($K77="","",(Y77-AB77)/J77*100)</f>
       </c>
       <c r="AA77" s="3">
         <f>IF($K77="","",M77-X77)</f>
@@ -21905,7 +21905,7 @@
         <f>IF($K78="","",L78-M78-R78-S78-T78-U78-V78-W78)</f>
       </c>
       <c r="Z78" s="3">
-        <f>IF($K78="","",(Y78-AB78)/K78*100)</f>
+        <f>IF($K78="","",(Y78-AB78)/J78*100)</f>
       </c>
       <c r="AA78" s="3">
         <f>IF($K78="","",M78-X78)</f>
@@ -21956,7 +21956,7 @@
         <f>IF($K79="","",L79-M79-R79-S79-T79-U79-V79-W79)</f>
       </c>
       <c r="Z79" s="3">
-        <f>IF($K79="","",(Y79-AB79)/K79*100)</f>
+        <f>IF($K79="","",(Y79-AB79)/J79*100)</f>
       </c>
       <c r="AA79" s="3">
         <f>IF($K79="","",M79-X79)</f>
@@ -22007,7 +22007,7 @@
         <f>IF($K80="","",L80-M80-R80-S80-T80-U80-V80-W80)</f>
       </c>
       <c r="Z80" s="3">
-        <f>IF($K80="","",(Y80-AB80)/K80*100)</f>
+        <f>IF($K80="","",(Y80-AB80)/J80*100)</f>
       </c>
       <c r="AA80" s="3">
         <f>IF($K80="","",M80-X80)</f>
@@ -22058,7 +22058,7 @@
         <f>IF($K81="","",L81-M81-R81-S81-T81-U81-V81-W81)</f>
       </c>
       <c r="Z81" s="3">
-        <f>IF($K81="","",(Y81-AB81)/K81*100)</f>
+        <f>IF($K81="","",(Y81-AB81)/J81*100)</f>
       </c>
       <c r="AA81" s="3">
         <f>IF($K81="","",M81-X81)</f>
@@ -22109,7 +22109,7 @@
         <f>IF($K82="","",L82-M82-R82-S82-T82-U82-V82-W82)</f>
       </c>
       <c r="Z82" s="3">
-        <f>IF($K82="","",(Y82-AB82)/K82*100)</f>
+        <f>IF($K82="","",(Y82-AB82)/J82*100)</f>
       </c>
       <c r="AA82" s="3">
         <f>IF($K82="","",M82-X82)</f>
@@ -22160,7 +22160,7 @@
         <f>IF($K83="","",L83-M83-R83-S83-T83-U83-V83-W83)</f>
       </c>
       <c r="Z83" s="3">
-        <f>IF($K83="","",(Y83-AB83)/K83*100)</f>
+        <f>IF($K83="","",(Y83-AB83)/J83*100)</f>
       </c>
       <c r="AA83" s="3">
         <f>IF($K83="","",M83-X83)</f>
@@ -22211,7 +22211,7 @@
         <f>IF($K84="","",L84-M84-R84-S84-T84-U84-V84-W84)</f>
       </c>
       <c r="Z84" s="3">
-        <f>IF($K84="","",(Y84-AB84)/K84*100)</f>
+        <f>IF($K84="","",(Y84-AB84)/J84*100)</f>
       </c>
       <c r="AA84" s="3">
         <f>IF($K84="","",M84-X84)</f>
@@ -22262,7 +22262,7 @@
         <f>IF($K85="","",L85-M85-R85-S85-T85-U85-V85-W85)</f>
       </c>
       <c r="Z85" s="3">
-        <f>IF($K85="","",(Y85-AB85)/K85*100)</f>
+        <f>IF($K85="","",(Y85-AB85)/J85*100)</f>
       </c>
       <c r="AA85" s="3">
         <f>IF($K85="","",M85-X85)</f>
@@ -22313,7 +22313,7 @@
         <f>IF($K86="","",L86-M86-R86-S86-T86-U86-V86-W86)</f>
       </c>
       <c r="Z86" s="3">
-        <f>IF($K86="","",(Y86-AB86)/K86*100)</f>
+        <f>IF($K86="","",(Y86-AB86)/J86*100)</f>
       </c>
       <c r="AA86" s="3">
         <f>IF($K86="","",M86-X86)</f>
@@ -22364,7 +22364,7 @@
         <f>IF($K87="","",L87-M87-R87-S87-T87-U87-V87-W87)</f>
       </c>
       <c r="Z87" s="3">
-        <f>IF($K87="","",(Y87-AB87)/K87*100)</f>
+        <f>IF($K87="","",(Y87-AB87)/J87*100)</f>
       </c>
       <c r="AA87" s="3">
         <f>IF($K87="","",M87-X87)</f>
@@ -22415,7 +22415,7 @@
         <f>IF($K88="","",L88-M88-R88-S88-T88-U88-V88-W88)</f>
       </c>
       <c r="Z88" s="3">
-        <f>IF($K88="","",(Y88-AB88)/K88*100)</f>
+        <f>IF($K88="","",(Y88-AB88)/J88*100)</f>
       </c>
       <c r="AA88" s="3">
         <f>IF($K88="","",M88-X88)</f>
@@ -22466,7 +22466,7 @@
         <f>IF($K89="","",L89-M89-R89-S89-T89-U89-V89-W89)</f>
       </c>
       <c r="Z89" s="3">
-        <f>IF($K89="","",(Y89-AB89)/K89*100)</f>
+        <f>IF($K89="","",(Y89-AB89)/J89*100)</f>
       </c>
       <c r="AA89" s="3">
         <f>IF($K89="","",M89-X89)</f>
@@ -22517,7 +22517,7 @@
         <f>IF($K90="","",L90-M90-R90-S90-T90-U90-V90-W90)</f>
       </c>
       <c r="Z90" s="3">
-        <f>IF($K90="","",(Y90-AB90)/K90*100)</f>
+        <f>IF($K90="","",(Y90-AB90)/J90*100)</f>
       </c>
       <c r="AA90" s="3">
         <f>IF($K90="","",M90-X90)</f>
@@ -22568,7 +22568,7 @@
         <f>IF($K91="","",L91-M91-R91-S91-T91-U91-V91-W91)</f>
       </c>
       <c r="Z91" s="3">
-        <f>IF($K91="","",(Y91-AB91)/K91*100)</f>
+        <f>IF($K91="","",(Y91-AB91)/J91*100)</f>
       </c>
       <c r="AA91" s="3">
         <f>IF($K91="","",M91-X91)</f>
@@ -22619,7 +22619,7 @@
         <f>IF($K92="","",L92-M92-R92-S92-T92-U92-V92-W92)</f>
       </c>
       <c r="Z92" s="3">
-        <f>IF($K92="","",(Y92-AB92)/K92*100)</f>
+        <f>IF($K92="","",(Y92-AB92)/J92*100)</f>
       </c>
       <c r="AA92" s="3">
         <f>IF($K92="","",M92-X92)</f>
@@ -22670,7 +22670,7 @@
         <f>IF($K93="","",L93-M93-R93-S93-T93-U93-V93-W93)</f>
       </c>
       <c r="Z93" s="3">
-        <f>IF($K93="","",(Y93-AB93)/K93*100)</f>
+        <f>IF($K93="","",(Y93-AB93)/J93*100)</f>
       </c>
       <c r="AA93" s="3">
         <f>IF($K93="","",M93-X93)</f>
@@ -22721,7 +22721,7 @@
         <f>IF($K94="","",L94-M94-R94-S94-T94-U94-V94-W94)</f>
       </c>
       <c r="Z94" s="3">
-        <f>IF($K94="","",(Y94-AB94)/K94*100)</f>
+        <f>IF($K94="","",(Y94-AB94)/J94*100)</f>
       </c>
       <c r="AA94" s="3">
         <f>IF($K94="","",M94-X94)</f>
@@ -22772,7 +22772,7 @@
         <f>IF($K95="","",L95-M95-R95-S95-T95-U95-V95-W95)</f>
       </c>
       <c r="Z95" s="3">
-        <f>IF($K95="","",(Y95-AB95)/K95*100)</f>
+        <f>IF($K95="","",(Y95-AB95)/J95*100)</f>
       </c>
       <c r="AA95" s="3">
         <f>IF($K95="","",M95-X95)</f>
@@ -22823,7 +22823,7 @@
         <f>IF($K96="","",L96-M96-R96-S96-T96-U96-V96-W96)</f>
       </c>
       <c r="Z96" s="3">
-        <f>IF($K96="","",(Y96-AB96)/K96*100)</f>
+        <f>IF($K96="","",(Y96-AB96)/J96*100)</f>
       </c>
       <c r="AA96" s="3">
         <f>IF($K96="","",M96-X96)</f>
@@ -22874,7 +22874,7 @@
         <f>IF($K97="","",L97-M97-R97-S97-T97-U97-V97-W97)</f>
       </c>
       <c r="Z97" s="3">
-        <f>IF($K97="","",(Y97-AB97)/K97*100)</f>
+        <f>IF($K97="","",(Y97-AB97)/J97*100)</f>
       </c>
       <c r="AA97" s="3">
         <f>IF($K97="","",M97-X97)</f>
@@ -22925,7 +22925,7 @@
         <f>IF($K98="","",L98-M98-R98-S98-T98-U98-V98-W98)</f>
       </c>
       <c r="Z98" s="3">
-        <f>IF($K98="","",(Y98-AB98)/K98*100)</f>
+        <f>IF($K98="","",(Y98-AB98)/J98*100)</f>
       </c>
       <c r="AA98" s="3">
         <f>IF($K98="","",M98-X98)</f>
@@ -22976,7 +22976,7 @@
         <f>IF($K99="","",L99-M99-R99-S99-T99-U99-V99-W99)</f>
       </c>
       <c r="Z99" s="3">
-        <f>IF($K99="","",(Y99-AB99)/K99*100)</f>
+        <f>IF($K99="","",(Y99-AB99)/J99*100)</f>
       </c>
       <c r="AA99" s="3">
         <f>IF($K99="","",M99-X99)</f>
@@ -23027,7 +23027,7 @@
         <f>IF($K100="","",L100-M100-R100-S100-T100-U100-V100-W100)</f>
       </c>
       <c r="Z100" s="3">
-        <f>IF($K100="","",(Y100-AB100)/K100*100)</f>
+        <f>IF($K100="","",(Y100-AB100)/J100*100)</f>
       </c>
       <c r="AA100" s="3">
         <f>IF($K100="","",M100-X100)</f>
@@ -23078,7 +23078,7 @@
         <f>IF($K101="","",L101-M101-R101-S101-T101-U101-V101-W101)</f>
       </c>
       <c r="Z101" s="3">
-        <f>IF($K101="","",(Y101-AB101)/K101*100)</f>
+        <f>IF($K101="","",(Y101-AB101)/J101*100)</f>
       </c>
       <c r="AA101" s="3">
         <f>IF($K101="","",M101-X101)</f>
@@ -23129,7 +23129,7 @@
         <f>IF($K102="","",L102-M102-R102-S102-T102-U102-V102-W102)</f>
       </c>
       <c r="Z102" s="3">
-        <f>IF($K102="","",(Y102-AB102)/K102*100)</f>
+        <f>IF($K102="","",(Y102-AB102)/J102*100)</f>
       </c>
       <c r="AA102" s="3">
         <f>IF($K102="","",M102-X102)</f>
@@ -23180,7 +23180,7 @@
         <f>IF($K103="","",L103-M103-R103-S103-T103-U103-V103-W103)</f>
       </c>
       <c r="Z103" s="3">
-        <f>IF($K103="","",(Y103-AB103)/K103*100)</f>
+        <f>IF($K103="","",(Y103-AB103)/J103*100)</f>
       </c>
       <c r="AA103" s="3">
         <f>IF($K103="","",M103-X103)</f>
@@ -23231,7 +23231,7 @@
         <f>IF($K104="","",L104-M104-R104-S104-T104-U104-V104-W104)</f>
       </c>
       <c r="Z104" s="3">
-        <f>IF($K104="","",(Y104-AB104)/K104*100)</f>
+        <f>IF($K104="","",(Y104-AB104)/J104*100)</f>
       </c>
       <c r="AA104" s="3">
         <f>IF($K104="","",M104-X104)</f>
@@ -23282,7 +23282,7 @@
         <f>IF($K105="","",L105-M105-R105-S105-T105-U105-V105-W105)</f>
       </c>
       <c r="Z105" s="3">
-        <f>IF($K105="","",(Y105-AB105)/K105*100)</f>
+        <f>IF($K105="","",(Y105-AB105)/J105*100)</f>
       </c>
       <c r="AA105" s="3">
         <f>IF($K105="","",M105-X105)</f>
@@ -23333,7 +23333,7 @@
         <f>IF($K106="","",L106-M106-R106-S106-T106-U106-V106-W106)</f>
       </c>
       <c r="Z106" s="3">
-        <f>IF($K106="","",(Y106-AB106)/K106*100)</f>
+        <f>IF($K106="","",(Y106-AB106)/J106*100)</f>
       </c>
       <c r="AA106" s="3">
         <f>IF($K106="","",M106-X106)</f>
@@ -23384,7 +23384,7 @@
         <f>IF($K107="","",L107-M107-R107-S107-T107-U107-V107-W107)</f>
       </c>
       <c r="Z107" s="3">
-        <f>IF($K107="","",(Y107-AB107)/K107*100)</f>
+        <f>IF($K107="","",(Y107-AB107)/J107*100)</f>
       </c>
       <c r="AA107" s="3">
         <f>IF($K107="","",M107-X107)</f>
@@ -23435,7 +23435,7 @@
         <f>IF($K108="","",L108-M108-R108-S108-T108-U108-V108-W108)</f>
       </c>
       <c r="Z108" s="3">
-        <f>IF($K108="","",(Y108-AB108)/K108*100)</f>
+        <f>IF($K108="","",(Y108-AB108)/J108*100)</f>
       </c>
       <c r="AA108" s="3">
         <f>IF($K108="","",M108-X108)</f>
@@ -23486,7 +23486,7 @@
         <f>IF($K109="","",L109-M109-R109-S109-T109-U109-V109-W109)</f>
       </c>
       <c r="Z109" s="3">
-        <f>IF($K109="","",(Y109-AB109)/K109*100)</f>
+        <f>IF($K109="","",(Y109-AB109)/J109*100)</f>
       </c>
       <c r="AA109" s="3">
         <f>IF($K109="","",M109-X109)</f>
@@ -23537,7 +23537,7 @@
         <f>IF($K110="","",L110-M110-R110-S110-T110-U110-V110-W110)</f>
       </c>
       <c r="Z110" s="3">
-        <f>IF($K110="","",(Y110-AB110)/K110*100)</f>
+        <f>IF($K110="","",(Y110-AB110)/J110*100)</f>
       </c>
       <c r="AA110" s="3">
         <f>IF($K110="","",M110-X110)</f>
@@ -23588,7 +23588,7 @@
         <f>IF($K111="","",L111-M111-R111-S111-T111-U111-V111-W111)</f>
       </c>
       <c r="Z111" s="3">
-        <f>IF($K111="","",(Y111-AB111)/K111*100)</f>
+        <f>IF($K111="","",(Y111-AB111)/J111*100)</f>
       </c>
       <c r="AA111" s="3">
         <f>IF($K111="","",M111-X111)</f>
@@ -23639,7 +23639,7 @@
         <f>IF($K112="","",L112-M112-R112-S112-T112-U112-V112-W112)</f>
       </c>
       <c r="Z112" s="3">
-        <f>IF($K112="","",(Y112-AB112)/K112*100)</f>
+        <f>IF($K112="","",(Y112-AB112)/J112*100)</f>
       </c>
       <c r="AA112" s="3">
         <f>IF($K112="","",M112-X112)</f>
@@ -23690,7 +23690,7 @@
         <f>IF($K113="","",L113-M113-R113-S113-T113-U113-V113-W113)</f>
       </c>
       <c r="Z113" s="3">
-        <f>IF($K113="","",(Y113-AB113)/K113*100)</f>
+        <f>IF($K113="","",(Y113-AB113)/J113*100)</f>
       </c>
       <c r="AA113" s="3">
         <f>IF($K113="","",M113-X113)</f>
@@ -23741,7 +23741,7 @@
         <f>IF($K114="","",L114-M114-R114-S114-T114-U114-V114-W114)</f>
       </c>
       <c r="Z114" s="3">
-        <f>IF($K114="","",(Y114-AB114)/K114*100)</f>
+        <f>IF($K114="","",(Y114-AB114)/J114*100)</f>
       </c>
       <c r="AA114" s="3">
         <f>IF($K114="","",M114-X114)</f>
@@ -23792,7 +23792,7 @@
         <f>IF($K115="","",L115-M115-R115-S115-T115-U115-V115-W115)</f>
       </c>
       <c r="Z115" s="3">
-        <f>IF($K115="","",(Y115-AB115)/K115*100)</f>
+        <f>IF($K115="","",(Y115-AB115)/J115*100)</f>
       </c>
       <c r="AA115" s="3">
         <f>IF($K115="","",M115-X115)</f>
@@ -23843,7 +23843,7 @@
         <f>IF($K116="","",L116-M116-R116-S116-T116-U116-V116-W116)</f>
       </c>
       <c r="Z116" s="3">
-        <f>IF($K116="","",(Y116-AB116)/K116*100)</f>
+        <f>IF($K116="","",(Y116-AB116)/J116*100)</f>
       </c>
       <c r="AA116" s="3">
         <f>IF($K116="","",M116-X116)</f>
@@ -23894,7 +23894,7 @@
         <f>IF($K117="","",L117-M117-R117-S117-T117-U117-V117-W117)</f>
       </c>
       <c r="Z117" s="3">
-        <f>IF($K117="","",(Y117-AB117)/K117*100)</f>
+        <f>IF($K117="","",(Y117-AB117)/J117*100)</f>
       </c>
       <c r="AA117" s="3">
         <f>IF($K117="","",M117-X117)</f>
@@ -23945,7 +23945,7 @@
         <f>IF($K118="","",L118-M118-R118-S118-T118-U118-V118-W118)</f>
       </c>
       <c r="Z118" s="3">
-        <f>IF($K118="","",(Y118-AB118)/K118*100)</f>
+        <f>IF($K118="","",(Y118-AB118)/J118*100)</f>
       </c>
       <c r="AA118" s="3">
         <f>IF($K118="","",M118-X118)</f>
@@ -23996,7 +23996,7 @@
         <f>IF($K119="","",L119-M119-R119-S119-T119-U119-V119-W119)</f>
       </c>
       <c r="Z119" s="3">
-        <f>IF($K119="","",(Y119-AB119)/K119*100)</f>
+        <f>IF($K119="","",(Y119-AB119)/J119*100)</f>
       </c>
       <c r="AA119" s="3">
         <f>IF($K119="","",M119-X119)</f>
@@ -24047,7 +24047,7 @@
         <f>IF($K120="","",L120-M120-R120-S120-T120-U120-V120-W120)</f>
       </c>
       <c r="Z120" s="3">
-        <f>IF($K120="","",(Y120-AB120)/K120*100)</f>
+        <f>IF($K120="","",(Y120-AB120)/J120*100)</f>
       </c>
       <c r="AA120" s="3">
         <f>IF($K120="","",M120-X120)</f>
@@ -24098,7 +24098,7 @@
         <f>IF($K121="","",L121-M121-R121-S121-T121-U121-V121-W121)</f>
       </c>
       <c r="Z121" s="3">
-        <f>IF($K121="","",(Y121-AB121)/K121*100)</f>
+        <f>IF($K121="","",(Y121-AB121)/J121*100)</f>
       </c>
       <c r="AA121" s="3">
         <f>IF($K121="","",M121-X121)</f>
@@ -24149,7 +24149,7 @@
         <f>IF($K122="","",L122-M122-R122-S122-T122-U122-V122-W122)</f>
       </c>
       <c r="Z122" s="3">
-        <f>IF($K122="","",(Y122-AB122)/K122*100)</f>
+        <f>IF($K122="","",(Y122-AB122)/J122*100)</f>
       </c>
       <c r="AA122" s="3">
         <f>IF($K122="","",M122-X122)</f>
@@ -24200,7 +24200,7 @@
         <f>IF($K123="","",L123-M123-R123-S123-T123-U123-V123-W123)</f>
       </c>
       <c r="Z123" s="3">
-        <f>IF($K123="","",(Y123-AB123)/K123*100)</f>
+        <f>IF($K123="","",(Y123-AB123)/J123*100)</f>
       </c>
       <c r="AA123" s="3">
         <f>IF($K123="","",M123-X123)</f>
@@ -24251,7 +24251,7 @@
         <f>IF($K124="","",L124-M124-R124-S124-T124-U124-V124-W124)</f>
       </c>
       <c r="Z124" s="3">
-        <f>IF($K124="","",(Y124-AB124)/K124*100)</f>
+        <f>IF($K124="","",(Y124-AB124)/J124*100)</f>
       </c>
       <c r="AA124" s="3">
         <f>IF($K124="","",M124-X124)</f>
@@ -24302,7 +24302,7 @@
         <f>IF($K125="","",L125-M125-R125-S125-T125-U125-V125-W125)</f>
       </c>
       <c r="Z125" s="3">
-        <f>IF($K125="","",(Y125-AB125)/K125*100)</f>
+        <f>IF($K125="","",(Y125-AB125)/J125*100)</f>
       </c>
       <c r="AA125" s="3">
         <f>IF($K125="","",M125-X125)</f>
@@ -24353,7 +24353,7 @@
         <f>IF($K126="","",L126-M126-R126-S126-T126-U126-V126-W126)</f>
       </c>
       <c r="Z126" s="3">
-        <f>IF($K126="","",(Y126-AB126)/K126*100)</f>
+        <f>IF($K126="","",(Y126-AB126)/J126*100)</f>
       </c>
       <c r="AA126" s="3">
         <f>IF($K126="","",M126-X126)</f>
@@ -24404,7 +24404,7 @@
         <f>IF($K127="","",L127-M127-R127-S127-T127-U127-V127-W127)</f>
       </c>
       <c r="Z127" s="3">
-        <f>IF($K127="","",(Y127-AB127)/K127*100)</f>
+        <f>IF($K127="","",(Y127-AB127)/J127*100)</f>
       </c>
       <c r="AA127" s="3">
         <f>IF($K127="","",M127-X127)</f>
@@ -24455,7 +24455,7 @@
         <f>IF($K128="","",L128-M128-R128-S128-T128-U128-V128-W128)</f>
       </c>
       <c r="Z128" s="3">
-        <f>IF($K128="","",(Y128-AB128)/K128*100)</f>
+        <f>IF($K128="","",(Y128-AB128)/J128*100)</f>
       </c>
       <c r="AA128" s="3">
         <f>IF($K128="","",M128-X128)</f>
@@ -24506,7 +24506,7 @@
         <f>IF($K129="","",L129-M129-R129-S129-T129-U129-V129-W129)</f>
       </c>
       <c r="Z129" s="3">
-        <f>IF($K129="","",(Y129-AB129)/K129*100)</f>
+        <f>IF($K129="","",(Y129-AB129)/J129*100)</f>
       </c>
       <c r="AA129" s="3">
         <f>IF($K129="","",M129-X129)</f>
@@ -24557,7 +24557,7 @@
         <f>IF($K130="","",L130-M130-R130-S130-T130-U130-V130-W130)</f>
       </c>
       <c r="Z130" s="3">
-        <f>IF($K130="","",(Y130-AB130)/K130*100)</f>
+        <f>IF($K130="","",(Y130-AB130)/J130*100)</f>
       </c>
       <c r="AA130" s="3">
         <f>IF($K130="","",M130-X130)</f>
@@ -24608,7 +24608,7 @@
         <f>IF($K131="","",L131-M131-R131-S131-T131-U131-V131-W131)</f>
       </c>
       <c r="Z131" s="3">
-        <f>IF($K131="","",(Y131-AB131)/K131*100)</f>
+        <f>IF($K131="","",(Y131-AB131)/J131*100)</f>
       </c>
       <c r="AA131" s="3">
         <f>IF($K131="","",M131-X131)</f>
@@ -24659,7 +24659,7 @@
         <f>IF($K132="","",L132-M132-R132-S132-T132-U132-V132-W132)</f>
       </c>
       <c r="Z132" s="3">
-        <f>IF($K132="","",(Y132-AB132)/K132*100)</f>
+        <f>IF($K132="","",(Y132-AB132)/J132*100)</f>
       </c>
       <c r="AA132" s="3">
         <f>IF($K132="","",M132-X132)</f>
@@ -24710,7 +24710,7 @@
         <f>IF($K133="","",L133-M133-R133-S133-T133-U133-V133-W133)</f>
       </c>
       <c r="Z133" s="3">
-        <f>IF($K133="","",(Y133-AB133)/K133*100)</f>
+        <f>IF($K133="","",(Y133-AB133)/J133*100)</f>
       </c>
       <c r="AA133" s="3">
         <f>IF($K133="","",M133-X133)</f>
@@ -24761,7 +24761,7 @@
         <f>IF($K134="","",L134-M134-R134-S134-T134-U134-V134-W134)</f>
       </c>
       <c r="Z134" s="3">
-        <f>IF($K134="","",(Y134-AB134)/K134*100)</f>
+        <f>IF($K134="","",(Y134-AB134)/J134*100)</f>
       </c>
       <c r="AA134" s="3">
         <f>IF($K134="","",M134-X134)</f>
@@ -24812,7 +24812,7 @@
         <f>IF($K135="","",L135-M135-R135-S135-T135-U135-V135-W135)</f>
       </c>
       <c r="Z135" s="3">
-        <f>IF($K135="","",(Y135-AB135)/K135*100)</f>
+        <f>IF($K135="","",(Y135-AB135)/J135*100)</f>
       </c>
       <c r="AA135" s="3">
         <f>IF($K135="","",M135-X135)</f>
@@ -24863,7 +24863,7 @@
         <f>IF($K136="","",L136-M136-R136-S136-T136-U136-V136-W136)</f>
       </c>
       <c r="Z136" s="3">
-        <f>IF($K136="","",(Y136-AB136)/K136*100)</f>
+        <f>IF($K136="","",(Y136-AB136)/J136*100)</f>
       </c>
       <c r="AA136" s="3">
         <f>IF($K136="","",M136-X136)</f>
@@ -24914,7 +24914,7 @@
         <f>IF($K137="","",L137-M137-R137-S137-T137-U137-V137-W137)</f>
       </c>
       <c r="Z137" s="3">
-        <f>IF($K137="","",(Y137-AB137)/K137*100)</f>
+        <f>IF($K137="","",(Y137-AB137)/J137*100)</f>
       </c>
       <c r="AA137" s="3">
         <f>IF($K137="","",M137-X137)</f>
@@ -24965,7 +24965,7 @@
         <f>IF($K138="","",L138-M138-R138-S138-T138-U138-V138-W138)</f>
       </c>
       <c r="Z138" s="3">
-        <f>IF($K138="","",(Y138-AB138)/K138*100)</f>
+        <f>IF($K138="","",(Y138-AB138)/J138*100)</f>
       </c>
       <c r="AA138" s="3">
         <f>IF($K138="","",M138-X138)</f>
@@ -25016,7 +25016,7 @@
         <f>IF($K139="","",L139-M139-R139-S139-T139-U139-V139-W139)</f>
       </c>
       <c r="Z139" s="3">
-        <f>IF($K139="","",(Y139-AB139)/K139*100)</f>
+        <f>IF($K139="","",(Y139-AB139)/J139*100)</f>
       </c>
       <c r="AA139" s="3">
         <f>IF($K139="","",M139-X139)</f>
@@ -25067,7 +25067,7 @@
         <f>IF($K140="","",L140-M140-R140-S140-T140-U140-V140-W140)</f>
       </c>
       <c r="Z140" s="3">
-        <f>IF($K140="","",(Y140-AB140)/K140*100)</f>
+        <f>IF($K140="","",(Y140-AB140)/J140*100)</f>
       </c>
       <c r="AA140" s="3">
         <f>IF($K140="","",M140-X140)</f>
@@ -25118,7 +25118,7 @@
         <f>IF($K141="","",L141-M141-R141-S141-T141-U141-V141-W141)</f>
       </c>
       <c r="Z141" s="3">
-        <f>IF($K141="","",(Y141-AB141)/K141*100)</f>
+        <f>IF($K141="","",(Y141-AB141)/J141*100)</f>
       </c>
       <c r="AA141" s="3">
         <f>IF($K141="","",M141-X141)</f>
@@ -25169,7 +25169,7 @@
         <f>IF($K142="","",L142-M142-R142-S142-T142-U142-V142-W142)</f>
       </c>
       <c r="Z142" s="3">
-        <f>IF($K142="","",(Y142-AB142)/K142*100)</f>
+        <f>IF($K142="","",(Y142-AB142)/J142*100)</f>
       </c>
       <c r="AA142" s="3">
         <f>IF($K142="","",M142-X142)</f>
@@ -25220,7 +25220,7 @@
         <f>IF($K143="","",L143-M143-R143-S143-T143-U143-V143-W143)</f>
       </c>
       <c r="Z143" s="3">
-        <f>IF($K143="","",(Y143-AB143)/K143*100)</f>
+        <f>IF($K143="","",(Y143-AB143)/J143*100)</f>
       </c>
       <c r="AA143" s="3">
         <f>IF($K143="","",M143-X143)</f>
@@ -25271,7 +25271,7 @@
         <f>IF($K144="","",L144-M144-R144-S144-T144-U144-V144-W144)</f>
       </c>
       <c r="Z144" s="3">
-        <f>IF($K144="","",(Y144-AB144)/K144*100)</f>
+        <f>IF($K144="","",(Y144-AB144)/J144*100)</f>
       </c>
       <c r="AA144" s="3">
         <f>IF($K144="","",M144-X144)</f>
@@ -25322,7 +25322,7 @@
         <f>IF($K145="","",L145-M145-R145-S145-T145-U145-V145-W145)</f>
       </c>
       <c r="Z145" s="3">
-        <f>IF($K145="","",(Y145-AB145)/K145*100)</f>
+        <f>IF($K145="","",(Y145-AB145)/J145*100)</f>
       </c>
       <c r="AA145" s="3">
         <f>IF($K145="","",M145-X145)</f>
@@ -25373,7 +25373,7 @@
         <f>IF($K146="","",L146-M146-R146-S146-T146-U146-V146-W146)</f>
       </c>
       <c r="Z146" s="3">
-        <f>IF($K146="","",(Y146-AB146)/K146*100)</f>
+        <f>IF($K146="","",(Y146-AB146)/J146*100)</f>
       </c>
       <c r="AA146" s="3">
         <f>IF($K146="","",M146-X146)</f>
@@ -25424,7 +25424,7 @@
         <f>IF($K147="","",L147-M147-R147-S147-T147-U147-V147-W147)</f>
       </c>
       <c r="Z147" s="3">
-        <f>IF($K147="","",(Y147-AB147)/K147*100)</f>
+        <f>IF($K147="","",(Y147-AB147)/J147*100)</f>
       </c>
       <c r="AA147" s="3">
         <f>IF($K147="","",M147-X147)</f>
@@ -25475,7 +25475,7 @@
         <f>IF($K148="","",L148-M148-R148-S148-T148-U148-V148-W148)</f>
       </c>
       <c r="Z148" s="3">
-        <f>IF($K148="","",(Y148-AB148)/K148*100)</f>
+        <f>IF($K148="","",(Y148-AB148)/J148*100)</f>
       </c>
       <c r="AA148" s="3">
         <f>IF($K148="","",M148-X148)</f>
@@ -25526,7 +25526,7 @@
         <f>IF($K149="","",L149-M149-R149-S149-T149-U149-V149-W149)</f>
       </c>
       <c r="Z149" s="3">
-        <f>IF($K149="","",(Y149-AB149)/K149*100)</f>
+        <f>IF($K149="","",(Y149-AB149)/J149*100)</f>
       </c>
       <c r="AA149" s="3">
         <f>IF($K149="","",M149-X149)</f>
@@ -25577,7 +25577,7 @@
         <f>IF($K150="","",L150-M150-R150-S150-T150-U150-V150-W150)</f>
       </c>
       <c r="Z150" s="3">
-        <f>IF($K150="","",(Y150-AB150)/K150*100)</f>
+        <f>IF($K150="","",(Y150-AB150)/J150*100)</f>
       </c>
       <c r="AA150" s="3">
         <f>IF($K150="","",M150-X150)</f>
@@ -25628,7 +25628,7 @@
         <f>IF($K151="","",L151-M151-R151-S151-T151-U151-V151-W151)</f>
       </c>
       <c r="Z151" s="3">
-        <f>IF($K151="","",(Y151-AB151)/K151*100)</f>
+        <f>IF($K151="","",(Y151-AB151)/J151*100)</f>
       </c>
       <c r="AA151" s="3">
         <f>IF($K151="","",M151-X151)</f>
@@ -25679,7 +25679,7 @@
         <f>IF($K152="","",L152-M152-R152-S152-T152-U152-V152-W152)</f>
       </c>
       <c r="Z152" s="3">
-        <f>IF($K152="","",(Y152-AB152)/K152*100)</f>
+        <f>IF($K152="","",(Y152-AB152)/J152*100)</f>
       </c>
       <c r="AA152" s="3">
         <f>IF($K152="","",M152-X152)</f>
@@ -25730,7 +25730,7 @@
         <f>IF($K153="","",L153-M153-R153-S153-T153-U153-V153-W153)</f>
       </c>
       <c r="Z153" s="3">
-        <f>IF($K153="","",(Y153-AB153)/K153*100)</f>
+        <f>IF($K153="","",(Y153-AB153)/J153*100)</f>
       </c>
       <c r="AA153" s="3">
         <f>IF($K153="","",M153-X153)</f>
@@ -25781,7 +25781,7 @@
         <f>IF($K154="","",L154-M154-R154-S154-T154-U154-V154-W154)</f>
       </c>
       <c r="Z154" s="3">
-        <f>IF($K154="","",(Y154-AB154)/K154*100)</f>
+        <f>IF($K154="","",(Y154-AB154)/J154*100)</f>
       </c>
       <c r="AA154" s="3">
         <f>IF($K154="","",M154-X154)</f>
@@ -25832,7 +25832,7 @@
         <f>IF($K155="","",L155-M155-R155-S155-T155-U155-V155-W155)</f>
       </c>
       <c r="Z155" s="3">
-        <f>IF($K155="","",(Y155-AB155)/K155*100)</f>
+        <f>IF($K155="","",(Y155-AB155)/J155*100)</f>
       </c>
       <c r="AA155" s="3">
         <f>IF($K155="","",M155-X155)</f>
@@ -25883,7 +25883,7 @@
         <f>IF($K156="","",L156-M156-R156-S156-T156-U156-V156-W156)</f>
       </c>
       <c r="Z156" s="3">
-        <f>IF($K156="","",(Y156-AB156)/K156*100)</f>
+        <f>IF($K156="","",(Y156-AB156)/J156*100)</f>
       </c>
       <c r="AA156" s="3">
         <f>IF($K156="","",M156-X156)</f>
@@ -25934,7 +25934,7 @@
         <f>IF($K157="","",L157-M157-R157-S157-T157-U157-V157-W157)</f>
       </c>
       <c r="Z157" s="3">
-        <f>IF($K157="","",(Y157-AB157)/K157*100)</f>
+        <f>IF($K157="","",(Y157-AB157)/J157*100)</f>
       </c>
       <c r="AA157" s="3">
         <f>IF($K157="","",M157-X157)</f>
@@ -25985,7 +25985,7 @@
         <f>IF($K158="","",L158-M158-R158-S158-T158-U158-V158-W158)</f>
       </c>
       <c r="Z158" s="3">
-        <f>IF($K158="","",(Y158-AB158)/K158*100)</f>
+        <f>IF($K158="","",(Y158-AB158)/J158*100)</f>
       </c>
       <c r="AA158" s="3">
         <f>IF($K158="","",M158-X158)</f>
@@ -26036,7 +26036,7 @@
         <f>IF($K159="","",L159-M159-R159-S159-T159-U159-V159-W159)</f>
       </c>
       <c r="Z159" s="3">
-        <f>IF($K159="","",(Y159-AB159)/K159*100)</f>
+        <f>IF($K159="","",(Y159-AB159)/J159*100)</f>
       </c>
       <c r="AA159" s="3">
         <f>IF($K159="","",M159-X159)</f>
@@ -26087,7 +26087,7 @@
         <f>IF($K160="","",L160-M160-R160-S160-T160-U160-V160-W160)</f>
       </c>
       <c r="Z160" s="3">
-        <f>IF($K160="","",(Y160-AB160)/K160*100)</f>
+        <f>IF($K160="","",(Y160-AB160)/J160*100)</f>
       </c>
       <c r="AA160" s="3">
         <f>IF($K160="","",M160-X160)</f>
@@ -26138,7 +26138,7 @@
         <f>IF($K161="","",L161-M161-R161-S161-T161-U161-V161-W161)</f>
       </c>
       <c r="Z161" s="3">
-        <f>IF($K161="","",(Y161-AB161)/K161*100)</f>
+        <f>IF($K161="","",(Y161-AB161)/J161*100)</f>
       </c>
       <c r="AA161" s="3">
         <f>IF($K161="","",M161-X161)</f>
@@ -26189,7 +26189,7 @@
         <f>IF($K162="","",L162-M162-R162-S162-T162-U162-V162-W162)</f>
       </c>
       <c r="Z162" s="3">
-        <f>IF($K162="","",(Y162-AB162)/K162*100)</f>
+        <f>IF($K162="","",(Y162-AB162)/J162*100)</f>
       </c>
       <c r="AA162" s="3">
         <f>IF($K162="","",M162-X162)</f>
@@ -26240,7 +26240,7 @@
         <f>IF($K163="","",L163-M163-R163-S163-T163-U163-V163-W163)</f>
       </c>
       <c r="Z163" s="3">
-        <f>IF($K163="","",(Y163-AB163)/K163*100)</f>
+        <f>IF($K163="","",(Y163-AB163)/J163*100)</f>
       </c>
       <c r="AA163" s="3">
         <f>IF($K163="","",M163-X163)</f>
@@ -26291,7 +26291,7 @@
         <f>IF($K164="","",L164-M164-R164-S164-T164-U164-V164-W164)</f>
       </c>
       <c r="Z164" s="3">
-        <f>IF($K164="","",(Y164-AB164)/K164*100)</f>
+        <f>IF($K164="","",(Y164-AB164)/J164*100)</f>
       </c>
       <c r="AA164" s="3">
         <f>IF($K164="","",M164-X164)</f>
@@ -26342,7 +26342,7 @@
         <f>IF($K165="","",L165-M165-R165-S165-T165-U165-V165-W165)</f>
       </c>
       <c r="Z165" s="3">
-        <f>IF($K165="","",(Y165-AB165)/K165*100)</f>
+        <f>IF($K165="","",(Y165-AB165)/J165*100)</f>
       </c>
       <c r="AA165" s="3">
         <f>IF($K165="","",M165-X165)</f>
@@ -26393,7 +26393,7 @@
         <f>IF($K166="","",L166-M166-R166-S166-T166-U166-V166-W166)</f>
       </c>
       <c r="Z166" s="3">
-        <f>IF($K166="","",(Y166-AB166)/K166*100)</f>
+        <f>IF($K166="","",(Y166-AB166)/J166*100)</f>
       </c>
       <c r="AA166" s="3">
         <f>IF($K166="","",M166-X166)</f>
@@ -26444,7 +26444,7 @@
         <f>IF($K167="","",L167-M167-R167-S167-T167-U167-V167-W167)</f>
       </c>
       <c r="Z167" s="3">
-        <f>IF($K167="","",(Y167-AB167)/K167*100)</f>
+        <f>IF($K167="","",(Y167-AB167)/J167*100)</f>
       </c>
       <c r="AA167" s="3">
         <f>IF($K167="","",M167-X167)</f>
@@ -26495,7 +26495,7 @@
         <f>IF($K168="","",L168-M168-R168-S168-T168-U168-V168-W168)</f>
       </c>
       <c r="Z168" s="3">
-        <f>IF($K168="","",(Y168-AB168)/K168*100)</f>
+        <f>IF($K168="","",(Y168-AB168)/J168*100)</f>
       </c>
       <c r="AA168" s="3">
         <f>IF($K168="","",M168-X168)</f>
@@ -26546,7 +26546,7 @@
         <f>IF($K169="","",L169-M169-R169-S169-T169-U169-V169-W169)</f>
       </c>
       <c r="Z169" s="3">
-        <f>IF($K169="","",(Y169-AB169)/K169*100)</f>
+        <f>IF($K169="","",(Y169-AB169)/J169*100)</f>
       </c>
       <c r="AA169" s="3">
         <f>IF($K169="","",M169-X169)</f>
@@ -26597,7 +26597,7 @@
         <f>IF($K170="","",L170-M170-R170-S170-T170-U170-V170-W170)</f>
       </c>
       <c r="Z170" s="3">
-        <f>IF($K170="","",(Y170-AB170)/K170*100)</f>
+        <f>IF($K170="","",(Y170-AB170)/J170*100)</f>
       </c>
       <c r="AA170" s="3">
         <f>IF($K170="","",M170-X170)</f>
@@ -26648,7 +26648,7 @@
         <f>IF($K171="","",L171-M171-R171-S171-T171-U171-V171-W171)</f>
       </c>
       <c r="Z171" s="3">
-        <f>IF($K171="","",(Y171-AB171)/K171*100)</f>
+        <f>IF($K171="","",(Y171-AB171)/J171*100)</f>
       </c>
       <c r="AA171" s="3">
         <f>IF($K171="","",M171-X171)</f>
@@ -26699,7 +26699,7 @@
         <f>IF($K172="","",L172-M172-R172-S172-T172-U172-V172-W172)</f>
       </c>
       <c r="Z172" s="3">
-        <f>IF($K172="","",(Y172-AB172)/K172*100)</f>
+        <f>IF($K172="","",(Y172-AB172)/J172*100)</f>
       </c>
       <c r="AA172" s="3">
         <f>IF($K172="","",M172-X172)</f>
@@ -26750,7 +26750,7 @@
         <f>IF($K173="","",L173-M173-R173-S173-T173-U173-V173-W173)</f>
       </c>
       <c r="Z173" s="3">
-        <f>IF($K173="","",(Y173-AB173)/K173*100)</f>
+        <f>IF($K173="","",(Y173-AB173)/J173*100)</f>
       </c>
       <c r="AA173" s="3">
         <f>IF($K173="","",M173-X173)</f>
@@ -26801,7 +26801,7 @@
         <f>IF($K174="","",L174-M174-R174-S174-T174-U174-V174-W174)</f>
       </c>
       <c r="Z174" s="3">
-        <f>IF($K174="","",(Y174-AB174)/K174*100)</f>
+        <f>IF($K174="","",(Y174-AB174)/J174*100)</f>
       </c>
       <c r="AA174" s="3">
         <f>IF($K174="","",M174-X174)</f>
@@ -26852,7 +26852,7 @@
         <f>IF($K175="","",L175-M175-R175-S175-T175-U175-V175-W175)</f>
       </c>
       <c r="Z175" s="3">
-        <f>IF($K175="","",(Y175-AB175)/K175*100)</f>
+        <f>IF($K175="","",(Y175-AB175)/J175*100)</f>
       </c>
       <c r="AA175" s="3">
         <f>IF($K175="","",M175-X175)</f>
@@ -26903,7 +26903,7 @@
         <f>IF($K176="","",L176-M176-R176-S176-T176-U176-V176-W176)</f>
       </c>
       <c r="Z176" s="3">
-        <f>IF($K176="","",(Y176-AB176)/K176*100)</f>
+        <f>IF($K176="","",(Y176-AB176)/J176*100)</f>
       </c>
       <c r="AA176" s="3">
         <f>IF($K176="","",M176-X176)</f>
@@ -26954,7 +26954,7 @@
         <f>IF($K177="","",L177-M177-R177-S177-T177-U177-V177-W177)</f>
       </c>
       <c r="Z177" s="3">
-        <f>IF($K177="","",(Y177-AB177)/K177*100)</f>
+        <f>IF($K177="","",(Y177-AB177)/J177*100)</f>
       </c>
       <c r="AA177" s="3">
         <f>IF($K177="","",M177-X177)</f>
@@ -27005,7 +27005,7 @@
         <f>IF($K178="","",L178-M178-R178-S178-T178-U178-V178-W178)</f>
       </c>
       <c r="Z178" s="3">
-        <f>IF($K178="","",(Y178-AB178)/K178*100)</f>
+        <f>IF($K178="","",(Y178-AB178)/J178*100)</f>
       </c>
       <c r="AA178" s="3">
         <f>IF($K178="","",M178-X178)</f>
@@ -27056,7 +27056,7 @@
         <f>IF($K179="","",L179-M179-R179-S179-T179-U179-V179-W179)</f>
       </c>
       <c r="Z179" s="3">
-        <f>IF($K179="","",(Y179-AB179)/K179*100)</f>
+        <f>IF($K179="","",(Y179-AB179)/J179*100)</f>
       </c>
       <c r="AA179" s="3">
         <f>IF($K179="","",M179-X179)</f>
@@ -27107,7 +27107,7 @@
         <f>IF($K180="","",L180-M180-R180-S180-T180-U180-V180-W180)</f>
       </c>
       <c r="Z180" s="3">
-        <f>IF($K180="","",(Y180-AB180)/K180*100)</f>
+        <f>IF($K180="","",(Y180-AB180)/J180*100)</f>
       </c>
       <c r="AA180" s="3">
         <f>IF($K180="","",M180-X180)</f>
@@ -27158,7 +27158,7 @@
         <f>IF($K181="","",L181-M181-R181-S181-T181-U181-V181-W181)</f>
       </c>
       <c r="Z181" s="3">
-        <f>IF($K181="","",(Y181-AB181)/K181*100)</f>
+        <f>IF($K181="","",(Y181-AB181)/J181*100)</f>
       </c>
       <c r="AA181" s="3">
         <f>IF($K181="","",M181-X181)</f>
@@ -27209,7 +27209,7 @@
         <f>IF($K182="","",L182-M182-R182-S182-T182-U182-V182-W182)</f>
       </c>
       <c r="Z182" s="3">
-        <f>IF($K182="","",(Y182-AB182)/K182*100)</f>
+        <f>IF($K182="","",(Y182-AB182)/J182*100)</f>
       </c>
       <c r="AA182" s="3">
         <f>IF($K182="","",M182-X182)</f>
@@ -27260,7 +27260,7 @@
         <f>IF($K183="","",L183-M183-R183-S183-T183-U183-V183-W183)</f>
       </c>
       <c r="Z183" s="3">
-        <f>IF($K183="","",(Y183-AB183)/K183*100)</f>
+        <f>IF($K183="","",(Y183-AB183)/J183*100)</f>
       </c>
       <c r="AA183" s="3">
         <f>IF($K183="","",M183-X183)</f>
@@ -27311,7 +27311,7 @@
         <f>IF($K184="","",L184-M184-R184-S184-T184-U184-V184-W184)</f>
       </c>
       <c r="Z184" s="3">
-        <f>IF($K184="","",(Y184-AB184)/K184*100)</f>
+        <f>IF($K184="","",(Y184-AB184)/J184*100)</f>
       </c>
       <c r="AA184" s="3">
         <f>IF($K184="","",M184-X184)</f>
@@ -27362,7 +27362,7 @@
         <f>IF($K185="","",L185-M185-R185-S185-T185-U185-V185-W185)</f>
       </c>
       <c r="Z185" s="3">
-        <f>IF($K185="","",(Y185-AB185)/K185*100)</f>
+        <f>IF($K185="","",(Y185-AB185)/J185*100)</f>
       </c>
       <c r="AA185" s="3">
         <f>IF($K185="","",M185-X185)</f>
@@ -27413,7 +27413,7 @@
         <f>IF($K186="","",L186-M186-R186-S186-T186-U186-V186-W186)</f>
       </c>
       <c r="Z186" s="3">
-        <f>IF($K186="","",(Y186-AB186)/K186*100)</f>
+        <f>IF($K186="","",(Y186-AB186)/J186*100)</f>
       </c>
       <c r="AA186" s="3">
         <f>IF($K186="","",M186-X186)</f>
@@ -27464,7 +27464,7 @@
         <f>IF($K187="","",L187-M187-R187-S187-T187-U187-V187-W187)</f>
       </c>
       <c r="Z187" s="3">
-        <f>IF($K187="","",(Y187-AB187)/K187*100)</f>
+        <f>IF($K187="","",(Y187-AB187)/J187*100)</f>
       </c>
       <c r="AA187" s="3">
         <f>IF($K187="","",M187-X187)</f>
@@ -27515,7 +27515,7 @@
         <f>IF($K188="","",L188-M188-R188-S188-T188-U188-V188-W188)</f>
       </c>
       <c r="Z188" s="3">
-        <f>IF($K188="","",(Y188-AB188)/K188*100)</f>
+        <f>IF($K188="","",(Y188-AB188)/J188*100)</f>
       </c>
       <c r="AA188" s="3">
         <f>IF($K188="","",M188-X188)</f>
@@ -27566,7 +27566,7 @@
         <f>IF($K189="","",L189-M189-R189-S189-T189-U189-V189-W189)</f>
       </c>
       <c r="Z189" s="3">
-        <f>IF($K189="","",(Y189-AB189)/K189*100)</f>
+        <f>IF($K189="","",(Y189-AB189)/J189*100)</f>
       </c>
       <c r="AA189" s="3">
         <f>IF($K189="","",M189-X189)</f>
@@ -27617,7 +27617,7 @@
         <f>IF($K190="","",L190-M190-R190-S190-T190-U190-V190-W190)</f>
       </c>
       <c r="Z190" s="3">
-        <f>IF($K190="","",(Y190-AB190)/K190*100)</f>
+        <f>IF($K190="","",(Y190-AB190)/J190*100)</f>
       </c>
       <c r="AA190" s="3">
         <f>IF($K190="","",M190-X190)</f>
@@ -27668,7 +27668,7 @@
         <f>IF($K191="","",L191-M191-R191-S191-T191-U191-V191-W191)</f>
       </c>
       <c r="Z191" s="3">
-        <f>IF($K191="","",(Y191-AB191)/K191*100)</f>
+        <f>IF($K191="","",(Y191-AB191)/J191*100)</f>
       </c>
       <c r="AA191" s="3">
         <f>IF($K191="","",M191-X191)</f>
@@ -27719,7 +27719,7 @@
         <f>IF($K192="","",L192-M192-R192-S192-T192-U192-V192-W192)</f>
       </c>
       <c r="Z192" s="3">
-        <f>IF($K192="","",(Y192-AB192)/K192*100)</f>
+        <f>IF($K192="","",(Y192-AB192)/J192*100)</f>
       </c>
       <c r="AA192" s="3">
         <f>IF($K192="","",M192-X192)</f>
@@ -27770,7 +27770,7 @@
         <f>IF($K193="","",L193-M193-R193-S193-T193-U193-V193-W193)</f>
       </c>
       <c r="Z193" s="3">
-        <f>IF($K193="","",(Y193-AB193)/K193*100)</f>
+        <f>IF($K193="","",(Y193-AB193)/J193*100)</f>
       </c>
       <c r="AA193" s="3">
         <f>IF($K193="","",M193-X193)</f>
@@ -27821,7 +27821,7 @@
         <f>IF($K194="","",L194-M194-R194-S194-T194-U194-V194-W194)</f>
       </c>
       <c r="Z194" s="3">
-        <f>IF($K194="","",(Y194-AB194)/K194*100)</f>
+        <f>IF($K194="","",(Y194-AB194)/J194*100)</f>
       </c>
       <c r="AA194" s="3">
         <f>IF($K194="","",M194-X194)</f>
@@ -27872,7 +27872,7 @@
         <f>IF($K195="","",L195-M195-R195-S195-T195-U195-V195-W195)</f>
       </c>
       <c r="Z195" s="3">
-        <f>IF($K195="","",(Y195-AB195)/K195*100)</f>
+        <f>IF($K195="","",(Y195-AB195)/J195*100)</f>
       </c>
       <c r="AA195" s="3">
         <f>IF($K195="","",M195-X195)</f>
@@ -27923,7 +27923,7 @@
         <f>IF($K196="","",L196-M196-R196-S196-T196-U196-V196-W196)</f>
       </c>
       <c r="Z196" s="3">
-        <f>IF($K196="","",(Y196-AB196)/K196*100)</f>
+        <f>IF($K196="","",(Y196-AB196)/J196*100)</f>
       </c>
       <c r="AA196" s="3">
         <f>IF($K196="","",M196-X196)</f>
@@ -27974,7 +27974,7 @@
         <f>IF($K197="","",L197-M197-R197-S197-T197-U197-V197-W197)</f>
       </c>
       <c r="Z197" s="3">
-        <f>IF($K197="","",(Y197-AB197)/K197*100)</f>
+        <f>IF($K197="","",(Y197-AB197)/J197*100)</f>
       </c>
       <c r="AA197" s="3">
         <f>IF($K197="","",M197-X197)</f>
@@ -28025,7 +28025,7 @@
         <f>IF($K198="","",L198-M198-R198-S198-T198-U198-V198-W198)</f>
       </c>
       <c r="Z198" s="3">
-        <f>IF($K198="","",(Y198-AB198)/K198*100)</f>
+        <f>IF($K198="","",(Y198-AB198)/J198*100)</f>
       </c>
       <c r="AA198" s="3">
         <f>IF($K198="","",M198-X198)</f>
@@ -28076,7 +28076,7 @@
         <f>IF($K199="","",L199-M199-R199-S199-T199-U199-V199-W199)</f>
       </c>
       <c r="Z199" s="3">
-        <f>IF($K199="","",(Y199-AB199)/K199*100)</f>
+        <f>IF($K199="","",(Y199-AB199)/J199*100)</f>
       </c>
       <c r="AA199" s="3">
         <f>IF($K199="","",M199-X199)</f>
@@ -28127,7 +28127,7 @@
         <f>IF($K200="","",L200-M200-R200-S200-T200-U200-V200-W200)</f>
       </c>
       <c r="Z200" s="3">
-        <f>IF($K200="","",(Y200-AB200)/K200*100)</f>
+        <f>IF($K200="","",(Y200-AB200)/J200*100)</f>
       </c>
       <c r="AA200" s="3">
         <f>IF($K200="","",M200-X200)</f>
@@ -28178,7 +28178,7 @@
         <f>IF($K201="","",L201-M201-R201-S201-T201-U201-V201-W201)</f>
       </c>
       <c r="Z201" s="3">
-        <f>IF($K201="","",(Y201-AB201)/K201*100)</f>
+        <f>IF($K201="","",(Y201-AB201)/J201*100)</f>
       </c>
       <c r="AA201" s="3">
         <f>IF($K201="","",M201-X201)</f>
@@ -28229,7 +28229,7 @@
         <f>IF($K202="","",L202-M202-R202-S202-T202-U202-V202-W202)</f>
       </c>
       <c r="Z202" s="3">
-        <f>IF($K202="","",(Y202-AB202)/K202*100)</f>
+        <f>IF($K202="","",(Y202-AB202)/J202*100)</f>
       </c>
       <c r="AA202" s="3">
         <f>IF($K202="","",M202-X202)</f>
